--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,6 +86,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -528,24 +534,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>BUGÜN</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>1</v>
@@ -558,17 +564,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (1g/+1)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (0g/0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 34 hisse / 24 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -580,102 +586,100 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (19g/-13)
-M - TP5/20G - %93 / 41 işlem - ONAY (0g/0)
-R - TP5/10G - %61 / 99 işlem - ADAY (8g/-7)
-R - TP5/20G - %81 / 94 işlem - ADAY (8g/-7)</t>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/+2)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (3g/-4)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (3g/0)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 24 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 29 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -687,108 +691,109 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>M-TP2/10G, M-TP5/20G, M-TP5/10G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/-2)
-I - TP5/20G - %83 / 60 işlem - ADAY (18g/-2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (18g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (18g/-2)</t>
+          <t>M - TP2/10G - %98 / 59 işlem - ONAY (0g/0)
+M - TP5/20G - %93 / 41 işlem - ONAY (4g/-4)
+M - TP5/10G - %71 / 49 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY M: TDA ve PFY-S birlikte dönüş teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 29 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (0g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (2g/0)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (0g/0)
+I - TP5/20G - %83 / 60 işlem - ADAY (19g/-2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (19g/-2)
+R - TP5/20G - %81 / 94 işlem - ADAY (19g/-2)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 29 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -799,20 +804,20 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -830,12 +835,12 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (16g/-9)
-E - TP5/10G - %61 / 95 işlem - ADAY (7g/-2)
-E - TP5/20G - %78 / 41 işlem - ADAY (5g/-4)
-I - TP5/10G - %60 / 101 işlem - ADAY (5g/-4)
-I - TP5/20G - %83 / 60 işlem - ADAY (5g/-4)
-Q - TP5/20G - %69 / 81 işlem - ADAY (5g/-4)</t>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-9)
+E - TP5/10G - %61 / 95 işlem - ADAY (8g/-1)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/-3)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/-3)
+I - TP5/20G - %83 / 60 işlem - ADAY (6g/-3)
+Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-3)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -845,7 +850,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -856,20 +861,20 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>1</v>
@@ -887,8 +892,8 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (3g/-7)
-P - TP5/10G - %84 / 43 işlem - ADAY (3g/-7)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-6)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/-6)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -898,58 +903,56 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P-TP2/10G, P-TP5/20G, P-TP5/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>P - TP2/10G - %96 / 53 işlem - ONAY (9g/-2)
-P - TP5/20G - %90 / 41 işlem - ONAY (9g/-2)
-P - TP5/10G - %84 / 43 işlem - ADAY (9g/-2)
-R - TP5/10G - %61 / 99 işlem - ADAY (3g/+1)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/+1)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
+R - TP5/10G - %61 / 99 işlem - ADAY (9g/-6)
+R - TP5/20G - %81 / 94 işlem - ADAY (9g/-6)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -961,74 +964,72 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CANTE</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+          <t>P-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (0g/0)
-I - TP5/20G - %83 / 60 işlem - ADAY (10g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (14g/+2)
-R - TP2/10G - %82 / 108 işlem - ADAY (5g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (10g/+1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/0)
+R - TP5/10G - %61 / 99 işlem - ADAY (4g/+2)
+R - TP5/20G - %81 / 94 işlem - ADAY (4g/+2)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1037,50 +1038,51 @@
         <v>56</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (18g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (8g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (7g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (7g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)
+I - TP5/20G - %83 / 60 işlem - ADAY (11g/+2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+3)
+R - TP2/10G - %82 / 108 işlem - ADAY (6g/-1)
+R - TP5/20G - %81 / 94 işlem - ADAY (11g/+2)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>-0.1</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>ELDEKİ</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1089,34 +1091,33 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G</t>
+          <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (9g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (9g/0)
-Q - TP2/10G - %81 / 93 işlem - ADAY (9g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (9g/0)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/0)
+E - TP5/10G - %61 / 95 işlem - ADAY (9g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (8g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (8g/+1)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1132,20 +1133,20 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1163,10 +1164,10 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (17g/+1)
-I - TP5/20G - %83 / 60 işlem - ADAY (10g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/0)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (18g/+1)
+I - TP5/20G - %83 / 60 işlem - ADAY (11g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (11g/0)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1176,54 +1177,55 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 122 işlem - ADAY (10g/-15)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1239,20 +1241,20 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1270,9 +1272,9 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (3g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-4)
-R - TP5/20G - %81 / 94 işlem - ADAY (15g/-4)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)
+R - TP5/20G - %81 / 94 işlem - ADAY (16g/-3)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1282,7 +1284,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1293,20 +1295,20 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
@@ -1324,9 +1326,9 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (8g/+1)
-I - TP5/20G - %83 / 60 işlem - ADAY (3g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-4)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/+2)
+I - TP5/20G - %83 / 60 işlem - ADAY (4g/+2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1336,25 +1338,25 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1363,84 +1365,80 @@
         <v>48</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (9g/+2)
-T - TP5/10G - %64 / 129 işlem - ADAY (5g/+1)
-T - TP5/20G - %77 / 122 işlem - ADAY (5g/+1)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/-3)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+        <v>-1.8</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/-1)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/-3)
-E - TP5/20G - %78 / 41 işlem - ADAY (9g/-3)</t>
+          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1452,72 +1450,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G</t>
+          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (1g/+1)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (9g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+3)
+Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+3)
+T - TP5/10G - %64 / 129 işlem - ADAY (6g/+2)
+T - TP5/20G - %77 / 122 işlem - ADAY (6g/+2)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1541,8 +1540,8 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/+1)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/+1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/0)
+R - TP5/20G - %81 / 94 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1559,18 +1558,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1582,26 +1581,25 @@
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (3g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (3g/+1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+1)
+R - TP5/20G - %81 / 94 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1613,18 +1611,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1648,9 +1646,9 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (3g/-1)
-E - TP5/20G - %78 / 41 işlem - ADAY (1g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (14g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (3g/+2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1667,70 +1665,71 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-7)</t>
+          <t>E - TP5/20G - %78 / 41 işlem - ADAY (10g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (10g/0)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1754,7 +1753,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (13g/-6)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-6)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1771,101 +1770,101 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/-1)
-R - TP5/20G - %81 / 94 işlem - ADAY (1g/-1)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-5)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (1g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/+1)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -1877,24 +1876,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>0</v>
@@ -1907,19 +1906,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (5g/+1)
-I - TP5/10G - %60 / 101 işlem - ADAY (5g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-3)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-1)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -1931,47 +1930,48 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>E-TP5/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/+1)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -1983,52 +1983,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
+        <v>1.8</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>L-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+1)</t>
+          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+2)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2039,20 +2039,20 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (3g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-1)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2080,161 +2080,159 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>ZOREN</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>K-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/10G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (19g/-16)
-Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-15)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>E-TP5/10G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %93 / 46 işlem - ONAY (0g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (0g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (16g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+3)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+3)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/+3)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2246,47 +2244,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>S-TP2/10G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/+2)</t>
+          <t>S - TP2/10G - %91 / 54 işlem - ONAY (1g/0)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2298,101 +2296,101 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (1g/+1)
-U - TP5/20G - %75 / 72 işlem - ADAY (0g/0)</t>
+          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (1g/0)
+U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
+        <v>-0.1</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (5g/-3)
-R - TP5/20G - %81 / 94 işlem - ADAY (5g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+2)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2408,20 +2406,20 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
@@ -2439,10 +2437,10 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/0)
-I - TP5/10G - %60 / 101 işlem - ADAY (5g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (3g/0)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (7g/0)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2452,170 +2450,432 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
+        <v>0.4</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (3g/-2)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/+2)
+U - TP5/20G - %75 / 72 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-5)
-R - TP5/20G - %81 / 94 işlem - ADAY (2g/-5)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (3g/+3)
-P - TP5/10G - %84 / 43 işlem - ADAY (3g/+3)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+1)
+R - TP5/20G - %81 / 94 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-3)
+R - TP5/20G - %81 / 94 işlem - ADAY (6g/-3)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ENERY</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/+3)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-3)
+R - TP5/20G - %81 / 94 işlem - ADAY (3g/-3)</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-14)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BRYAT</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,11 +534,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -551,30 +551,32 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>P-TP2/10G, P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (0g/0)</t>
+          <t>P - TP2/10G - %96 / 53 işlem - ONAY (0g/0)
+P - TP5/20G - %90 / 41 işlem - ONAY (0g/0)
+P - TP5/10G - %84 / 43 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 34 hisse / 24 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Bugün 3 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 21 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -590,7 +592,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -621,7 +623,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/+2)</t>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/+1)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -642,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -691,177 +693,176 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, E-TP5/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-10)
+E - TP5/10G - %61 / 95 işlem - ADAY (8g/-2)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/-4)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/-4)
+I - TP5/20G - %83 / 60 işlem - ADAY (6g/-4)
+Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-4)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>I - TP5/20G - %83 / 60 işlem - ADAY (19g/-2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (19g/-2)
+R - TP5/20G - %81 / 94 işlem - ADAY (19g/-2)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>KONTR</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>M-TP2/10G, M-TP5/20G, M-TP5/10G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>M - TP2/10G - %98 / 59 işlem - ONAY (0g/0)
 M - TP5/20G - %93 / 41 işlem - ONAY (4g/-4)
 M - TP5/10G - %71 / 49 işlem - ADAY (0g/0)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY M: TDA ve PFY-S birlikte dönüş teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 29 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (0g/0)
-I - TP5/20G - %83 / 60 işlem - ADAY (19g/-2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (19g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (19g/-2)</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>K-TP5/20G, E-TP5/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-9)
-E - TP5/10G - %61 / 95 işlem - ADAY (8g/-1)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/-3)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/-3)
-I - TP5/20G - %83 / 60 işlem - ADAY (6g/-3)
-Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-3)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -880,41 +881,42 @@
         <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-6)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/-6)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
+R - TP5/10G - %61 / 99 işlem - ADAY (9g/-5)
+R - TP5/20G - %81 / 94 işlem - ADAY (9g/-5)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -927,131 +929,23 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
-R - TP5/10G - %61 / 99 işlem - ADAY (9g/-6)
-R - TP5/20G - %81 / 94 işlem - ADAY (9g/-6)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>P-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/0)
-R - TP5/10G - %61 / 99 işlem - ADAY (4g/+2)
-R - TP5/20G - %81 / 94 işlem - ADAY (4g/+2)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CANTE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)
 I - TP5/20G - %83 / 60 işlem - ADAY (11g/+2)
@@ -1060,25 +954,134 @@
 R - TP5/20G - %81 / 94 işlem - ADAY (11g/+2)</t>
         </is>
       </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (18g/0)
+I - TP5/20G - %83 / 60 işlem - ADAY (11g/-1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (11g/-1)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %93 / 46 işlem - ONAY (0g/0)
+H - TP5/10G - %67 / 21 işlem - ADAY (0g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (0g/0)</t>
+        </is>
+      </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 32 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1091,49 +1094,48 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (8g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (8g/+1)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/-1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (10g/-1)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1146,49 +1148,49 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (18g/+1)
-I - TP5/20G - %83 / 60 işlem - ADAY (11g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (11g/0)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/-1)
+E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)
+E - TP5/20G - %78 / 41 işlem - ADAY (8g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (8g/0)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1207,30 +1209,32 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
+E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (3g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1245,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1272,9 +1276,9 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)
-R - TP5/20G - %81 / 94 işlem - ADAY (16g/-3)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-2)
+R - TP5/20G - %81 / 94 işlem - ADAY (16g/-2)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1291,11 +1295,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1308,192 +1312,192 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H16" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
+E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/+1)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/+1)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 43 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-1)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/-4)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-18)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ISMEN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="H19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/+2)
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/+1)
 I - TP5/20G - %83 / 60 işlem - ADAY (4g/+2)
 Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AGHOL</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/-3)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+3)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+3)
-T - TP5/10G - %64 / 129 işlem - ADAY (6g/+2)
-T - TP5/20G - %77 / 122 işlem - ADAY (6g/+2)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1505,11 +1509,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -1522,47 +1526,48 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/0)
-R - TP5/20G - %81 / 94 işlem - ADAY (2g/0)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
+E - TP5/10G - %61 / 95 işlem - ADAY (0g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1575,47 +1580,49 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+1)
-R - TP5/20G - %81 / 94 işlem - ADAY (4g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+2)
+T - TP5/10G - %64 / 129 işlem - ADAY (6g/+1)
+T - TP5/20G - %77 / 122 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1634,26 +1641,25 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (3g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/+1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-1)
+R - TP5/20G - %81 / 94 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1665,11 +1671,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1682,7 +1688,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
@@ -1695,23 +1701,23 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %78 / 41 işlem - ADAY (10g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/0)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+2)
+R - TP5/20G - %81 / 94 işlem - ADAY (4g/+2)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1728,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1753,7 +1759,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-6)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1774,7 +1780,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1805,7 +1811,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-5)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-6)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1822,11 +1828,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.4</v>
+        <v>-2.2</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1839,7 +1845,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
@@ -1852,35 +1858,35 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/+1)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-4)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/-1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-2)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -1893,48 +1899,47 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-3)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1947,47 +1952,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G</t>
+          <t>L-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/+1)</t>
+          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+1)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -2000,46 +2004,46 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>L-TP5/20G</t>
+          <t>E-TP5/10G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+2)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-1)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>ZOREN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2070,7 +2074,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2087,11 +2091,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2104,7 +2108,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>0</v>
@@ -2122,7 +2126,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2132,18 +2136,18 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2156,35 +2160,35 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+2)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2199,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2226,8 +2230,8 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+3)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/+3)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+1)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2244,11 +2248,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2267,24 +2271,26 @@
         <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>S-TP2/10G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>S - TP2/10G - %91 / 54 işlem - ONAY (1g/0)</t>
+          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/-1)
+H - TP5/20G - %82 / 39 işlem - ADAY (1g/-1)
+U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2296,11 +2302,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.3</v>
+        <v>2.9</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2313,37 +2319,36 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (1g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-4)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/-4)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2359,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -2406,7 +2411,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -2457,11 +2462,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2474,31 +2479,30 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/+2)
-U - TP5/20G - %75 / 72 işlem - ADAY (1g/0)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2510,11 +2514,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.5</v>
+        <v>2.1</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -2533,24 +2537,25 @@
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+2)
+R - TP5/20G - %81 / 94 işlem - ADAY (1g/+2)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2562,11 +2567,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -2597,8 +2602,8 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+1)
-R - TP5/20G - %81 / 94 işlem - ADAY (1g/+1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-4)
+R - TP5/20G - %81 / 94 işlem - ADAY (6g/-4)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2615,11 +2620,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -2632,7 +2637,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>0</v>
@@ -2645,34 +2650,34 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-3)
-R - TP5/20G - %81 / 94 işlem - ADAY (6g/-3)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/0)
+U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -2685,30 +2690,31 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/+3)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-4)
+R - TP5/20G - %81 / 94 işlem - ADAY (3g/-4)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -2720,11 +2726,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
@@ -2737,31 +2743,30 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-3)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/-3)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-13)</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
@@ -2773,11 +2778,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
@@ -2808,7 +2813,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-14)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -2822,60 +2827,8 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L45"/>
+  <autoFilter ref="A1:L44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/+1)</t>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/0)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -728,12 +728,12 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-10)
-E - TP5/10G - %61 / 95 işlem - ADAY (8g/-2)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/-4)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/-4)
-I - TP5/20G - %83 / 60 işlem - ADAY (6g/-4)
-Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-4)</t>
+          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-11)
+E - TP5/10G - %61 / 95 işlem - ADAY (8g/-3)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/-5)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/-5)
+I - TP5/20G - %83 / 60 işlem - ADAY (6g/-5)
+Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-5)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -858,11 +858,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>CANTE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -875,77 +875,23 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
-R - TP5/10G - %61 / 99 işlem - ADAY (9g/-5)
-R - TP5/20G - %81 / 94 işlem - ADAY (9g/-5)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CANTE</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)
 I - TP5/20G - %83 / 60 işlem - ADAY (11g/+2)
@@ -954,25 +900,80 @@
 R - TP5/20G - %81 / 94 işlem - ADAY (11g/+2)</t>
         </is>
       </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/-1)
+H - TP5/20G - %82 / 39 işlem - ADAY (18g/-1)
+I - TP5/20G - %83 / 60 işlem - ADAY (11g/-2)
+Q - TP5/20G - %69 / 81 işlem - ADAY (11g/-2)</t>
+        </is>
+      </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -985,62 +986,61 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (18g/0)
-I - TP5/20G - %83 / 60 işlem - ADAY (11g/-1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (11g/-1)</t>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/-1)
+R - TP5/10G - %61 / 99 işlem - ADAY (9g/-7)
+R - TP5/20G - %81 / 94 işlem - ADAY (9g/-7)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>1</v>
@@ -1053,118 +1053,64 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %93 / 46 işlem - ONAY (0g/0)
-H - TP5/10G - %67 / 21 işlem - ADAY (0g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (0g/0)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 32 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
 E - TP5/20G - %78 / 41 işlem - ADAY (10g/-1)
 Q - TP5/20G - %69 / 81 işlem - ADAY (10g/-1)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PGSUS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>-1.6</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/-1)
 E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)
@@ -1172,25 +1118,80 @@
 Q - TP5/20G - %69 / 81 işlem - ADAY (8g/0)</t>
         </is>
       </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
+E - TP5/10G - %61 / 95 işlem - ADAY (4g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (3g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
+        </is>
+      </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1209,32 +1210,30 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (3g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/+1)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1244,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1276,9 +1275,9 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (16g/-2)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)
+R - TP5/20G - %81 / 94 işlem - ADAY (16g/-3)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1299,7 +1298,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1354,7 +1353,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.4</v>
+        <v>-1.7</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -1385,8 +1384,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-1)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/-4)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-2)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/-5)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1407,7 +1406,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-3.5</v>
+        <v>-1.8</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -1438,7 +1437,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-18)</t>
+          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1459,7 +1458,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1490,9 +1489,9 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/+1)
-I - TP5/20G - %83 / 60 işlem - ADAY (4g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/0)
+I - TP5/20G - %83 / 60 işlem - ADAY (4g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-5)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1509,11 +1508,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -1526,77 +1525,23 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G</t>
+          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
-E - TP5/10G - %61 / 95 işlem - ADAY (0g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+2)
 Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+2)
@@ -1604,25 +1549,78 @@
 T - TP5/20G - %77 / 122 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-1)
+R - TP5/20G - %81 / 94 işlem - ADAY (2g/-1)</t>
+        </is>
+      </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.2</v>
+        <v>2.6</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1653,8 +1651,8 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-1)
-R - TP5/20G - %81 / 94 işlem - ADAY (2g/-1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+3)
+R - TP5/20G - %81 / 94 işlem - ADAY (4g/+3)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1671,11 +1669,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1688,31 +1686,30 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+2)
-R - TP5/20G - %81 / 94 işlem - ADAY (4g/+2)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1724,11 +1721,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.4</v>
+        <v>-1.3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1741,35 +1738,37 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-3)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-1)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1779,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1793,7 +1792,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
@@ -1821,18 +1820,18 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-2.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1845,48 +1844,47 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-4)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/-1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-2)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -1899,47 +1897,46 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G</t>
+          <t>L-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)</t>
+          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/0)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>ZOREN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1952,46 +1949,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>L-TP5/20G</t>
+          <t>E-TP5/10G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -2004,7 +2001,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
@@ -2022,7 +2019,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2032,18 +2029,18 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2056,7 +2053,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
@@ -2074,7 +2071,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-2)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2084,18 +2081,18 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.4</v>
+        <v>3.6</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2108,46 +2105,46 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+2)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4.3</v>
+        <v>-1.4</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2160,30 +2157,31 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+2)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+1)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2195,11 +2193,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2212,101 +2210,101 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+1)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/+1)</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TAVHL</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/-1)
 H - TP5/20G - %82 / 39 işlem - ADAY (1g/-1)
 U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-3)
+P - TP5/10G - %84 / 43 işlem - ADAY (4g/-3)</t>
+        </is>
+      </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2.9</v>
+        <v>-0.1</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2319,47 +2317,46 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-4)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/-4)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+2)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -2372,30 +2369,31 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+2)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/+1)
+U - TP5/20G - %75 / 72 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2407,11 +2405,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -2424,33 +2422,30 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (7g/0)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-4)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2462,11 +2457,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2485,24 +2480,25 @@
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+1)
+R - TP5/20G - %81 / 94 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2514,11 +2510,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -2549,8 +2545,8 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+2)
-R - TP5/20G - %81 / 94 işlem - ADAY (1g/+2)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-4)
+R - TP5/20G - %81 / 94 işlem - ADAY (6g/-4)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2567,11 +2563,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -2584,47 +2580,49 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-4)
-R - TP5/20G - %81 / 94 işlem - ADAY (6g/-4)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/-1)
+E - TP5/20G - %78 / 41 işlem - ADAY (7g/-1)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/-1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/-1)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-1.4</v>
+        <v>0.6</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -2637,7 +2635,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>0</v>
@@ -2650,18 +2648,18 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-4)
+R - TP5/20G - %81 / 94 işlem - ADAY (3g/-4)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
@@ -2673,11 +2671,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -2690,31 +2688,30 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-4)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/-4)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-14)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
@@ -2726,11 +2723,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
@@ -2761,7 +2758,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-13)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -2775,60 +2772,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -693,261 +693,365 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>KONTR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>M-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (4g/-4)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 24 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+1)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CCOLA</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B7" s="2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>K-TP5/20G, E-TP5/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-11)
-E - TP5/10G - %61 / 95 işlem - ADAY (8g/-3)
+E - TP5/10G - %61 / 95 işlem - ADAY (8g/-4)
 E - TP5/20G - %78 / 41 işlem - ADAY (6g/-5)
 I - TP5/10G - %60 / 101 işlem - ADAY (6g/-5)
 I - TP5/20G - %83 / 60 işlem - ADAY (6g/-5)
 Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-5)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>I - TP5/20G - %83 / 60 işlem - ADAY (19g/-2)
 Q - TP5/20G - %69 / 81 işlem - ADAY (19g/-2)
 R - TP5/20G - %81 / 94 işlem - ADAY (19g/-2)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KONTR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>M-TP2/10G, M-TP5/20G, M-TP5/10G</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>M - TP2/10G - %98 / 59 işlem - ONAY (0g/0)
-M - TP5/20G - %93 / 41 işlem - ONAY (4g/-4)
-M - TP5/10G - %71 / 49 işlem - ADAY (0g/0)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY M: TDA ve PFY-S birlikte dönüş teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 29 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CANTE</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)
-I - TP5/20G - %83 / 60 işlem - ADAY (11g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+3)
-R - TP2/10G - %82 / 108 işlem - ADAY (6g/-1)
-R - TP5/20G - %81 / 94 işlem - ADAY (11g/+2)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>CANTE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)
+I - TP5/20G - %83 / 60 işlem - ADAY (11g/+1)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+2)
+R - TP2/10G - %82 / 108 işlem - ADAY (6g/-2)
+R - TP5/20G - %81 / 94 işlem - ADAY (11g/+1)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
+R - TP5/10G - %61 / 99 işlem - ADAY (9g/-6)
+R - TP5/20G - %81 / 94 işlem - ADAY (9g/-6)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>FROTO</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B11" s="2" t="n">
         <v>-1.4</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/-1)
 H - TP5/20G - %82 / 39 işlem - ADAY (18g/-1)
@@ -955,122 +1059,14 @@
 Q - TP5/20G - %69 / 81 işlem - ADAY (11g/-2)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/-1)
-R - TP5/10G - %61 / 99 işlem - ADAY (9g/-7)
-R - TP5/20G - %81 / 94 işlem - ADAY (9g/-7)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/-1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/-1)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1077,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1113,7 +1109,7 @@
       <c r="J12" s="5" t="inlineStr">
         <is>
           <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/-1)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)
+E - TP5/10G - %61 / 95 işlem - ADAY (9g/0)
 E - TP5/20G - %78 / 41 işlem - ADAY (8g/0)
 Q - TP5/20G - %69 / 81 işlem - ADAY (8g/0)</t>
         </is>
@@ -1136,7 +1132,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1191,7 +1187,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1244,7 +1240,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1294,11 +1290,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1311,49 +1307,47 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/+1)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/+1)</t>
+          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-3)
+E - TP5/20G - %78 / 41 işlem - ADAY (10g/-5)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -1369,44 +1363,43 @@
         <v>48</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-2)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/-5)</t>
+          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -1425,40 +1418,42 @@
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)
+I - TP5/20G - %83 / 60 işlem - ADAY (4g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-5)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1477,71 +1472,17 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/0)
-I - TP5/20G - %83 / 60 işlem - ADAY (4g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-5)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+2)
 Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+2)
@@ -1549,9 +1490,62 @@
 T - TP5/20G - %77 / 122 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-2)
+R - TP5/20G - %81 / 94 işlem - ADAY (2g/-2)</t>
+        </is>
+      </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1563,11 +1557,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.7</v>
+        <v>1.7</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1598,8 +1592,8 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-1)
-R - TP5/20G - %81 / 94 işlem - ADAY (2g/-1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+3)
+R - TP5/20G - %81 / 94 işlem - ADAY (4g/+3)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1616,11 +1610,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1639,25 +1633,26 @@
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+3)
-R - TP5/20G - %81 / 94 işlem - ADAY (4g/+3)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (2g/+3)
+Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+2)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1669,11 +1664,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1686,46 +1681,47 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
+          <t>E - TP5/20G - %78 / 41 işlem - ADAY (10g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (10g/0)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1738,48 +1734,46 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-3)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-1)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1792,46 +1786,48 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-6)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+2)
+E - TP5/20G - %78 / 41 işlem - ADAY (6g/+2)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/+2)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1850,93 +1846,93 @@
         <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-6)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>E-TP5/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/0)
 E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TRMET</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>L-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/0)</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>TRMET</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1949,46 +1945,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>L-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/0)</t>
+          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+2)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>MIATK</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -2001,7 +1997,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
@@ -2019,7 +2015,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/+1)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-2)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2029,18 +2025,18 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>ZOREN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2053,7 +2049,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-2)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2081,18 +2077,18 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2105,35 +2101,35 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>E-TP5/10G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+2)</t>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2140,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2197,7 +2193,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2228,8 +2224,8 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/-1)
-H - TP5/20G - %82 / 39 işlem - ADAY (1g/-1)
+          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/0)
+H - TP5/20G - %82 / 39 işlem - ADAY (1g/0)
 U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
@@ -2251,7 +2247,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2304,7 +2300,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2335,7 +2331,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2352,100 +2348,103 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/0)
+E - TP5/20G - %78 / 41 işlem - ADAY (7g/0)
+I - TP5/10G - %60 / 101 işlem - ADAY (6g/0)
+Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>OYAKC</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
+      <c r="B37" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/+1)
 U - TP5/20G - %75 / 72 işlem - ADAY (1g/0)</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TOASO</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>U-TP2/10G</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-4)</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2457,11 +2456,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2480,75 +2479,74 @@
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>U-TP2/10G</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+1)
 R - TP5/20G - %81 / 94 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-4)
-R - TP5/20G - %81 / 94 işlem - ADAY (6g/-4)</t>
-        </is>
-      </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
@@ -2563,11 +2561,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -2580,38 +2578,36 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/-1)
-E - TP5/20G - %78 / 41 işlem - ADAY (7g/-1)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/-1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/-1)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-5)
+R - TP5/20G - %81 / 94 işlem - ADAY (6g/-5)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2618,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
@@ -2653,8 +2649,8 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-4)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/-4)</t>
+          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-5)
+R - TP5/20G - %81 / 94 işlem - ADAY (3g/-5)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2675,7 +2671,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -2706,7 +2702,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-14)</t>
+          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-13)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -2727,7 +2723,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,11 +534,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -551,48 +551,47 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P-TP2/10G, P-TP5/20G, P-TP5/10G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>P - TP2/10G - %96 / 53 işlem - ONAY (0g/0)
-P - TP5/20G - %90 / 41 işlem - ONAY (0g/0)
-P - TP5/10G - %84 / 43 işlem - ADAY (0g/0)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0)
+L - TP5/10G - %79 / 42 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Bugün 3 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 21 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -605,30 +604,31 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (2g/0)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-4)
+M - TP5/20G - %89 / 47 işlem - ONAY (5g/-4)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -640,11 +640,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -657,31 +657,30 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (3g/0)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (3g/+2)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 29 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -693,11 +692,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -710,46 +709,50 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (4g/-4)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (18g/-11)
+E - TP5/20G - %79 / 42 işlem - ADAY (7g/-5)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/-5)
+I - TP5/20G - %84 / 49 işlem - ADAY (7g/-5)
+Q - TP5/20G - %67 / 83 işlem - ADAY (7g/-5)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 34 hisse / 24 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -768,24 +771,25 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (10g/+1)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/0)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/0)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -797,11 +801,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -820,45 +824,40 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>K-TP5/20G, E-TP5/10G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %96 / 45 işlem - ONAY (17g/-11)
-E - TP5/10G - %61 / 95 işlem - ADAY (8g/-4)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/-5)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/-5)
-I - TP5/20G - %83 / 60 işlem - ADAY (6g/-5)
-Q - TP5/20G - %69 / 81 işlem - ADAY (6g/-5)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/0)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -874,45 +873,45 @@
         <v>59</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>I-TP5/20G, Q-TP5/20G, R-TP5/20G</t>
+          <t>P-TP2/10G, P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>I - TP5/20G - %83 / 60 işlem - ADAY (19g/-2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (19g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (19g/-2)</t>
+          <t>P - TP2/10G - %96 / 55 işlem - ONAY (1g/0)
+P - TP5/20G - %90 / 41 işlem - ONAY (1g/0)
+P - TP5/10G - %82 / 45 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CANTE</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -925,50 +924,48 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)
-I - TP5/20G - %83 / 60 işlem - ADAY (11g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+2)
-R - TP2/10G - %82 / 108 işlem - ADAY (6g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (11g/+1)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/+2)
+R - TP5/10G - %60 / 103 işlem - ADAY (0g/0)
+R - TP5/20G - %80 / 95 işlem - ADAY (10g/-5)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -981,48 +978,47 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (1g/+1)
-R - TP5/10G - %61 / 99 işlem - ADAY (9g/-6)
-R - TP5/20G - %81 / 94 işlem - ADAY (9g/-6)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (11g/+2)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-1.4</v>
+        <v>0.9</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1035,33 +1031,31 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>E-TP5/10G, H-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/-1)
-H - TP5/20G - %82 / 39 işlem - ADAY (18g/-1)
-I - TP5/20G - %83 / 60 işlem - ADAY (11g/-2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (11g/-2)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2)
+E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1073,11 +1067,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.2</v>
+        <v>0.1</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1090,38 +1084,36 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>M-TP5/20G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %93 / 41 işlem - ONAY (19g/-1)
-E - TP5/10G - %61 / 95 işlem - ADAY (9g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (8g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (8g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (17g/-3)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1124,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1145,49 +1137,48 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (0g/0)
-E - TP5/10G - %61 / 95 işlem - ADAY (4g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (3g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
+E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+1)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1200,31 +1191,31 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (2g/+1)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/+2)</t>
+          <t>H - TP5/20G - %83 / 40 işlem - ADAY (19g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1236,11 +1227,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VESTL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1253,32 +1244,31 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>E-TP5/10G, Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/+1)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-3)
-R - TP5/20G - %81 / 94 işlem - ADAY (16g/-3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1290,11 +1280,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-2.1</v>
+        <v>0.3</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1307,47 +1297,46 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %86 / 50 işlem - ONAY (3g/-3)
-E - TP5/20G - %78 / 41 işlem - ADAY (10g/-5)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/0)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 25 hisse / 34 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -1360,46 +1349,47 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 122 işlem - ADAY (11g/-16)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/0)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 67 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.4</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -1412,32 +1402,31 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (9g/-1)
-I - TP5/20G - %83 / 60 işlem - ADAY (4g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (16g/-5)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+2)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1449,11 +1438,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.6</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1466,33 +1455,31 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E-TP5/10G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (5g/+2)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/+2)
-T - TP5/10G - %64 / 129 işlem - ADAY (6g/+1)
-T - TP5/20G - %77 / 122 işlem - ADAY (6g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+4)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/+4)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
@@ -1504,11 +1491,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.1</v>
+        <v>0.6</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -1521,47 +1508,48 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (2g/-2)
-R - TP5/20G - %81 / 94 işlem - ADAY (2g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (11g/+2)
+T - TP5/10G - %64 / 133 işlem - ADAY (7g/+1)
+T - TP5/20G - %77 / 124 işlem - ADAY (7g/+1)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.7</v>
+        <v>-0.8</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1562,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
@@ -1587,34 +1575,34 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (4g/+3)
-R - TP5/20G - %81 / 94 işlem - ADAY (4g/+3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/+1)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/+1)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1627,48 +1615,47 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/+3)
-Q - TP5/20G - %69 / 81 işlem - ADAY (15g/+2)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.4</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1681,36 +1668,35 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %78 / 41 işlem - ADAY (10g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (10g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1707,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.3</v>
+        <v>2.3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1734,7 +1720,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
@@ -1752,28 +1738,28 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-7)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-5)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1786,48 +1772,47 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+2)
-E - TP5/20G - %78 / 41 işlem - ADAY (6g/+2)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/+2)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-1)
+P - TP5/10G - %82 / 45 işlem - ADAY (5g/-1)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1840,46 +1825,48 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (14g/-6)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0)
+H - TP5/20G - %83 / 40 işlem - ADAY (2g/0)
+U - TP5/20G - %75 / 72 işlem - ADAY (18g/0)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.7</v>
+        <v>1.8</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -1892,47 +1879,47 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (2g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (2g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/+2)
+P - TP5/10G - %82 / 45 işlem - ADAY (5g/+2)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRMET</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1945,30 +1932,31 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>L-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %95 / 55 işlem - ONAY (1g/+2)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-13)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-13)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 43 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -1980,11 +1968,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MIATK</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.3</v>
+        <v>-3.2</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -1997,7 +1985,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
@@ -2010,33 +1998,33 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (4g/-2)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (12g/-19)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2049,46 +2037,48 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (6g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/0)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (5g/0)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2101,46 +2091,48 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>E-TP5/10G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (1g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0)
+R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2153,31 +2145,31 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/+1)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/+1)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
+U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2189,11 +2181,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2206,32 +2198,30 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %93 / 46 işlem - ONAY (1g/0)
-H - TP5/20G - %82 / 39 işlem - ADAY (1g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (17g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2243,11 +2233,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2260,47 +2250,46 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (4g/-3)
-P - TP5/10G - %84 / 43 işlem - ADAY (4g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2313,7 +2302,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
@@ -2326,29 +2315,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/+1)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -2365,49 +2354,47 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>E-TP5/10G, E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/10G - %61 / 95 işlem - ADAY (7g/0)
-E - TP5/20G - %78 / 41 işlem - ADAY (7g/0)
-I - TP5/10G - %60 / 101 işlem - ADAY (6g/0)
-Q - TP5/20G - %69 / 81 işlem - ADAY (4g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (2g/+1)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/+1)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -2420,7 +2407,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
@@ -2433,34 +2420,34 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (2g/+1)
-U - TP5/20G - %75 / 72 işlem - ADAY (1g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2473,7 +2460,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
@@ -2486,17 +2473,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 90 işlem - ADAY (4g/-3)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2508,11 +2495,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -2525,251 +2512,41 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (1g/+1)
-R - TP5/20G - %81 / 94 işlem - ADAY (1g/+1)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-1)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (6g/-5)
-R - TP5/20G - %81 / 94 işlem - ADAY (6g/-5)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %61 / 99 işlem - ADAY (3g/-5)
-R - TP5/20G - %81 / 94 işlem - ADAY (3g/-5)</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (15g/-13)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %69 / 81 işlem - ADAY (1g/0)</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>1</v>
@@ -580,7 +580,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -622,8 +622,8 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-4)
-M - TP5/20G - %89 / 47 işlem - ONAY (5g/-4)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-5)
+M - TP5/20G - %89 / 47 işlem - ONAY (5g/-5)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -748,11 +748,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -765,47 +765,46 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/0)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/-1)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -818,46 +817,48 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+1)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -870,48 +871,47 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P-TP2/10G, P-TP5/20G, P-TP5/10G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P - TP2/10G - %96 / 55 işlem - ONAY (1g/0)
-P - TP5/20G - %90 / 41 işlem - ONAY (1g/0)
-P - TP5/10G - %82 / 45 işlem - ADAY (1g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2)
+E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -924,48 +924,47 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/+2)
-R - TP5/10G - %60 / 103 işlem - ADAY (0g/0)
-R - TP5/20G - %80 / 95 işlem - ADAY (10g/-5)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-2)
+R - TP5/20G - %80 / 95 işlem - ADAY (17g/-2)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -978,100 +977,99 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (11g/+2)</t>
+          <t>H - TP5/20G - %83 / 40 işlem - ADAY (19g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2)
-E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VESTL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1084,7 +1082,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
@@ -1097,18 +1095,18 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (17g/-3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/0)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1120,11 +1118,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1137,48 +1135,46 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
-E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/+1)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1191,7 +1187,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1204,34 +1200,34 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>H-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>H - TP5/20G - %83 / 40 işlem - ADAY (19g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/0)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1244,7 +1240,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1262,8 +1258,8 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+2)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1273,18 +1269,18 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1297,30 +1293,31 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+3)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/+3)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1332,11 +1329,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.7</v>
+        <v>1.9</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -1355,25 +1352,26 @@
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (11g/+3)
+T - TP5/10G - %64 / 133 işlem - ADAY (7g/+3)
+T - TP5/20G - %77 / 124 işlem - ADAY (7g/+3)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1385,11 +1383,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -1402,7 +1400,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1415,18 +1413,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/+1)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/+1)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1438,11 +1436,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1455,47 +1453,46 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+4)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/+4)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+1)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -1508,32 +1505,31 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (11g/+2)
-T - TP5/10G - %64 / 133 işlem - ADAY (7g/+1)
-T - TP5/20G - %77 / 124 işlem - ADAY (7g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1545,11 +1541,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.8</v>
+        <v>1.8</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1562,47 +1558,46 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/+1)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1615,31 +1610,30 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-7)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1651,11 +1645,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1668,46 +1662,47 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/+1)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/+1)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1720,46 +1715,47 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-5)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (1g/+3)
+P - TP5/10G - %82 / 45 işlem - ADAY (1g/+3)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1778,25 +1774,26 @@
         <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-1)
-P - TP5/10G - %82 / 45 işlem - ADAY (5g/-1)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0)
+H - TP5/20G - %83 / 40 işlem - ADAY (2g/0)
+U - TP5/20G - %75 / 72 işlem - ADAY (18g/-1)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -1808,11 +1805,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1825,37 +1822,36 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0)
-H - TP5/20G - %83 / 40 işlem - ADAY (2g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (18g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-3)
+P - TP5/10G - %82 / 45 işlem - ADAY (5g/-3)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1862,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -1919,7 +1915,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1968,11 +1964,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-3.2</v>
+        <v>3.6</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
@@ -1998,17 +1994,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (12g/-19)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (10g/-3)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2020,11 +2016,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-0.3</v>
+        <v>-4.3</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2037,32 +2033,30 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/0)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (5g/0)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (12g/-20)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2078,7 +2072,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2104,19 +2098,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0)
-R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4)</t>
+          <t>R - TP2/10G - %83 / 113 işlem - ADAY (0g/0)
+R - TP5/10G - %60 / 103 işlem - ADAY (7g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-3)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2128,11 +2122,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2151,25 +2145,24 @@
         <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
-U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2181,11 +2174,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2216,7 +2209,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+2)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2233,11 +2226,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2250,46 +2243,48 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2302,30 +2297,31 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
+U - TP5/20G - %75 / 72 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2337,98 +2333,97 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>U-TP2/10G</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ALARK</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
+      <c r="B37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (2g/+1)
 R - TP5/20G - %80 / 95 işlem - ADAY (2g/+1)</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
-        </is>
-      </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
@@ -2443,11 +2438,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2466,87 +2461,140 @@
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-4)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>BRYAT</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/0)</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>ODAS</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="B40" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-1)</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/0)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L39"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -587,48 +587,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
+        <v>0.8</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>BUGÜN</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>AL</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-5)
-M - TP5/20G - %89 / 47 işlem - ONAY (5g/-5)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (0g/0)
+R - TP5/10G - %60 / 103 işlem - ADAY (0g/0)
+R - TP5/20G - %80 / 95 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -640,11 +641,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -657,75 +658,128 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (3g/+2)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-6)
+M - TP5/20G - %89 / 47 işlem - ONAY (5g/-6)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (3g/+1)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>CCOLA</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>K - TP5/20G - %93 / 68 işlem - ONAY (18g/-11)
 E - TP5/20G - %79 / 42 işlem - ADAY (7g/-5)
@@ -734,906 +788,855 @@
 Q - TP5/20G - %67 / 83 işlem - ADAY (7g/-5)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/-1)</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/0)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/0)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/+1)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SISE</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B9" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="n">
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
 E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
 Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+1)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>AGHOL</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B10" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2)
 E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>VESTL</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-2)
-R - TP5/20G - %80 / 95 işlem - ADAY (17g/-2)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (17g/-3)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>FROTO</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B12" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>H - TP5/20G - %83 / 40 işlem - ADAY (19g/-1)
 Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>TUKAS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>İZLEME</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>İZLE</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>U-TP5/20G</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>U - TP5/20G - %75 / 72 işlem - ADAY (0g/0)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>THYAO</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="B14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/0)
 Q - TP5/20G - %67 / 83 işlem - ADAY (11g/0)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MGROS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>-0.9</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/+1)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>PGSUS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0)
 Q - TP5/20G - %67 / 83 işlem - ADAY (9g/0)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>TURSG</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="B17" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+2)</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+1)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>SASA</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="B18" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+3)
 R - TP5/20G - %80 / 95 işlem - ADAY (5g/+3)</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="B19" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="n">
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Q - TP5/20G - %67 / 83 işlem - ADAY (11g/+3)
-T - TP5/10G - %64 / 133 işlem - ADAY (7g/+3)
-T - TP5/20G - %77 / 124 işlem - ADAY (7g/+3)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
+T - TP5/10G - %64 / 133 işlem - ADAY (7g/+2)
+T - TP5/20G - %77 / 124 işlem - ADAY (7g/+2)</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>ARCLK</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
+      <c r="B20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/+1)
 I - TP5/10G - %61 / 103 işlem - ADAY (7g/+1)</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>TCELL</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
+      <c r="B21" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+1)</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>MAVI</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
+      <c r="B22" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
 R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ISMEN</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EREGL</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-7)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -1645,11 +1648,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1662,47 +1665,46 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/+1)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1715,47 +1717,46 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (1g/+3)
-P - TP5/10G - %82 / 45 işlem - ADAY (1g/+3)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-6)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1774,148 +1775,148 @@
         <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (1g/+2)
+P - TP5/10G - %82 / 45 işlem - ADAY (1g/+2)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/0)
+P - TP5/10G - %82 / 45 işlem - ADAY (5g/0)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TAVHL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0)
 H - TP5/20G - %83 / 40 işlem - ADAY (2g/0)
 U - TP5/20G - %75 / 72 işlem - ADAY (18g/-1)</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-3)
-P - TP5/10G - %82 / 45 işlem - ADAY (5g/-3)</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/+2)
-P - TP5/10G - %82 / 45 işlem - ADAY (5g/+2)</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -1941,70 +1942,71 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-4)
+P - TP5/10G - %82 / 45 işlem - ADAY (5g/-4)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-13)
 Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-13)</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (10g/-3)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2020,7 +2022,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2068,11 +2070,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2085,7 +2087,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>0</v>
@@ -2098,35 +2100,35 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>R - TP2/10G - %83 / 113 işlem - ADAY (0g/0)
-R - TP5/10G - %60 / 103 işlem - ADAY (7g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/+3)
+I - TP5/10G - %61 / 103 işlem - ADAY (7g/+3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+3)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2145,40 +2147,42 @@
         <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0)
+R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2197,24 +2201,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+2)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
+U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2226,11 +2231,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.7</v>
+        <v>1.4</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2243,48 +2248,46 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2297,47 +2300,46 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
-U - TP5/20G - %75 / 72 işlem - ADAY (2g/0)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+1)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -2350,46 +2352,47 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (2g/+2)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/+2)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -2402,31 +2405,30 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (2g/+1)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/+1)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2442,7 +2444,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2473,8 +2475,8 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-4)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2495,7 +2497,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -2543,58 +2545,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (10g/+1)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ODAS</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="B41" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/0)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-1)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,7 +81,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,48 +528,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUGÜN</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0)
-L - TP5/10G - %79 / 42 işlem - ADAY (0g/0)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-6)
+M - TP5/20G - %89 / 47 işlem - ONAY (6g/-6)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -587,49 +581,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>BUGÜN</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (0g/0)
-R - TP5/10G - %60 / 103 işlem - ADAY (0g/0)
-R - TP5/20G - %80 / 95 işlem - ADAY (0g/0)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/+1)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -641,129 +633,133 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
+          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-6)
-M - TP5/20G - %89 / 47 işlem - ONAY (5g/-6)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-11)
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-5)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/-5)
+I - TP5/20G - %84 / 49 işlem - ADAY (8g/-5)
+Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-5)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+        <v>-1.8</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (3g/+1)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-2)
+H - TP5/20G - %83 / 40 işlem - ADAY (5g/-2)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
@@ -776,74 +772,75 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (18g/-11)
-E - TP5/20G - %79 / 42 işlem - ADAY (7g/-5)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/-5)
-I - TP5/20G - %84 / 49 işlem - ADAY (7g/-5)
-Q - TP5/20G - %67 / 83 işlem - ADAY (7g/-5)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/+2)
+T - TP5/10G - %64 / 133 işlem - ADAY (8g/+1)
+T - TP5/20G - %77 / 124 işlem - ADAY (8g/+1)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+        <v>-2.4</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/0)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/0)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-2)
+R - TP5/10G - %60 / 103 işlem - ADAY (1g/-2)
+R - TP5/20G - %80 / 95 işlem - ADAY (1g/-2)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -855,47 +852,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (11g/+1)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/0)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -907,18 +905,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -942,39 +940,39 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+1)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (10g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-1)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
+        <v>-0.7</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -996,66 +994,66 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2)
-E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VESTL</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+        <v>1.9</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (17g/-3)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1067,15 +1065,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1084,60 +1082,61 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>H-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>H - TP5/20G - %83 / 40 işlem - ADAY (19g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>-7.6</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>ELDEKİ</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1150,46 +1149,46 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (0g/0)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-26)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+        <v>-0.4</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1202,47 +1201,47 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (18g/-3)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1255,17 +1254,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/+1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1277,24 +1276,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
@@ -1312,8 +1311,8 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/+1)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1323,31 +1322,31 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
@@ -1360,71 +1359,70 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/0)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/0)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+3)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/+3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/+1)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1436,78 +1434,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (11g/+3)
-T - TP5/10G - %64 / 133 işlem - ADAY (7g/+2)
-T - TP5/20G - %77 / 124 işlem - ADAY (7g/+2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
@@ -1520,18 +1516,18 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/+1)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
@@ -1543,52 +1539,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+3)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/+3)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1599,14 +1596,14 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1630,8 +1627,8 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1648,18 +1645,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+        <v>1.8</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1683,7 +1680,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1700,24 +1697,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
@@ -1735,7 +1732,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-6)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1745,108 +1742,106 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (1g/+2)
-P - TP5/10G - %82 / 45 işlem - ADAY (1g/+2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/0)
-P - TP5/10G - %82 / 45 işlem - ADAY (5g/0)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/+2)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -1858,72 +1853,71 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+        <v>-0.1</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0)
-H - TP5/20G - %83 / 40 işlem - ADAY (2g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (18g/-1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-4)
+P - TP5/10G - %82 / 45 işlem - ADAY (6g/-4)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1947,8 +1941,8 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (5g/-4)
-P - TP5/10G - %82 / 45 işlem - ADAY (5g/-4)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (2g/+3)
+P - TP5/10G - %82 / 45 işlem - ADAY (2g/+3)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1965,18 +1959,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+        <v>-1.1</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1995,124 +1989,125 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-13)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-13)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-1)
+P - TP5/10G - %82 / 45 işlem - ADAY (6g/-1)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
+        <v>-1.2</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (12g/-20)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-2)
+H - TP5/20G - %83 / 40 işlem - ADAY (3g/-2)
+U - TP5/20G - %75 / 72 işlem - ADAY (19g/-2)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, Q-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/+3)
-I - TP5/10G - %61 / 103 işlem - ADAY (7g/+3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (5g/+3)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-14)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-14)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2124,102 +2119,100 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
+        <v>1.6</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0)
-R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+1)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (3g/+1)
-U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/+1)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2231,18 +2224,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -2254,24 +2247,25 @@
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/0)
+U - TP5/20G - %75 / 72 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2283,18 +2277,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -2318,7 +2312,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/+1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/+1)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2335,48 +2329,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+        <v>-1.4</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (2g/+2)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/+2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2388,24 +2381,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
@@ -2418,99 +2411,100 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-1)
+R - TP5/10G - %60 / 103 işlem - ADAY (8g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-4)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -2523,17 +2517,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/0)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-3)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2545,110 +2539,163 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (10g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/+1)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/+1)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (16g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-5)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BRYAT</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/0)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2</v>
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-6)
-M - TP5/20G - %89 / 47 işlem - ONAY (6g/-6)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-7)
+M - TP5/20G - %89 / 47 işlem - ONAY (6g/-7)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -574,18 +574,18 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -598,75 +598,23 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/+1)</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-11)
 E - TP5/20G - %79 / 42 işlem - ADAY (8g/-5)
@@ -675,14 +623,66 @@
 Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-5)</t>
         </is>
       </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/-3)</t>
+        </is>
+      </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-2)
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-3)
 H - TP5/20G - %83 / 40 işlem - ADAY (5g/-2)</t>
         </is>
       </c>
@@ -742,11 +742,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.8</v>
+        <v>-3</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -759,39 +759,36 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/+2)
-T - TP5/10G - %64 / 133 işlem - ADAY (8g/+1)
-T - TP5/20G - %77 / 124 işlem - ADAY (8g/+1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-7)
+P - TP5/10G - %82 / 45 işlem - ADAY (6g/-7)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -802,7 +799,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -833,9 +830,9 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-2)
-R - TP5/10G - %60 / 103 işlem - ADAY (1g/-2)
-R - TP5/20G - %80 / 95 işlem - ADAY (1g/-2)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-4)
+R - TP5/10G - %60 / 103 işlem - ADAY (1g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (1g/-4)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -856,7 +853,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -887,8 +884,8 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/0)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/0)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-1)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-1)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -905,74 +902,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.7</v>
+        <v>-2.1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (10g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-1)</t>
+E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>TP5/20G ONAY yok</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.7</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -994,29 +990,29 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1029,47 +1025,48 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (6g/0)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1082,48 +1079,46 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (6g/+1)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-28)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-7.6</v>
+        <v>0</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1136,46 +1131,47 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-26)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (18g/-3)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VESTL</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.4</v>
+        <v>-1.5</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1188,47 +1184,46 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (18g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1247,24 +1242,25 @@
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-1)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1276,11 +1272,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.3</v>
+        <v>-1.8</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1299,25 +1295,26 @@
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (12g/+1)
+T - TP5/10G - %64 / 133 işlem - ADAY (8g/0)
+T - TP5/20G - %77 / 124 işlem - ADAY (8g/0)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1333,7 +1330,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-1.6</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1364,8 +1361,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/0)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/-1)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1386,7 +1383,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.3</v>
+        <v>-2</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1417,7 +1414,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/+1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1434,11 +1431,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1451,46 +1448,47 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1521,8 +1519,8 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/0)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1539,11 +1537,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1574,82 +1572,82 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-2)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-2)</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+3)
 R - TP5/20G - %80 / 95 işlem - ADAY (6g/+3)</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.8</v>
+        <v>-1.3</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1662,7 +1660,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
@@ -1675,33 +1673,33 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1732,7 +1730,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-6)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1749,11 +1747,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1784,7 +1782,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1801,11 +1799,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1818,46 +1816,46 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/+2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.1</v>
+        <v>-3.3</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1870,36 +1868,35 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-4)
-P - TP5/10G - %82 / 45 işlem - ADAY (6g/-4)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-2)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1907,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1923,7 +1920,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>1</v>
@@ -1952,7 +1949,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1960,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2016,7 +2013,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.2</v>
+        <v>-3.4</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2047,9 +2044,9 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-2)
-H - TP5/20G - %83 / 40 işlem - ADAY (3g/-2)
-U - TP5/20G - %75 / 72 işlem - ADAY (19g/-2)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-4)
+H - TP5/20G - %83 / 40 işlem - ADAY (3g/-4)
+U - TP5/20G - %75 / 72 işlem - ADAY (19g/-4)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2070,7 +2067,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.7</v>
+        <v>-2</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2101,8 +2098,8 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-14)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-14)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-15)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-15)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2123,7 +2120,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2154,8 +2151,8 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/+1)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/0)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2176,7 +2173,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2207,7 +2204,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/+1)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/+2)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2228,7 +2225,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2259,8 +2256,8 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/0)
-U - TP5/20G - %75 / 72 işlem - ADAY (3g/-1)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-1)
+U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2281,7 +2278,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2312,7 +2309,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/+1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2333,7 +2330,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-1.4</v>
+        <v>-4.2</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2364,7 +2361,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-4)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2385,7 +2382,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2416,7 +2413,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+3)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2437,7 +2434,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2491,7 +2488,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2543,7 +2540,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2596,7 +2593,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -2627,8 +2624,8 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-5)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-6)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-6)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2649,7 +2646,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -2680,7 +2677,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-1.9</v>
+        <v>-2.2</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-7)
-M - TP5/20G - %89 / 47 işlem - ONAY (6g/-7)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-8)
+M - TP5/20G - %89 / 47 işlem - ONAY (6g/-8)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-11)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-5)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/-5)
-I - TP5/20G - %84 / 49 işlem - ADAY (8g/-5)
-Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-5)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-13)
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-7)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/-7)
+I - TP5/20G - %84 / 49 işlem - ADAY (8g/-7)
+Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-7)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-3.7</v>
+        <v>-7.4</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/-3)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/-6)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -689,11 +689,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.4</v>
+        <v>-4.2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
@@ -719,34 +719,34 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-3)
-H - TP5/20G - %83 / 40 işlem - ADAY (5g/-2)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-8)
+P - TP5/10G - %82 / 45 işlem - ADAY (6g/-8)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -759,36 +759,39 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-7)
-P - TP5/10G - %82 / 45 işlem - ADAY (6g/-7)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/0)
+T - TP5/10G - %64 / 133 işlem - ADAY (8g/-1)
+T - TP5/20G - %77 / 124 işlem - ADAY (8g/-1)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -799,7 +802,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -853,7 +856,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -902,160 +905,159 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/-3)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-1)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>İZLE</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
 E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AGHOL</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SISE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (6g/0)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1116,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VESTL</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1131,47 +1133,46 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (18g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-2)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.5</v>
+        <v>-2.8</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1190,24 +1191,25 @@
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-3)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1219,11 +1221,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.1</v>
+        <v>-2.6</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1236,7 +1238,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1249,18 +1251,18 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/-2)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1272,11 +1274,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1.8</v>
+        <v>3.1</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1289,32 +1291,30 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (12g/+1)
-T - TP5/10G - %64 / 133 işlem - ADAY (8g/0)
-T - TP5/20G - %77 / 124 işlem - ADAY (8g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 68 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1326,11 +1326,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1.6</v>
+        <v>-3.3</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1343,31 +1343,30 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -1379,11 +1378,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1396,46 +1395,47 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.1</v>
+        <v>-2.4</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1466,8 +1466,8 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1484,11 +1484,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1.1</v>
+        <v>-3.5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1514,34 +1514,34 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-4)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-1.4</v>
+        <v>-3.9</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1572,8 +1572,8 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-2)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-2)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-8)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-8)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1590,11 +1590,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1607,47 +1607,46 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+3)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/+3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/-7)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.1</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1660,30 +1659,31 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+1)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-6)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-7)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.3</v>
+        <v>-1.8</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-4)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1799,11 +1799,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.6</v>
+        <v>-6.3</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1816,46 +1816,46 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-3)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-5)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-3.3</v>
+        <v>-1.1</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1868,46 +1868,46 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-4)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.8</v>
+        <v>-5.3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>1</v>
@@ -1933,23 +1933,23 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (2g/+3)
-P - TP5/10G - %82 / 45 işlem - ADAY (2g/+3)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-6)
+H - TP5/20G - %83 / 40 işlem - ADAY (5g/-5)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-3.4</v>
+        <v>-5.7</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2044,9 +2044,9 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-4)
-H - TP5/20G - %83 / 40 işlem - ADAY (3g/-4)
-U - TP5/20G - %75 / 72 işlem - ADAY (19g/-4)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-6)
+H - TP5/20G - %83 / 40 işlem - ADAY (3g/-6)
+U - TP5/20G - %75 / 72 işlem - ADAY (19g/-7)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2</v>
+        <v>-4.9</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2098,8 +2098,8 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-15)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-15)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-18)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-18)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>1</v>
@@ -2151,8 +2151,8 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/0)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-2)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2162,18 +2162,18 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.4</v>
+        <v>-1.9</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2186,30 +2186,31 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/+2)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-1)
+U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2221,11 +2222,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-1.3</v>
+        <v>-3.1</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2244,25 +2245,24 @@
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-1)
-U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-2)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2274,11 +2274,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-1.8</v>
+        <v>-5.9</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/0)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-6)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2326,11 +2326,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-4.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-4)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/0)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2378,11 +2378,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1.2</v>
+        <v>-2</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2401,24 +2401,26 @@
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+3)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-2)
+R - TP5/10G - %60 / 103 işlem - ADAY (8g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-5)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2430,11 +2432,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2447,32 +2449,30 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-1)
-R - TP5/10G - %60 / 103 işlem - ADAY (8g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-4)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-4)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2484,11 +2484,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.5</v>
+        <v>-2.5</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2501,30 +2501,31 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-3)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -2536,11 +2537,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2553,146 +2554,40 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/+1)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-2)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-6)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-6)</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-1)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L42"/>
+  <autoFilter ref="A1:L40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.2</v>
+        <v>-3</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.1</v>
+        <v>-3.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -616,11 +616,11 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-13)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-7)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/-7)
-I - TP5/20G - %84 / 49 işlem - ADAY (8g/-7)
-Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-7)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-14)
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-8)
+I - TP5/10G - %61 / 103 işlem - ADAY (8g/-8)
+I - TP5/20G - %84 / 49 işlem - ADAY (8g/-8)
+Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-8)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-7.4</v>
+        <v>-6.7</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -689,93 +689,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-6)
+H - TP5/20G - %83 / 40 işlem - ADAY (5g/-6)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>ALTNY</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="B6" s="2" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-8)
 P - TP5/10G - %82 / 45 işlem - ADAY (6g/-8)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0)
+L - TP5/20G - %91 / 44 işlem - ONAY (1g/0)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/0)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
 E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)
@@ -784,132 +891,25 @@
 T - TP5/20G - %77 / 124 işlem - ADAY (8g/-1)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-4)
-R - TP5/10G - %60 / 103 işlem - ADAY (1g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (1g/-4)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-1)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-1)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-3.7</v>
+        <v>-6.1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -922,30 +922,32 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/-3)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-6)
+R - TP5/10G - %60 / 103 işlem - ADAY (1g/-6)
+R - TP5/20G - %80 / 95 işlem - ADAY (1g/-6)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -961,7 +963,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -993,7 +995,7 @@
       <c r="J10" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/0)
 Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-1)</t>
         </is>
       </c>
@@ -1015,7 +1017,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-3.5</v>
+        <v>-4.5</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1064,11 +1066,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-10</v>
+        <v>-4.4</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1081,46 +1083,47 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-28)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (12g/-3)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-2.4</v>
+        <v>-10</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1133,7 +1136,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1146,17 +1149,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-2)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-28)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1168,11 +1171,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-2.8</v>
+        <v>-1.9</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1191,130 +1194,130 @@
         <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-2)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PGSUS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3)
 Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-3)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ARCLK</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>-2.6</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="G16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2)
 I - TP5/10G - %61 / 103 işlem - ADAY (8g/-2)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AGHOL</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1)</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1326,11 +1329,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-3.3</v>
+        <v>4.4</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/0)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1382,7 +1385,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1435,7 +1438,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-2.4</v>
+        <v>-4.6</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1466,8 +1469,8 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/-3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1488,7 +1491,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1519,8 +1522,8 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-4)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1646,7 +1649,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1699,7 +1702,7 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1803,7 +1806,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-6.3</v>
+        <v>-5.3</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1834,7 +1837,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-5)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-4)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1855,7 +1858,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1903,11 +1906,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-5.3</v>
+        <v>-1.3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1920,7 +1923,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>1</v>
@@ -1933,18 +1936,18 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-6)
-H - TP5/20G - %83 / 40 işlem - ADAY (5g/-5)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-1)
+P - TP5/10G - %82 / 45 işlem - ADAY (6g/-1)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
@@ -1956,11 +1959,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.3</v>
+        <v>-6.4</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1979,25 +1982,26 @@
         <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-1)
-P - TP5/10G - %82 / 45 işlem - ADAY (6g/-1)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-7)
+H - TP5/20G - %83 / 40 işlem - ADAY (3g/-7)
+U - TP5/20G - %75 / 72 işlem - ADAY (19g/-7)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2009,11 +2013,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-5.7</v>
+        <v>-4.7</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2032,42 +2036,41 @@
         <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-6)
-H - TP5/20G - %83 / 40 işlem - ADAY (3g/-6)
-U - TP5/20G - %75 / 72 işlem - ADAY (19g/-7)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-17)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-17)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-4.9</v>
+        <v>-3.1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2080,31 +2083,30 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-18)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-18)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/-2)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2120,7 +2122,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-1.2</v>
+        <v>-2.1</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2151,8 +2153,8 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-2)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-3)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2173,7 +2175,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1.9</v>
+        <v>-2.3</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2204,8 +2206,8 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-1)
-U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-2)
+U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2226,7 +2228,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2257,7 +2259,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2278,7 +2280,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-5.9</v>
+        <v>-6.6</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2309,7 +2311,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-6)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-7)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2330,7 +2332,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2361,7 +2363,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/0)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+1)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2382,7 +2384,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-2</v>
+        <v>-1.1</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2413,7 +2415,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-2)
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-1)
 R - TP5/10G - %60 / 103 işlem - ADAY (8g/-5)
 R - TP5/20G - %80 / 95 işlem - ADAY (8g/-5)</t>
         </is>
@@ -2436,7 +2438,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2488,7 +2490,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-2.5</v>
+        <v>-1.7</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2519,8 +2521,8 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/-1)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/-1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/0)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/0)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2</v>
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-8)
-M - TP5/20G - %89 / 47 işlem - ONAY (6g/-8)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-11)
+M - TP5/20G - %89 / 47 işlem - ONAY (7g/-11)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -574,18 +574,18 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -598,34 +598,30 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>K-TP5/20G, E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (19g/-14)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-8)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/-8)
-I - TP5/20G - %84 / 49 işlem - ADAY (8g/-8)
-Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-8)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-6)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
@@ -637,11 +633,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-6.7</v>
+        <v>-0.6</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -660,24 +656,25 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (12g/-6)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-7)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -689,11 +686,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-6.2</v>
+        <v>0.5</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -706,31 +703,32 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-6)
-H - TP5/20G - %83 / 40 işlem - ADAY (5g/-6)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/+1)
+L - TP5/20G - %91 / 44 işlem - ONAY (2g/+1)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/+1)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -746,7 +744,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-4.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -759,7 +757,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>1</v>
@@ -777,8 +775,8 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-8)
-P - TP5/10G - %82 / 45 işlem - ADAY (6g/-8)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-8)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-8)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -788,18 +786,18 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -812,37 +810,37 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0)
-L - TP5/20G - %91 / 44 işlem - ONAY (1g/0)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/0)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-7)
+R - TP5/10G - %60 / 103 işlem - ADAY (2g/-7)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/-7)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -853,7 +851,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-3.2</v>
+        <v>1.1</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -866,7 +864,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>1</v>
@@ -884,32 +882,32 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/0)
-T - TP5/10G - %64 / 133 işlem - ADAY (8g/-1)
-T - TP5/20G - %77 / 124 işlem - ADAY (8g/-1)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/+1)
+T - TP5/10G - %64 / 133 işlem - ADAY (9g/0)
+T - TP5/20G - %77 / 124 işlem - ADAY (9g/0)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-6.1</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -922,32 +920,31 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (1g/-6)
-R - TP5/10G - %60 / 103 işlem - ADAY (1g/-6)
-R - TP5/20G - %80 / 95 işlem - ADAY (1g/-6)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -959,11 +956,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -976,32 +973,31 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-1)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1013,64 +1009,65 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-4.5</v>
+        <v>0.6</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (0g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (6g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (7g/0)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-4.4</v>
+        <v>-10</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1083,47 +1080,46 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (0g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (12g/-3)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-10</v>
+        <v>1.3</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1136,35 +1132,38 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>T-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (13g/-28)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-7)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-7)
+I - TP5/20G - %84 / 49 işlem - ADAY (9g/-7)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-7)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1174,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.9</v>
+        <v>1</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1205,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1227,7 +1226,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1258,8 +1257,8 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-3)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-2)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1276,11 +1275,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-2.6</v>
+        <v>0.4</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1293,7 +1292,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
@@ -1306,34 +1305,34 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2)
-I - TP5/10G - %61 / 103 işlem - ADAY (8g/-2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1346,46 +1345,47 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/0)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-1)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.7</v>
+        <v>0.6</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1411,34 +1411,34 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-2)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-4)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-4.6</v>
+        <v>0</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1464,34 +1464,34 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/-3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-4)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-8)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/-8)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-3.6</v>
+        <v>0.9</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1522,8 +1522,8 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-5)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+2)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/+2)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1540,11 +1540,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-3.9</v>
+        <v>0.8</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
@@ -1570,34 +1570,34 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-8)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-8)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-8.199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/-7)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1645,11 +1645,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.7</v>
+        <v>0.3</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1668,41 +1668,40 @@
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+1)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/+1)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-6)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1733,7 +1732,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-7)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1750,11 +1749,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-1.8</v>
+        <v>3.4</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1767,46 +1766,46 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-4)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-5.3</v>
+        <v>1.4</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1819,46 +1818,46 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (4g/-4)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1</v>
+        <v>1.7</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1871,35 +1870,36 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-4)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-5)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/-5)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.3</v>
+        <v>0.6</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1941,8 +1941,8 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (6g/-1)
-P - TP5/10G - %82 / 45 işlem - ADAY (6g/-1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/0)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/0)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1959,11 +1959,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-6.4</v>
+        <v>0.3</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1982,42 +1982,41 @@
         <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G, U-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-7)
-H - TP5/20G - %83 / 40 işlem - ADAY (3g/-7)
-U - TP5/20G - %75 / 72 işlem - ADAY (19g/-7)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-17)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-17)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-4.7</v>
+        <v>1.1</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2030,31 +2029,30 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-17)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-17)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-1)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2066,11 +2064,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-3.1</v>
+        <v>0.1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2083,46 +2081,47 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (11g/-2)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-3)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-2.1</v>
+        <v>0.9</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2135,47 +2134,47 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (17g/-3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-3)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-1)
+U - TP5/20G - %75 / 72 işlem - ADAY (4g/-2)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-2.3</v>
+        <v>0.4</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2194,25 +2193,24 @@
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (4g/-2)
-U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2224,11 +2222,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-2.4</v>
+        <v>1.3</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2259,7 +2257,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2276,11 +2274,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-6.6</v>
+        <v>-0.3</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2293,7 +2291,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
@@ -2311,7 +2309,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/-7)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-1)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2321,18 +2319,18 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2345,30 +2343,31 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (6g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2384,7 +2383,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2397,7 +2396,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
@@ -2415,9 +2414,9 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (1g/-1)
-R - TP5/10G - %60 / 103 işlem - ADAY (8g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-5)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1)
+R - TP5/10G - %60 / 103 işlem - ADAY (9g/-4)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-4)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2427,18 +2426,18 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2451,7 +2450,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
@@ -2464,33 +2463,33 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-4)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-6)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-1.7</v>
+        <v>0.5</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2503,36 +2502,35 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (3g/0)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/0)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-3)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2541,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2556,7 +2554,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
@@ -2574,7 +2572,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-2)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -2584,7 +2582,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.3</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
@@ -616,7 +616,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-6)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-8)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -721,9 +721,9 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/+1)
-L - TP5/20G - %91 / 44 işlem - ONAY (2g/+1)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/+1)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0)
+L - TP5/20G - %91 / 44 işlem - ONAY (2g/0)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/0)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -740,11 +740,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -770,18 +770,18 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-8)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-8)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-9)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/-9)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -793,11 +793,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.7</v>
+        <v>-1.7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -816,71 +816,229 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-7)
-R - TP5/10G - %60 / 103 işlem - ADAY (2g/-7)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/-7)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-9)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-9)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-19)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-19)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-9)
+R - TP5/10G - %60 / 103 işlem - ADAY (2g/-9)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/-9)</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-5)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
 E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1)
@@ -889,276 +1047,116 @@
 T - TP5/20G - %77 / 124 işlem - ADAY (9g/0)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1)
+E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SISE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/0)
 E - TP5/20G - %79 / 42 işlem - ADAY (6g/0)
 Q - TP5/20G - %67 / 83 işlem - ADAY (7g/0)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35)</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-7)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-7)
-I - TP5/20G - %84 / 49 işlem - ADAY (9g/-7)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-7)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1170,11 +1168,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1187,46 +1185,47 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/0)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1239,31 +1238,30 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>T-TP5/20G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-2)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1275,11 +1273,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1292,31 +1290,33 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-6)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-6)
+I - TP5/20G - %84 / 49 işlem - ADAY (9g/-6)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-6)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1328,11 +1328,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
@@ -1363,8 +1363,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1374,18 +1374,18 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1411,18 +1411,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-4)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1434,11 +1434,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1457,41 +1457,40 @@
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-8)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/-8)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1517,34 +1516,34 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+2)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/+2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1557,7 +1556,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
@@ -1570,18 +1569,18 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1593,11 +1592,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1610,46 +1609,47 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1662,30 +1662,31 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-6)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-9)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/-9)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -1697,11 +1698,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1714,30 +1715,31 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+3)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/+3)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L24" s="5" t="inlineStr">
@@ -1749,11 +1751,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3.4</v>
+        <v>-0.3</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1766,46 +1768,46 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1818,7 +1820,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
@@ -1836,7 +1838,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1846,18 +1848,18 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1870,31 +1872,30 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-5)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/-5)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -1906,11 +1907,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1923,47 +1924,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/0)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/0)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-7)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1976,47 +1976,46 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-17)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-17)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2029,30 +2028,31 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-1)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-2)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-2)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>1</v>
@@ -2099,8 +2099,8 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-3)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-3)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-1)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2152,8 +2152,8 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-1)
-U - TP5/20G - %75 / 72 işlem - ADAY (4g/-2)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-2)
+U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2170,11 +2170,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2222,11 +2222,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2274,11 +2274,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2319,18 +2319,18 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2343,31 +2343,30 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-7)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2379,11 +2378,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2402,42 +2401,41 @@
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1)
-R - TP5/10G - %60 / 103 işlem - ADAY (9g/-4)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-4)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/0)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/0)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2450,30 +2448,32 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-6)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1)
+R - TP5/10G - %60 / 103 işlem - ADAY (9g/-5)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-5)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-3)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-11)
-M - TP5/20G - %89 / 47 işlem - ONAY (7g/-11)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-11/%78)
+M - TP5/20G - %89 / 47 işlem - ONAY (7g/-11/%93)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-8)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-8/%67)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -668,8 +668,8 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-7)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-7/%94)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -721,9 +721,9 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0)
-L - TP5/20G - %91 / 44 işlem - ONAY (2g/0)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/0)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (2g/0/%100)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/0/%91)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -775,8 +775,8 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-9)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/-9)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-9/%82)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/-9/%93)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -828,8 +828,8 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-9)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-9)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-9/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-9/%60)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -881,8 +881,8 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-19)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-19)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-19/%25)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-19/%21)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -934,9 +934,9 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-9)
-R - TP5/10G - %60 / 103 işlem - ADAY (2g/-9)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/-9)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-9/%95)
+R - TP5/10G - %60 / 103 işlem - ADAY (2g/-9/%75)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/-9/%80)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-5)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-5/%45)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1040,11 +1040,11 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/+1)
-T - TP5/10G - %64 / 133 işlem - ADAY (9g/0)
-T - TP5/20G - %77 / 124 işlem - ADAY (9g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/+1/%100)
+T - TP5/10G - %64 / 133 işlem - ADAY (9g/0/%50)
+T - TP5/20G - %77 / 124 işlem - ADAY (9g/0/%65)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1096,8 +1096,8 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1)
-E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1/%85)
+E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4/%55)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1149,9 +1149,9 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (6g/0)
-Q - TP5/20G - %67 / 83 işlem - ADAY (7g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/0/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (6g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (7g/0/%100)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1203,8 +1203,8 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/0)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35/%10)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1308,10 +1308,10 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-6)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-6)
-I - TP5/20G - %84 / 49 işlem - ADAY (9g/-6)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-6)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-6/%64)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-6/%30)
+I - TP5/20G - %84 / 49 işlem - ADAY (9g/-6/%88)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-6/%45)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1363,8 +1363,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1/%58)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1/%70)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1416,8 +1416,8 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1/%50)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1/%80)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1521,8 +1521,8 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%60)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1574,8 +1574,8 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1/%76)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2/%21)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1627,8 +1627,8 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3/%65)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3/%70)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1680,8 +1680,8 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-9)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/-9)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-9/%25)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/-9/%60)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1733,8 +1733,8 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+3)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/+3)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+3/%100)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/+3/%100)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0/%55)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4/%15)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1/%80)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-7)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-7/%21)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2/%60)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2046,8 +2046,8 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-2)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-2)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-2/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-2/%60)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2099,8 +2099,8 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-1)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-1/%50)
+Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1/%40)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2152,8 +2152,8 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-2)
-U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-2/%65)
+U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%70)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2/%90)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6/%85)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2/%100)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-7)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-7/%76)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2413,8 +2413,8 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/0)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/0)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/0/%100)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/0/%100)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -2466,9 +2466,9 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1)
-R - TP5/10G - %60 / 103 işlem - ADAY (9g/-5)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-5)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1/%95)
+R - TP5/10G - %60 / 103 işlem - ADAY (9g/-5/%15)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-5/%60)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4/%50)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-2)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-2/%85)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.8</v>
+        <v>-3.9</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-11/%78)
-M - TP5/20G - %89 / 47 işlem - ONAY (7g/-11/%93)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-12/%78)
+M - TP5/20G - %89 / 47 işlem - ONAY (7g/-12/%93)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.3</v>
+        <v>-2.8</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -668,8 +668,8 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-7/%94)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-9/%94)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-8/%91)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -686,11 +686,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -703,85 +703,86 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
+L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (14g/-26/%10)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
 L - TP5/20G - %91 / 44 işlem - ONAY (2g/0/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/0/%91)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/0/%100)</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TAVHL</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-9/%82)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/-9/%93)</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -793,11 +794,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -823,87 +824,87 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-8/%82)
+H - TP5/20G - %83 / 40 işlem - ADAY (4g/-8/%93)</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-9/%78)
 P - TP5/10G - %82 / 45 işlem - ADAY (7g/-9/%60)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-19/%25)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-19/%21)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -922,26 +923,25 @@
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-9/%95)
-R - TP5/10G - %60 / 103 işlem - ADAY (2g/-9/%75)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/-9/%80)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-18/%25)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-18/%21)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
@@ -953,11 +953,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-2.4</v>
+        <v>0.9</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -970,30 +970,32 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-5/%45)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-5/%100)
+R - TP5/10G - %60 / 103 işlem - ADAY (2g/-5/%75)
+R - TP5/20G - %80 / 95 işlem - ADAY (2g/-5/%80)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1005,11 +1007,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.7</v>
+        <v>-5.1</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1025,243 +1027,243 @@
         <v>54</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-7/%45)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1/%100)
 E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/+1/%100)
-T - TP5/10G - %64 / 133 işlem - ADAY (9g/0/%50)
-T - TP5/20G - %77 / 124 işlem - ADAY (9g/0/%65)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/0/%100)
+T - TP5/10G - %64 / 133 işlem - ADAY (9g/-1/%50)
+T - TP5/20G - %77 / 124 işlem - ADAY (9g/-1/%65)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-1/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (6g/0/%74)
+Q - TP5/20G - %67 / 83 işlem - ADAY (7g/-1/%85)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1/%85)
+E - TP5/20G - %79 / 42 işlem - ADAY (1g/-1/%93)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>MGROS</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>-0.8</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="F15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1/%85)
 E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4/%55)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SISE</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/0/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (6g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (7g/0/%100)</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/-35/%10)</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1277,7 +1279,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1332,7 +1334,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1363,8 +1365,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1/%58)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-1/%70)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/0/%100)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1385,7 +1387,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1416,8 +1418,8 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-1/%50)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-2/%64)
+I - TP5/10G - %61 / 103 işlem - ADAY (9g/-2/%50)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1434,11 +1436,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1451,7 +1453,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
@@ -1464,33 +1466,33 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-1/%80)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1/%100)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1509,147 +1511,146 @@
         <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
 Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%60)</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>TURSG</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="F22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1/%76)
 Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2/%21)</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3/%65)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1680,8 +1681,8 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-9/%25)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/-9/%60)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-4/%55)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-4/%65)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1698,11 +1699,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1.3</v>
+        <v>-1.6</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1715,7 +1716,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
@@ -1733,8 +1734,8 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+3/%100)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/+3/%100)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-10/%25)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/-10/%60)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1744,18 +1745,18 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1768,30 +1769,31 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0/%55)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+2/%100)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/+2/%100)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -1803,11 +1805,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1838,7 +1840,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4/%15)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-3/%60)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1855,11 +1857,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1872,46 +1874,46 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-1/%80)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2/%15)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.7</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1924,46 +1926,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-7/%21)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-2/%80)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1994,7 +1996,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-2/%60)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-3/%85)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2011,11 +2013,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.6</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2028,137 +2030,136 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-2/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-2/%60)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-9/%21)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-4/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (7g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ODAS</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
+      <c r="B32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="F32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-1/%50)
 Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1/%40)</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>OYAKC</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-2/%65)
-U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%70)</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2170,11 +2171,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-0.8</v>
+        <v>-3.5</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2193,24 +2194,25 @@
         <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-2/%90)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-5/%50)
+U - TP5/20G - %75 / 72 işlem - ADAY (4g/-6/%70)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2222,11 +2224,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.9</v>
+        <v>-2.2</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2257,7 +2259,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6/%85)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3/%75)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2274,11 +2276,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2309,7 +2311,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+2/%100)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6/%85)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2326,11 +2328,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2343,7 +2345,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0</v>
@@ -2356,17 +2358,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-7/%76)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+1/%100)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
@@ -2378,11 +2380,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2395,31 +2397,32 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/0/%100)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/0/%100)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-2/%85)
+R - TP5/10G - %60 / 103 işlem - ADAY (9g/-6/%10)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-6/%60)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2431,11 +2434,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2448,44 +2451,42 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-1/%95)
-R - TP5/10G - %60 / 103 işlem - ADAY (9g/-5/%15)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-5/%60)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-5/%40)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -2502,46 +2503,47 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4/%50)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1/%85)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1/%100)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.3</v>
+        <v>1.6</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2554,7 +2556,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>0</v>
@@ -2567,22 +2569,22 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-2/%85)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-6/%76)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-3.9</v>
+        <v>-0.3</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>2</v>
@@ -563,8 +563,8 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-12/%78)
-M - TP5/20G - %89 / 47 işlem - ONAY (7g/-12/%93)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (8g/-12/%76)
+M - TP5/20G - %89 / 47 işlem - ONAY (8g/-12/%92)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.8</v>
+        <v>-2.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>1</v>
@@ -616,7 +616,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (13g/-8/%67)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (14g/-10/%67)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -626,18 +626,18 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.2</v>
+        <v>-1.4</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -653,44 +653,45 @@
         <v>61</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-9/%94)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-8/%91)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-1/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (3g/-1/%100)
+L - TP5/10G - %79 / 42 işlem - ADAY (3g/-1/%90)</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -703,48 +704,47 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (14g/-26/%10)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (5g/-8/%93)
+H - TP5/20G - %83 / 40 işlem - ADAY (7g/-8/%91)</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2</v>
+        <v>-1</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -757,37 +757,38 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (2g/0/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/0/%100)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0/%75)
+E - TP5/20G - %79 / 42 işlem - ADAY (2g/0/%89)
+Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-1/%65)
+T - TP5/20G - %77 / 124 işlem - ADAY (10g/-2/%70)</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -798,7 +799,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.8</v>
+        <v>-0.9</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -811,7 +812,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -829,8 +830,8 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-8/%82)
-H - TP5/20G - %83 / 40 işlem - ADAY (4g/-8/%93)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-9/%80)
+H - TP5/20G - %83 / 40 işlem - ADAY (5g/-9/%94)</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -840,7 +841,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -851,7 +852,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.9</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -864,7 +865,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>1</v>
@@ -882,8 +883,8 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-9/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-9/%60)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-9/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (8g/-9/%60)</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -893,7 +894,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -904,7 +905,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -935,8 +936,8 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-18/%25)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-18/%21)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-19/%25)
+Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-19/%15)</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -953,11 +954,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -970,7 +971,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
@@ -983,19 +984,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (2g/-5/%100)
-R - TP5/10G - %60 / 103 işlem - ADAY (2g/-5/%75)
-R - TP5/20G - %80 / 95 işlem - ADAY (2g/-5/%80)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2/%57)
+E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)
+Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-2/%75)</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1007,11 +1008,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-5.1</v>
+        <v>-1</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1024,30 +1025,32 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (12g/-7/%45)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-7/%58)
+I - TP5/20G - %84 / 49 işlem - ADAY (10g/-7/%77)
+Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-7/%55)</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1059,11 +1062,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1076,34 +1079,32 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/10G, T-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/+1/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/+1/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/0/%100)
-T - TP5/10G - %64 / 133 işlem - ADAY (9g/-1/%50)
-T - TP5/20G - %77 / 124 işlem - ADAY (9g/-1/%65)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-7/%94)
+R - TP5/10G - %60 / 103 işlem - ADAY (3g/-7/%60)
+R - TP5/20G - %80 / 95 işlem - ADAY (3g/-7/%65)</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1115,11 +1116,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.2</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1132,32 +1133,31 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-1/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (6g/0/%74)
-Q - TP5/20G - %67 / 83 işlem - ADAY (7g/-1/%85)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-3/%75)
+E - TP5/20G - %79 / 42 işlem - ADAY (2g/-3/%89)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1169,11 +1169,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1204,8 +1204,8 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1/%85)
-E - TP5/20G - %79 / 42 işlem - ADAY (1g/-1/%93)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1/%75)
+E - TP5/20G - %79 / 42 işlem - ADAY (14g/-4/%33)</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1222,11 +1222,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1239,47 +1239,46 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (1g/-1/%85)
-E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4/%55)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (13g/-10/%30)</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2.1</v>
+        <v>-1</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1292,38 +1291,36 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G, I-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-6/%64)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-6/%30)
-I - TP5/20G - %84 / 49 işlem - ADAY (9g/-6/%88)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-6/%45)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-3/%70)
+R - TP5/20G - %80 / 95 işlem - ADAY (10g/-7/%55)</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1331,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.3</v>
+        <v>-1</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1365,8 +1362,8 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1/%55)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1/%65)</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1383,11 +1380,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1400,7 +1397,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1413,18 +1410,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-2/%64)
-I - TP5/10G - %61 / 103 işlem - ADAY (9g/-2/%50)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-3/%33)
+Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-3/%65)</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
@@ -1440,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1471,7 +1468,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+1/%100)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1488,11 +1485,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1505,7 +1502,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
@@ -1518,33 +1515,33 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-2/%80)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3/%58)</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1563,25 +1560,24 @@
         <v>0</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%60)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3/%75)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1597,7 +1593,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1628,8 +1624,8 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1/%76)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2/%21)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-2/%74)
+Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-3/%15)</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1650,7 +1646,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1681,8 +1677,8 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-4/%55)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-4/%65)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-5/%40)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/-5/%65)</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1699,11 +1695,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-1.6</v>
+        <v>-3</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1716,7 +1712,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
@@ -1734,8 +1730,8 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-10/%25)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/-10/%60)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (8g/-1/%50)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-1/%85)</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1745,18 +1741,18 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.4</v>
+        <v>-2.8</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1787,8 +1783,8 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/+2/%100)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/+2/%100)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-12/%15)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-12/%50)</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1805,11 +1801,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1840,7 +1836,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-3/%60)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-3/%75)</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -1857,11 +1853,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2.2</v>
+        <v>-0.6</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1892,7 +1888,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2/%15)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-10/%15)</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1909,11 +1905,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.4</v>
+        <v>-1</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1926,46 +1922,46 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (5g/-2/%80)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-4/%55)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.7</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -1978,46 +1974,46 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="H29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-3/%85)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-3/%80)</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-2.6</v>
+        <v>-3.1</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2030,46 +2026,48 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-9/%21)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%100)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-3/%93)
+T - TP5/20G - %77 / 124 işlem - ADAY (15g/-28/%5)</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2.7</v>
+        <v>-1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2095,18 +2093,18 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (7g/-4/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (7g/-4/%60)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/-1/%100)</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2118,11 +2116,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>-1.5</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2135,7 +2133,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>1</v>
@@ -2148,18 +2146,18 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (18g/-1/%50)
-Q - TP5/20G - %67 / 83 işlem - ADAY (17g/-1/%40)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-5/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (8g/-5/%60)</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
@@ -2171,11 +2169,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-3.5</v>
+        <v>-0.4</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2188,31 +2186,31 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (5g/-5/%50)
-U - TP5/20G - %75 / 72 işlem - ADAY (4g/-6/%70)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-1/%25)
+Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-1/%20)</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2224,11 +2222,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2247,24 +2245,25 @@
         <v>0</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3/%75)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-7/%40)
+U - TP5/20G - %75 / 72 işlem - ADAY (5g/-8/%75)</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
@@ -2276,11 +2275,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.6</v>
+        <v>-1</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2311,7 +2310,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (2g/-6/%85)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-4/%70)</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2328,11 +2327,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2363,7 +2362,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (7g/+1/%100)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-5/%75)</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2380,11 +2379,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2403,26 +2402,24 @@
         <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (2g/-2/%85)
-R - TP5/10G - %60 / 103 işlem - ADAY (9g/-6/%10)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-6/%60)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (8g/-1/%90)</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2434,11 +2431,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.2</v>
+        <v>-2.1</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2451,30 +2448,31 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-5/%40)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3/%65)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3/%80)</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
@@ -2486,11 +2484,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2503,47 +2501,46 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (4g/-1/%85)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-1/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-7/%74)</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2569,17 +2566,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/-6/%76)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (8g/-6/%25)</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -76,10 +76,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -446,21 +446,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,53 +487,58 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Puan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Onaylı_Sistem_Sayısı</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Aday_Sistem_Sayısı</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Toplam_Öneren_Sistem</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sistem_Kodları</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sistem_Detayı</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Neden</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Engel_Risk</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -544,48 +550,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (8g/-12/%76)
-M - TP5/20G - %89 / 47 işlem - ONAY (8g/-12/%92)</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (8g/-13/%76)
+M - TP5/20G - %89 / 47 işlem - ONAY (8g/-13/%92)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>ASTOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -597,47 +609,53 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>P-TP5/20G</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (14g/-10/%67)</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (14g/-11/%67)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>KLRHO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -649,49 +667,55 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 4, İZLE</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="G4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-1/%100)
 L - TP5/20G - %91 / 44 işlem - ONAY (3g/-1/%100)
 L - TP5/10G - %79 / 42 işlem - ADAY (3g/-1/%90)</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -703,48 +727,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (5g/-8/%93)
-H - TP5/20G - %83 / 40 işlem - ADAY (7g/-8/%91)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (5g/-9/%93)
+H - TP5/20G - %83 / 40 işlem - ADAY (7g/-9/%91)</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>TSKB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -756,50 +786,56 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0/%75)
-E - TP5/20G - %79 / 42 işlem - ADAY (2g/0/%89)
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1/%75)
+E - TP5/20G - %79 / 42 işlem - ADAY (2g/-1/%89)
 Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-1/%65)
 T - TP5/20G - %77 / 124 işlem - ADAY (10g/-2/%70)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t>TAVHL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -811,48 +847,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-9/%80)
-H - TP5/20G - %83 / 40 işlem - ADAY (5g/-9/%94)</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-10/%80)
+H - TP5/20G - %83 / 40 işlem - ADAY (5g/-10/%94)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>ALTNY</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -864,48 +906,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-9/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (8g/-9/%60)</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-10/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (8g/-10/%60)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>AKSEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.4</v>
+        <v>0.8</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -917,156 +965,174 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-19/%25)
-Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-19/%15)</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-18/%25)
+Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-18/%15)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-3/%57)
+E - TP5/20G - %79 / 42 işlem - ADAY (7g/-3/%67)
+Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-3/%75)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SISE</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2/%57)
-E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)
-Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-7/%58)
 I - TP5/20G - %84 / 49 işlem - ADAY (10g/-7/%77)
 Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-7/%55)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>EFOR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1078,49 +1144,55 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-7/%94)
 R - TP5/10G - %60 / 103 işlem - ADAY (3g/-7/%60)
 R - TP5/20G - %80 / 95 işlem - ADAY (3g/-7/%65)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>HEKTS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1132,48 +1204,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="G13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-3/%75)
 E - TP5/20G - %79 / 42 işlem - ADAY (2g/-3/%89)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
           <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1.9</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1185,48 +1263,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="G14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-1/%75)
-E - TP5/20G - %79 / 42 işlem - ADAY (14g/-4/%33)</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-3/%75)
+E - TP5/20G - %79 / 42 işlem - ADAY (14g/-6/%33)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>MAGEN</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1238,47 +1322,53 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>R-TP5/20G</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>R - TP5/20G - %80 / 95 işlem - ADAY (13g/-10/%30)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>ANSGR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-1</v>
+        <v>-1.6</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1290,48 +1380,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-3/%70)
-R - TP5/20G - %80 / 95 işlem - ADAY (10g/-7/%55)</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-4/%70)
+R - TP5/20G - %80 / 95 işlem - ADAY (10g/-7/%50)</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1343,97 +1439,108 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1/%55)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1/%65)</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-3/%33)
 Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-3/%65)</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1449,47 +1556,53 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3/%58)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1501,43 +1614,49 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="F20" s="4" t="n">
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-3/%58)</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3/%75)</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1553,47 +1672,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (12g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>TURSG</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1605,48 +1731,54 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-2/%74)
 Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-3/%15)</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>MAVI</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1658,41 +1790,47 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="H23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-5/%40)
 R - TP5/20G - %80 / 95 işlem - ADAY (6g/-5/%65)</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>SASA</t>
@@ -1711,882 +1849,984 @@
           <t>ELDE TUT</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="H24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (8g/-1/%50)
 R - TP5/20G - %80 / 95 işlem - ADAY (8g/-1/%85)</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>U-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (8g/-8/%25)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>PSGYO</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="B26" s="2" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="H26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-12/%15)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-12/%50)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-13/%15)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-13/%50)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>BRYAT</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B27" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EREGL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-10/%15)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F26" s="4" t="n">
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 4, İZLE</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-5/%55)</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>EREGL</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-10/%15)</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>FROTO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-5/%100)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-5/%93)
+T - TP5/20G - %77 / 124 işlem - ADAY (15g/-30/%5)</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-4/%55)</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TKFEN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>K-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-3/%80)</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-3/%93)
-T - TP5/20G - %77 / 124 işlem - ADAY (15g/-28/%5)</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
 H - TP5/20G - %83 / 40 işlem - ADAY (1g/-1/%100)</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>TRENJ</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="B33" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 5, AL</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-5/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (8g/-5/%60)</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-4/%78)
+P - TP5/10G - %82 / 45 işlem - ADAY (8g/-4/%60)</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ODAS</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>-0.4</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>L-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-1/%25)
 Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-1/%20)</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>OYAKC</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B35" s="2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 4, İZLE</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-6/%40)
+U - TP5/20G - %75 / 72 işlem - ADAY (5g/-7/%75)</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1
+TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-6/%75)</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (8g/-3/%90)</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-2/%65)
+R - TP5/20G - %80 / 95 işlem - ADAY (5g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
         <v>-2</v>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F34" s="4" t="n">
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-7/%40)
-U - TP5/20G - %75 / 72 işlem - ADAY (5g/-8/%75)</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-4/%70)</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ENJSA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-5/%75)</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SAHOL</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (8g/-1/%90)</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ALARK</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/-3/%65)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/-3/%80)</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
+      <c r="H40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-7/%74)</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-8/%74)</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TOASO</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>U-TP2/10G</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (8g/-6/%25)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:M40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -540,11 +540,11 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>PASEU</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -558,41 +558,40 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL +1, XU030 +1
-TOPLAM 4, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -603,7 +602,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-3.8</v>
+        <v>-1.5</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
@@ -617,8 +616,8 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -640,8 +639,8 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (8g/-15/%76)
-M - TP5/20G - %89 / 47 işlem - ONAY (8g/-15/%92)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (9g/-17/%71)
+M - TP5/20G - %89 / 47 işlem - ONAY (9g/-17/%86)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -662,7 +661,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.5</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -676,8 +675,8 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL +1, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -699,7 +698,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (14g/-9/%67)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-11/%60)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -720,7 +719,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -734,41 +733,42 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (5g/-7/%93)
-H - TP5/20G - %83 / 40 işlem - ADAY (7g/-7/%91)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-7/%93)
+H - TP5/20G - %83 / 40 işlem - ADAY (8g/-6/%90)
+Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -793,8 +793,8 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -816,9 +816,9 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/-1/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (3g/-1/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (3g/-1/%90)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-1/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (4g/-1/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-1/%91)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -835,11 +835,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -853,44 +853,42 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1/%55)
-H - TP5/10G - %70 / 20 işlem - ADAY (0g/0/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (12g/-1/%70)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-10/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/-10/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (16g/-34/%5)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -901,7 +899,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -915,7 +913,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
@@ -938,8 +936,8 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-8/%80)
-H - TP5/20G - %83 / 40 işlem - ADAY (5g/-8/%94)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-7/%80)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -956,11 +954,11 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -974,50 +972,48 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (2g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (14g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (10g/-1/%70)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-10/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-10/%50)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1035,8 +1031,8 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -1046,25 +1042,28 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-9/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (8g/-9/%60)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (13g/-1/%55)
+H - TP5/10G - %70 / 20 işlem - ADAY (1g/0/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1/%75)</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1076,11 +1075,11 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1094,35 +1093,37 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (13g/-7/%30)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-14/%94)
+R - TP5/10G - %60 / 103 işlem - ADAY (4g/-14/%45)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-14/%60)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1134,11 +1135,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1152,52 +1153,51 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-15/%25)
-Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-15/%20)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-7/%35)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-1.2</v>
+        <v>-0.4</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1211,37 +1211,36 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (4g/-2/%57)
-E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)
-Q - TP5/20G - %67 / 83 işlem - ADAY (8g/-2/%75)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (3g/-3/%82)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1253,11 +1252,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.1</v>
+        <v>-0.6</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -1271,37 +1270,36 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-4/%58)
-I - TP5/20G - %84 / 49 işlem - ADAY (10g/-4/%77)
-Q - TP5/20G - %67 / 83 işlem - ADAY (10g/-4/%60)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-2/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-5/%40)</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1313,11 +1311,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-7</v>
+        <v>1.4</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -1331,37 +1329,37 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (3g/-12/%94)
-R - TP5/10G - %60 / 103 işlem - ADAY (3g/-12/%65)
-R - TP5/20G - %80 / 95 işlem - ADAY (3g/-12/%65)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+2/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (11g/+1/%100)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1373,11 +1371,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-2.2</v>
+        <v>0.1</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -1391,36 +1389,36 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-3/%75)
-E - TP5/20G - %79 / 42 işlem - ADAY (2g/-3/%89)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%85)
+R - TP5/20G - %80 / 95 işlem - ADAY (11g/-7/%50)</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1432,11 +1430,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -1450,52 +1448,53 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (2g/-2/%75)
-E - TP5/20G - %79 / 42 işlem - ADAY (14g/-5/%33)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/-2/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1/%64)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-2/%70)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -1509,52 +1508,53 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (3g/-4/%75)
-R - TP5/20G - %80 / 95 işlem - ADAY (10g/-7/%55)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-5/%58)
+I - TP5/20G - %84 / 49 işlem - ADAY (11g/-5/%79)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-5/%60)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-1.5</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -1568,51 +1568,54 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-4/%80)</t>
+          <t>Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %60 / 103 işlem - ADAY (8g/-11/%20)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-11/%50)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-3.3</v>
+        <v>0.5</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -1626,8 +1629,8 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -1637,25 +1640,24 @@
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-5/%33)
-Q - TP5/20G - %67 / 83 işlem - ADAY (14g/-5/%55)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%70)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1671,7 +1673,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1685,8 +1687,8 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL +1, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1708,7 +1710,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-2/%58)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-2/%58)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1725,11 +1727,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1743,52 +1745,51 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-1/%74)
-Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2/%20)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-0.6</v>
+        <v>1.5</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -1802,8 +1803,8 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1820,34 +1821,34 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/-5/%40)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/-5/%65)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-4/%40)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-4/%60)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-3.8</v>
+        <v>0.3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -1861,8 +1862,8 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -1884,8 +1885,8 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (8g/-2/%45)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-2/%85)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+2/%100)
+R - TP5/20G - %80 / 95 işlem - ADAY (6g/+2/%100)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1902,11 +1903,11 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-2.8</v>
+        <v>0.2</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -1920,51 +1921,52 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (8g/-7/%25)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4/%30)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4/%65)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
@@ -1978,36 +1980,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (5g/+2/%100)
-R - TP5/20G - %80 / 95 işlem - ADAY (5g/+2/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-1/%67)</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2019,11 +2020,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-1.9</v>
+        <v>0.4</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
@@ -2037,8 +2038,8 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -2060,8 +2061,8 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-11/%15)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-11/%50)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-2/%25)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-2/%75)</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2082,7 +2083,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -2096,8 +2097,8 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -2119,7 +2120,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (5g/-4/%80)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-3/%75)</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2136,11 +2137,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -2154,12 +2155,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
@@ -2177,7 +2178,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-10/%20)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-4/%65)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2187,18 +2188,18 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -2212,51 +2213,51 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="I30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-4/%60)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-4/%78)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>SKBNK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -2270,51 +2271,52 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (6g/-4/%80)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-9.4</v>
+        <v>-0.7</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -2328,37 +2330,36 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-9/%100)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-9/%93)
-T - TP5/20G - %77 / 124 işlem - ADAY (15g/-33/%5)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-1/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-1/%50)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2370,11 +2371,11 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.7</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -2388,12 +2389,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
 TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
@@ -2406,18 +2407,18 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/-1/%100)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%93)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-3/%93)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2429,11 +2430,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -2447,8 +2448,8 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL +1, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -2465,18 +2466,18 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (8g/-1/%78)
-P - TP5/10G - %82 / 45 işlem - ADAY (8g/-1/%60)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)
+H - TP5/20G - %83 / 40 işlem - ADAY (2g/-1/%100)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2488,11 +2489,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -2506,52 +2507,51 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1
-TOPLAM -2, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>L-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (19g/-2/%25)
-Q - TP5/20G - %67 / 83 işlem - ADAY (18g/-2/%25)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%85)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -2565,8 +2565,8 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL +2, CNDL -1, XU030 -1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
@@ -2576,25 +2576,24 @@
         <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (6g/-4/%50)
-U - TP5/20G - %75 / 72 işlem - ADAY (5g/-5/%75)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2606,11 +2605,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -2624,8 +2623,8 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 5, AL</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
@@ -2647,7 +2646,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%70)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/+1/%100)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2664,11 +2663,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -2682,51 +2681,53 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
         <v>13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>T-TP2/10G, T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (3g/-4/%80)</t>
+          <t>T - TP2/10G - %86 / 49 işlem - ONAY (1g/+1/%100)
+T - TP5/10G - %64 / 133 işlem - ADAY (1g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY T: gap-down sonrası gün içi toparlanma teyidi; ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.3</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -2740,51 +2741,52 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (8g/0/%100)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4/%45)
+U - TP5/20G - %75 / 72 işlem - ADAY (6g/-6/%80)</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -2798,12 +2800,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
@@ -2816,27 +2818,143 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
+TOPLAM -2, ALMA</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>E-TP5/20G</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/-5/%74)</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-5/%67)</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ODAS</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2/%25)</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M40"/>
+  <autoFilter ref="A1:M42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,7 +81,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -540,112 +534,112 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PASEU</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.1</v>
+        <v>-2.1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUGÜN</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (0g/0/%100)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (9g/-17/%71)
+M - TP5/20G - %89 / 47 işlem - ONAY (9g/-17/%86)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+        <v>-4.7</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS -1, PHL +2, CNDL 0, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (9g/-17/%71)
-M - TP5/20G - %89 / 47 işlem - ONAY (9g/-17/%86)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-13/%60)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -657,26 +651,26 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -686,24 +680,25 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-11/%60)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-8/%93)
+H - TP5/20G - %83 / 40 işlem - ADAY (8g/-8/%90)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -715,206 +710,205 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+        <v>-2.2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
         <v>61</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G, Q-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-7/%93)
-H - TP5/20G - %83 / 40 işlem - ADAY (8g/-6/%90)
-Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-3/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (4g/-3/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-3/%91)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+        <v>-6.7</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-1/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (4g/-1/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-1/%91)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-16/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/-16/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (16g/-38/%5)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-10/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/-10/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (16g/-34/%5)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-8/%80)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-8/%91)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -931,18 +925,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>P-TP5/20G, P-TP5/10G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-7/%80)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-14/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-14/%50)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -954,85 +948,88 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-10/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-10/%50)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
+E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
+H - TP5/10G - %70 / 20 işlem - ADAY (1g/-1/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/-1/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%75)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+        <v>-5.1</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL -2, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -1042,88 +1039,84 @@
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (13g/-1/%55)
-H - TP5/10G - %70 / 20 işlem - ADAY (1g/0/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-1/%75)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-16/%94)
+R - TP5/10G - %60 / 103 işlem - ADAY (4g/-16/%45)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-16/%60)</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+        <v>-0.4</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-14/%94)
-R - TP5/10G - %60 / 103 işlem - ADAY (4g/-14/%45)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-14/%60)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-8/%30)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1135,15 +1128,15 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1153,35 +1146,37 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-7/%35)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/-3/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-3/%65)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1197,22 +1192,22 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1234,8 +1229,8 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (3g/-3/%82)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-4/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (3g/-4/%82)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1256,22 +1251,22 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+        <v>-1.3</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -1293,8 +1288,8 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-2/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-5/%40)</t>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-6/%40)</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1315,22 +1310,22 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+        <v>1.2</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1353,8 +1348,8 @@
       <c r="K15" s="4" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+2/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (11g/+1/%100)</t>
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (11g/0/%100)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1375,22 +1370,22 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
+        <v>-0.4</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
-TOPLAM 0, ALMA</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -1412,7 +1407,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%85)
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%75)
 R - TP5/20G - %80 / 95 işlem - ADAY (11g/-7/%50)</t>
         </is>
       </c>
@@ -1430,55 +1425,55 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
         <v>50</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/-2/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1/%64)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-2/%70)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4/%58)
+I - TP5/20G - %84 / 49 işlem - ADAY (11g/-4/%79)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-4/%70)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1490,151 +1485,149 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-5/%58)
-I - TP5/20G - %84 / 49 işlem - ADAY (11g/-5/%79)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-5/%60)</t>
+          <t>Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %60 / 103 işlem - ADAY (8g/-12/%20)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-12/%50)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+        <v>1.2</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 5, AL</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 103 işlem - ADAY (8g/-11/%20)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-11/%50)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
+        <v>-0.8</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1647,17 +1640,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%70)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-3/%58)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1669,26 +1662,26 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+        <v>0.2</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1705,17 +1698,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-2/%58)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1727,30 +1720,30 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -1763,22 +1756,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1789,22 +1782,22 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
+        <v>0.6</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1826,8 +1819,8 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-4/%40)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-4/%60)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-5/%40)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-5/%60)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1844,26 +1837,26 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -1885,927 +1878,925 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-5/%35)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-5/%60)</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-2/%25)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-2/%75)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BRYAT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-6/%78)</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SKBNK</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/+1/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 5, AL</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-3/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-3/%50)</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 5, AL</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-4/%93)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-4/%93)</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/+1/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (2g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%85)</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-6/%67)</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-6/%35)
+U - TP5/20G - %75 / 72 işlem - ADAY (6g/-7/%75)</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-4/%70)</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL -1, XU030 +1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
           <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+2/%100)
 R - TP5/20G - %80 / 95 işlem - ADAY (6g/+2/%100)</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-4/%30)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-4/%65)</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-1/%67)</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SASA</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-2/%25)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-2/%75)</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
-TOPLAM 0, ALMA</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-3/%75)</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>FROTO</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
-TOPLAM -2, ALMA</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-4/%65)</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TKFEN</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>K-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-4/%78)</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SKBNK</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-1/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-1/%50)</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>IZENR</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-3/%93)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-3/%93)</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)
-H - TP5/20G - %83 / 40 işlem - ADAY (2g/-1/%100)</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%85)</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL -1, XU030 -1
-TOPLAM 2, ALMA</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SAHOL</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ISCTR</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>T-TP2/10G, T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>T - TP2/10G - %86 / 49 işlem - ONAY (1g/+1/%100)
-T - TP5/10G - %64 / 133 işlem - ADAY (1g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>ONAY T: gap-down sonrası gün içi toparlanma teyidi; ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 49 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OYAKC</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-4/%45)
-U - TP5/20G - %75 / 72 işlem - ADAY (6g/-6/%80)</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>ODAS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+        <v>-1.4</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
@@ -2818,75 +2809,76 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4/%25)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-5/%67)</t>
+          <t>T - TP5/10G - %64 / 133 işlem - ADAY (1g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -2895,66 +2887,8 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ODAS</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-2/%25)</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M42"/>
+  <autoFilter ref="A1:M41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -552,8 +552,8 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
@@ -593,11 +593,11 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-4.7</v>
+        <v>0.7</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -611,51 +611,58 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL +2, CNDL 0, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP2/10G, M-TP2/10G, M-TP5/20G, M-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-13/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+M - TP2/10G - %98 / 59 işlem - ONAY (0g/0/%100)
+M - TP5/20G - %89 / 47 işlem - ONAY (4g/-11/%94)
+M - TP5/10G - %71 / 49 işlem - ADAY (0g/0/%100)
+Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %60 / 103 işlem - ADAY (4g/-11/%45)
+R - TP5/20G - %80 / 95 işlem - ADAY (4g/-11/%60)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY M: TDA ve PFY-S birlikte dönüş teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 50 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-1.3</v>
+        <v>-4.9</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -669,8 +676,8 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -680,25 +687,24 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-8/%93)
-H - TP5/20G - %83 / 40 işlem - ADAY (8g/-8/%90)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-13/%60)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -710,11 +716,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.2</v>
+        <v>-2.8</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -728,37 +734,36 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+          <t>BIS 0, PHL +2, CNDL 0, XU030 -1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>M-TP5/20G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-3/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (4g/-3/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-3/%91)</t>
+          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-10/%93)
+H - TP5/20G - %83 / 40 işlem - ADAY (8g/-9/%90)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -770,11 +775,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-6.7</v>
+        <v>-3.5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -788,53 +793,53 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-16/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/-16/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (16g/-38/%5)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-5/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (4g/-4/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-4/%91)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -848,52 +853,53 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-8/%80)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-8/%91)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-17/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/-17/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (16g/-39/%5)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-5</v>
+        <v>1.4</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -907,8 +913,8 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -925,18 +931,18 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-14/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-14/%50)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-7/%80)
+H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -948,46 +954,105 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
+TOPLAM 0, ALMA</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>P-TP5/20G, P-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-13/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-13/%50)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>PGSUS</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>-0.6</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
 E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
@@ -996,74 +1061,14 @@
 Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%75)</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL -2, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (4g/-16/%94)
-R - TP5/10G - %60 / 103 işlem - ADAY (4g/-16/%45)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-16/%60)</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1079,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1088,8 +1093,8 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-8/%30)</t>
+          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-7/%35)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1132,7 +1137,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1146,8 +1151,8 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1170,8 +1175,8 @@
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/-3/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-3/%65)</t>
+E - TP5/20G - %79 / 42 işlem - ADAY (8g/-3/%64)
+Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-3/%60)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1188,110 +1193,111 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4/%58)
+I - TP5/20G - %84 / 49 işlem - ADAY (11g/-4/%79)
+Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="B14" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="G14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-4/%64)
 E - TP5/20G - %79 / 42 işlem - ADAY (3g/-4/%82)</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-6/%40)</t>
-        </is>
-      </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
@@ -1306,130 +1312,130 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-7/%40)</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>TSKB</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="B16" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+2/%100)
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+1/%100)
 Q - TP5/20G - %67 / 83 işlem - ADAY (15g/+1/%100)
 T - TP5/20G - %77 / 124 işlem - ADAY (11g/0/%100)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1
-TOPLAM 2, ALMA</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%75)
-R - TP5/20G - %80 / 95 işlem - ADAY (11g/-7/%50)</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1443,42 +1449,41 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4/%58)
-I - TP5/20G - %84 / 49 işlem - ADAY (11g/-4/%79)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-4/%70)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%65)
+R - TP5/20G - %80 / 95 işlem - ADAY (11g/-8/%50)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1494,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1503,38 +1508,37 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>Q-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 103 işlem - ADAY (8g/-12/%20)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-12/%50)</t>
+R - TP5/10G - %60 / 103 işlem - ADAY (8g/-13/%20)
+R - TP5/20G - %80 / 95 işlem - ADAY (8g/-13/%50)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 60 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1550,7 +1554,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1564,8 +1568,8 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 5, AL</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1587,7 +1591,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+1/%100)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+3/%100)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1608,7 +1612,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1622,8 +1626,8 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -1662,11 +1666,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1680,8 +1684,8 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1698,17 +1702,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1720,11 +1724,11 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1738,12 +1742,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
@@ -1756,33 +1760,33 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1796,8 +1800,8 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1807,25 +1811,24 @@
         <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-5/%40)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-5/%60)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1837,11 +1840,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1855,8 +1858,8 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -1873,34 +1876,34 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-5/%35)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-5/%60)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-6/%40)
+Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-6/%60)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1914,40 +1917,41 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-7/%20)
+R - TP5/20G - %80 / 95 işlem - ADAY (7g/-7/%50)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1972,8 +1976,8 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -1995,8 +1999,8 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-2/%25)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-2/%75)</t>
+          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-3/%20)
+R - TP5/20G - %80 / 95 işlem - ADAY (9g/-3/%70)</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2017,7 +2021,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2031,7 +2035,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
@@ -2075,7 +2079,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2089,8 +2093,8 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -2112,7 +2116,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-4/%65)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-5/%55)</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2133,7 +2137,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2147,12 +2151,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>1</v>
@@ -2170,7 +2174,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-6/%78)</t>
+          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-4/%78)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2180,7 +2184,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2195,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2205,7 +2209,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
@@ -2228,8 +2232,8 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/+1/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/+1/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2250,7 +2254,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-2.7</v>
+        <v>-0.7</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2264,8 +2268,8 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 5, AL</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 -1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -2287,8 +2291,8 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-3/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-3/%50)</t>
+          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-1/%80)
+P - TP5/10G - %82 / 45 işlem - ADAY (9g/-1/%50)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2309,7 +2313,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-4.2</v>
+        <v>-6</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2323,8 +2327,8 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 5, AL</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -2346,8 +2350,8 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-4/%93)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-4/%93)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-6/%93)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/-6/%93)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2368,7 +2372,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2382,8 +2386,8 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
@@ -2405,8 +2409,8 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/+1/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (2g/+1/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0/%100)
+H - TP5/20G - %83 / 40 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2427,7 +2431,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2441,8 +2445,8 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -2464,7 +2468,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%85)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%80)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2485,7 +2489,7 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2499,8 +2503,8 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
@@ -2522,7 +2526,7 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/0/%100)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/+1/%100)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2543,7 +2547,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2557,8 +2561,8 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
@@ -2601,7 +2605,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-1.6</v>
+        <v>-3.7</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2615,8 +2619,8 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
@@ -2638,8 +2642,8 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-6/%35)
-U - TP5/20G - %75 / 72 işlem - ADAY (6g/-7/%75)</t>
+          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-8/%35)
+U - TP5/20G - %75 / 72 işlem - ADAY (6g/-9/%75)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2660,7 +2664,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-0.1</v>
+        <v>1.3</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2674,8 +2678,8 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
@@ -2697,7 +2701,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-4/%70)</t>
+          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%85)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2718,7 +2722,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2732,8 +2736,8 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL -1, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS +1, PHL 0, CNDL -1, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
@@ -2777,7 +2781,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2791,8 +2795,8 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
@@ -2814,7 +2818,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-4/%25)</t>
+          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-3/%25)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2835,7 +2839,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -2849,8 +2853,8 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
+TOPLAM -3, ALMA</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
@@ -2872,8 +2876,8 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %64 / 133 işlem - ADAY (1g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+1/%100)</t>
+          <t>T - TP5/10G - %64 / 133 işlem - ADAY (1g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,6 +86,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,124 +540,117 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-2.4</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>BUGÜN</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
+          <t>L-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (9g/-17/%71)
-M - TP5/20G - %89 / 47 işlem - ONAY (9g/-17/%86)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 21 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+        <v>2.8</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 -1
-TOPLAM 0, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L-TP2/10G, M-TP2/10G, M-TP5/20G, M-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-M - TP2/10G - %98 / 59 işlem - ONAY (0g/0/%100)
-M - TP5/20G - %89 / 47 işlem - ONAY (4g/-11/%94)
-M - TP5/10G - %71 / 49 işlem - ADAY (0g/0/%100)
-Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 103 işlem - ADAY (4g/-11/%45)
-R - TP5/20G - %80 / 95 işlem - ADAY (4g/-11/%60)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-15/%69)
+M - TP5/20G - %90 / 49 işlem - ONAY (10g/-15/%82)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY M: TDA ve PFY-S birlikte dönüş teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -662,108 +661,108 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+        <v>0.9</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP2/10G, P-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (15g/-13/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (16g/-14/%60)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 37 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G, H-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %89 / 47 işlem - ONAY (6g/-10/%93)
-H - TP5/20G - %83 / 40 işlem - ADAY (8g/-9/%90)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (7g/-7/%80)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -775,205 +774,202 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>-3.5</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (3g/-5/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (4g/-4/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-4/%91)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-16/%80)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 13 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G, T-TP5/20G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-17/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/-17/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (16g/-39/%5)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (5g/-4/%89)
+L - TP5/10G - %79 / 42 işlem - ADAY (5g/-4/%89)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 47 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
 TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-7/%80)
-H - TP5/20G - %83 / 40 işlem - ADAY (6g/-7/%91)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-10/%93)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
+        <v>-1.9</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 -1
-TOPLAM 0, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
@@ -983,87 +979,83 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-13/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-13/%50)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+        <v>3.9</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-1/%95)
-E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)
-H - TP5/10G - %70 / 20 işlem - ADAY (1g/-1/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/-1/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (13g/-2/%75)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-6/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/-6/%91)</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -1075,53 +1067,55 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 95 işlem - ADAY (14g/-7/%35)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (12g/0/%100)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 58 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1133,15 +1127,15 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>ELDEKİ</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1151,37 +1145,36 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (5g/-3/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (8g/-3/%64)
-Q - TP5/20G - %67 / 83 işlem - ADAY (9g/-3/%60)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-5/%57)
+E - TP5/20G - %79 / 42 işlem - ADAY (4g/-5/%78)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -1193,55 +1186,53 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-4/%58)
-I - TP5/20G - %84 / 49 işlem - ADAY (11g/-4/%79)
-Q - TP5/20G - %67 / 83 işlem - ADAY (11g/-4/%65)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (12g/-9/%35)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1253,54 +1244,53 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-4/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (3g/-4/%82)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (8g/-6/%65)</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1312,268 +1302,268 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %85 / 54 işlem - ONAY (3g/-3/%64)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-7/%40)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)
+E - TP5/20G - %79 / 42 işlem - ADAY (14g/-2/%33)
+H - TP5/10G - %70 / 20 işlem - ADAY (2g/-1/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (2g/-1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-2/%55)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 28 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+        <v>-3.9</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (3g/+1/%100)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (11g/0/%100)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (3g/-22/%90)
+T - TP5/20G - %77 / 124 işlem - ADAY (17g/-42/%10)</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+        <v>1.1</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
         <v>51</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q-TP5/20G, R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (4g/-4/%65)
-R - TP5/20G - %80 / 95 işlem - ADAY (11g/-8/%50)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-2/%57)
+E - TP5/20G - %79 / 42 işlem - ADAY (16g/-6/%25)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %81 / 98 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %60 / 103 işlem - ADAY (8g/-13/%20)
-R - TP5/20G - %80 / 95 işlem - ADAY (8g/-13/%50)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (15g/-5/%35)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 60 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+        <v>0.9</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 0, ALMA</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1586,196 +1576,203 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (1g/+3/%100)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-3/%65)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-3/%58)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (9g/-15/%20)
+R - TP5/20G - %80 / 97 işlem - ADAY (9g/-15/%50)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-2/%67)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-4/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (9g/-3/%64)
+Q - TP5/20G - %68 / 68 işlem - ADAY (10g/-3/%60)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 -1
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1
 TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>U-TP2/10G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (9g/-7/%10)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-4/%55)
+I - TP5/20G - %84 / 49 işlem - ADAY (12g/-4/%79)
+Q - TP5/20G - %68 / 68 işlem - ADAY (12g/-4/%65)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1786,26 +1783,26 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -1823,130 +1820,130 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-5/%70)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-6/%75)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-6/%40)
-Q - TP5/20G - %67 / 83 işlem - ADAY (15g/-6/%60)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (0g/0/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (0g/0/%100)
+U - TP5/20G - %74 / 73 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 51 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (7g/-7/%20)
-R - TP5/20G - %80 / 95 işlem - ADAY (7g/-7/%50)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-3/%55)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -1958,112 +1955,112 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (9g/-3/%20)
-R - TP5/20G - %80 / 95 işlem - ADAY (9g/-3/%70)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (6g/-4/%70)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/-4/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-4/%55)</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -2075,58 +2072,63 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+        <v>1.2</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL -2, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP2/10G, M-TP5/20G, L-TP5/10G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (16g/-5/%55)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/+1/%100)
+M - TP5/20G - %90 / 49 işlem - ONAY (5g/-9/%93)
+L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (5g/-9/%50)
+R - TP5/20G - %80 / 97 işlem - ADAY (5g/-9/%60)</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 43 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2137,26 +2139,26 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+        <v>-2.7</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 -1
-TOPLAM -2, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>1</v>
@@ -2174,130 +2176,128 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %93 / 68 işlem - ONAY (7g/-4/%78)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (8g/-7/%76)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 -1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (1g/0/%100)</t>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>SKBNK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+        <v>1.3</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 -1
-TOPLAM 2, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
+TOPLAM 3, İZLE</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>P-TP5/20G, P-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %90 / 41 işlem - ONAY (9g/-1/%80)
-P - TP5/10G - %82 / 45 işlem - ADAY (9g/-1/%50)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -2309,59 +2309,58 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+        <v>1.2</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 -1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (1g/-6/%93)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/-6/%93)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-1/%80)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2372,50 +2371,49 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
+TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0/%100)
-H - TP5/20G - %83 / 40 işlem - ADAY (2g/0/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2427,53 +2425,54 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1
+TOPLAM 2, ALMA</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (5g/-4/%80)</t>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (7g/+2/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (7g/+2/%100)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2485,30 +2484,30 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
@@ -2526,12 +2525,12 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (9g/+1/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-4/%90)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2543,30 +2542,30 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+        <v>-0.9</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
@@ -2579,17 +2578,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (7g/-6/%67)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-4/%85)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -2601,89 +2600,88 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
+TOPLAM 1, ALMA</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %76 / 93 işlem - ADAY (7g/-8/%35)
-U - TP5/20G - %75 / 72 işlem - ADAY (6g/-9/%75)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (10g/0/%100)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
+TOPLAM 4, İZLE</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0</v>
@@ -2696,52 +2694,52 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %75 / 72 işlem - ADAY (4g/-3/%85)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-6/%64)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
+        <v>1.1</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL -1, XU030 -1
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
 TOPLAM -1, ALMA</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
@@ -2754,49 +2752,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %60 / 103 işlem - ADAY (6g/+2/%100)
-R - TP5/20G - %80 / 95 işlem - ADAY (6g/+2/%100)</t>
+          <t>U - TP2/10G - %78 / 67 işlem - ADAY (8g/-7/%24)
+U - TP5/20G - %74 / 73 işlem - ADAY (7g/-8/%75)</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 61 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 -1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1
+TOPLAM -2, ALMA</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
@@ -2806,93 +2804,35 @@
         <v>0</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %67 / 83 işlem - ADAY (19g/-3/%25)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 63 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ISCTR</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 -1
-TOPLAM -3, ALMA</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %64 / 133 işlem - ADAY (1g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 69 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M41"/>
+  <autoFilter ref="A1:M40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -69,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,6 +86,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,14 +452,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -534,149 +540,147 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>BUGÜN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>KONTR</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-15/%69)
 M - TP5/20G - %90 / 49 işlem - ONAY (10g/-15/%82)</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASTOR</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, P-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (16g/-15/%60)
-L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 5 - 7/5 , SHORT - 5 - 6/6 , -</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>1</v>
@@ -689,17 +693,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (7g/-7/%80)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-12/%80)</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -711,30 +715,30 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+        <v>-0.1</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , ALT -  - 15/2 , -</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
@@ -752,7 +756,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-15/%80)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (16g/-15/%60)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -762,652 +766,653 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 31/3 , SHORT - 139 - 22/10 , LONG - 1 - 9/1</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-2/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (9g/-2/%64)
+Q - TP5/20G - %68 / 68 işlem - ADAY (10g/-2/%60)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 45 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TAVHL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 55 - 14/6 , SHORT - 55 - 13/4 , LONG - 2 - 9/1</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (7g/-7/%80)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>KLRHO</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B8" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 65 - 12/8 , SHORT - 65 - 13/7 , -</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-3/%100)
 L - TP5/20G - %91 / 44 işlem - ONAY (5g/-3/%89)
 L - TP5/10G - %79 / 42 işlem - ADAY (5g/-3/%89)</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>M-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-11/%93)</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ISMEN</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>İZLE</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 15/2 , ALT -  - 14/1 , -</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (12g/-1/%70)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-11/%93)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ISMEN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 1 - 1/8 , ALT -  - 22/8 , LONG - 8 - 9/7</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+LONG - 27 - 5/5 , LONG - 25 - 5/5 , LONG - 25 - 6/4</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (12g/0/%70)</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/1 , ALT -  - 12/1 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (12g/-8/%35)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 12/1</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (8g/-7/%65)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PGSUS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+LONG - 13 - 7/3 , LONG - 26 - 7/5 , LONG - 10 - 10/3</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0/%89)
+E - TP5/20G - %79 / 42 işlem - ADAY (14g/-2/%33)
+H - TP5/10G - %70 / 20 işlem - ADAY (2g/0/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (2g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-2/%55)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>HEKTS</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 4, İZLE</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="n">
+      <c r="B15" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 44/6 , ALT -  - 30/10 , ALT -  - 22/8</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-4/%57)
 E - TP5/20G - %79 / 42 işlem - ADAY (4g/-4/%78)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (12g/-8/%35)</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MAVI</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (8g/-7/%65)</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PGSUS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)
-E - TP5/20G - %79 / 42 işlem - ADAY (14g/-2/%33)
-H - TP5/10G - %70 / 20 işlem - ADAY (2g/-1/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (2g/-1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-2/%55)</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SISE</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 4, İZLE</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 26/3 , ALT -  - 27/4 , ALT -  - 28/9</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-2/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (9g/-2/%64)
-Q - TP5/20G - %68 / 68 işlem - ADAY (10g/-2/%60)</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MGROS</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-2/%57)
 E - TP5/20G - %79 / 42 işlem - ADAY (16g/-5/%25)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (15g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1419,26 +1424,26 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -1460,7 +1465,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-1/%65)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (15g/-4/%35)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1477,26 +1482,26 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+        <v>2.7</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 34/1 , LONG - 1 - 33/1 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -1506,25 +1511,24 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (3g/-15/%90)
-T - TP5/20G - %77 / 124 işlem - ADAY (17g/-37/%10)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-1/%65)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -1540,22 +1544,22 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1
-TOPLAM -2, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 13/2 , ALT -  - 13/2 , LONG - 3 - 17/1</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1600,86 +1604,84 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+        <v>-1.6</v>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 6 - 22/10 , ALT -  - 42/5 , UST -  - 0/10</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (0g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (0g/0/%100)
-U - TP5/20G - %74 / 73 işlem - ADAY (2g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 52 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 14 - 20/2 , ALT -  - 21/3 , LONG - 26 - 8/2</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -1692,17 +1694,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-3/%55)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-6/%75)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -1714,26 +1716,26 @@
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+        <v>1.7</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 1 - 34/1 , LONG - 1 - 34/1 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -1755,7 +1757,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2/%55)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1776,22 +1778,22 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
+        <v>1.7</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1813,8 +1815,8 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (9g/-15/%20)
-R - TP5/20G - %80 / 97 işlem - ADAY (9g/-15/%50)</t>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (9g/-14/%20)
+R - TP5/20G - %80 / 97 işlem - ADAY (9g/-14/%50)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1835,22 +1837,22 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+        <v>2.1</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 12/0 , SHORT - 57 - 7/5 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -1890,30 +1892,30 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
@@ -1926,17 +1928,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-6/%75)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -1954,20 +1956,20 @@
       <c r="B26" s="2" t="n">
         <v>1.4</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1
-TOPLAM 4, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 2 - 15/6 , SHORT - 33 - 14/10 , -</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -2014,22 +2016,22 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 13 - 13/4 , SHORT - 7 - 8/8 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -2051,7 +2053,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (8g/-5/%76)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (8g/-3/%76)</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2072,22 +2074,22 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , LONG - 75 - 11/9 , ALT -  - 30/7</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -2130,22 +2132,22 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+        <v>-0.3</v>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+UST -  - 2/11 , UST -  - 1/10 , SHORT - 5 - 3/7</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -2167,7 +2169,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-3/%80)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-2/%80)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2188,26 +2190,26 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 6 - 7/3 , SHORT - 6 - 7/3 , SHORT - 6 - 7/3</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>1</v>
@@ -2225,7 +2227,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%87)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2235,7 +2237,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2246,26 +2248,26 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>1</v>
@@ -2283,7 +2285,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/+1/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0/%89)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2293,7 +2295,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
@@ -2304,22 +2306,22 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+        <v>-0.5</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1
-TOPLAM 3, İZLE</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 12 - 1/9 , SHORT - 12 - 1/9 , SHORT - 12 - 1/8</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -2363,22 +2365,22 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
+        <v>-1.2</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 37 - 14/10 , SHORT - 5 - 3/7 , SHORT - 5 - 3/7</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
@@ -2400,7 +2402,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-4/%85)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-4/%80)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2421,22 +2423,22 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 26 - 7/9 , LONG - 26 - 7/9 , LONG - 24 - 4/8</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -2479,22 +2481,22 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1
-TOPLAM 2, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 4 - 8/4 , LONG - 1 - 10/0 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
@@ -2533,171 +2535,171 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+LONG - 26 - 3/6 , LONG - 10 - 11/6 , LONG - 11 - 9/7</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-3/%90)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 5 - 4/6 , SHORT - 5 - 4/6 , SHORT - 5 - 4/5</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-3/%90)</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>OYAKC</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="B38" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1
-TOPLAM -1, ALMA</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="n">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 8/2 , SHORT - 6 - 8/3 , SHORT - 5 - 6/6</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5" t="n">
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="I38" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>U - TP2/10G - %78 / 67 işlem - ADAY (8g/-6/%24)
 U - TP5/20G - %74 / 73 işlem - ADAY (7g/-7/%75)</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ISCTR</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1
-TOPLAM -2, ALMA</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (2g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -2713,22 +2715,22 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
+        <v>5.6</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1
-TOPLAM 1, ALMA</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 21/3 , ALT -  - 21/3 , -</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
@@ -2765,8 +2767,67 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 49/34 , ALT -  - 56/33 , ALT -  - 49/34</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (3g/-11/%90)
+T - TP5/20G - %77 / 124 işlem - ADAY (17g/-34/%10)</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M39"/>
+  <autoFilter ref="A1:M40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +44,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,7 +81,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -540,53 +534,54 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>KONTR</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>BUGÜN</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (0g/0/%100)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-15/%69)
+M - TP5/20G - %90 / 49 işlem - ONAY (10g/-15/%82)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Bugün 1 sistem/profil yeni giriş veriyor; TP5/20G için 1 ONAY var; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
@@ -598,59 +593,60 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KONTR</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 14/1 , ALT -  - 14/1 , -</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>K-TP5/20G, M-TP5/20G</t>
+          <t>L-TP2/10G, P-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-15/%69)
-M - TP5/20G - %90 / 49 işlem - ONAY (10g/-15/%82)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (16g/-15/%60)
+L - TP5/10G - %79 / 42 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -661,14 +657,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -676,7 +672,7 @@
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 5 - 7/5 , SHORT - 5 - 6/6 , -</t>
+SHORT - 5 - 7/5 , SHORT - 5 - 7/5 , -</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -715,26 +711,26 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+        <v>0.7</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 15/2 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/1 , LONG - 1 - 13/0 , -</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -751,17 +747,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>M-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (16g/-15/%60)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-10/%93)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -779,12 +775,12 @@
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -834,53 +830,55 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 55 - 14/6 , SHORT - 55 - 13/4 , LONG - 2 - 9/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 65 - 13/8 , SHORT - 65 - 14/7 , -</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
         <v>62</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (7g/-7/%80)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (5g/-4/%89)
+L - TP5/10G - %79 / 42 işlem - ADAY (5g/-4/%89)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -892,90 +890,88 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
+        <v>-2.6</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 65 - 12/8 , SHORT - 65 - 13/7 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 1 - 2/7 , ALT -  - 23/9 , LONG - 8 - 11/6</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (4g/-3/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (5g/-3/%89)
-L - TP5/10G - %79 / 42 işlem - ADAY (5g/-3/%89)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+        <v>0.8</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 15/2 , ALT -  - 14/1 , -</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+SHORT - 55 - 13/8 , SHORT - 55 - 11/5 , LONG - 2 - 8/3</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>1</v>
@@ -988,17 +984,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-11/%93)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (7g/-6/%80)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1010,76 +1006,78 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>İZLEME</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>İZLE</t>
+        <v>-0.6</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 1 - 1/8 , ALT -  - 22/8 , LONG - 8 - 9/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 27 - 6/4 , LONG - 25 - 6/4 , LONG - 25 - 6/4</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/0/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (12g/-1/%70)</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+        <v>-0.2</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1087,36 +1085,34 @@
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 27 - 5/5 , LONG - 25 - 5/5 , LONG - 25 - 6/4</t>
+ALT -  - 11/0 , ALT -  - 12/1 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (4g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (12g/0/%70)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (12g/-8/%35)</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1128,15 +1124,15 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>ELDEKİ</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1147,7 +1143,7 @@
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , ALT -  - 12/1 , ALT -  - 12/2</t>
+-</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (12g/-8/%35)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (15g/-5/%35)</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1190,14 +1186,14 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1205,7 +1201,7 @@
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 12/1</t>
+ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (8g/-7/%65)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (8g/-6/%65)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1248,14 +1244,14 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1310,14 +1306,14 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1325,7 +1321,7 @@
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 44/6 , ALT -  - 30/10 , ALT -  - 22/8</t>
+ALT -  - 43/6 , ALT -  - 29/10 , ALT -  - 21/8</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1347,8 +1343,8 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-4/%57)
-E - TP5/20G - %79 / 42 işlem - ADAY (4g/-4/%78)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-3/%57)
+E - TP5/20G - %79 / 42 işlem - ADAY (4g/-3/%78)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1369,14 +1365,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+        <v>2.1</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -1384,7 +1380,7 @@
       <c r="E16" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 26/3 , ALT -  - 27/4 , ALT -  - 28/9</t>
+ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 27/9</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -1406,7 +1402,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-2/%57)
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (4g/-1/%57)
 E - TP5/20G - %79 / 42 işlem - ADAY (16g/-5/%25)</t>
         </is>
       </c>
@@ -1424,734 +1420,730 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+        <v>2.7</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 34/1 , LONG - 1 - 33/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-1/%65)</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 12/1 , ALT -  - 12/1 , LONG - 3 - 16/2</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-4/%55)
+I - TP5/20G - %84 / 49 işlem - ADAY (12g/-4/%79)
+Q - TP5/20G - %68 / 68 işlem - ADAY (12g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 6 - 23/9 , ALT -  - 43/6 , SHORT - 1 - 0/9</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (2g/-1/%80)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 14 - 17/4 , ALT -  - 18/1 , LONG - 26 - 6/4</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-3/%85)</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 1 - 33/2 , LONG - 1 - 33/2 , LONG - 1 - 8/2</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-1/%55)</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (9g/-13/%25)
+R - TP5/20G - %80 / 97 işlem - ADAY (9g/-13/%50)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 13/0 , SHORT - 57 - 7/5 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/-4/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-4/%55)</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (15g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="F24" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-1/%64)</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SASA</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 34/1 , LONG - 1 - 33/1 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-1/%65)</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 13 - 13/4 , SHORT - 7 - 7/8 , LONG - 1 - 9/1</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (8g/-3/%76)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , LONG - 3 - 17/1</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-5/%55)
-I - TP5/20G - %84 / 49 işlem - ADAY (12g/-5/%79)
-Q - TP5/20G - %68 / 68 işlem - ADAY (12g/-5/%65)</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 36/1 , LONG - 75 - 11/9 , ALT -  - 30/7</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-3/%40)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+UST -  - 1/11 , UST -  - 1/10 , SHORT - 5 - 3/7</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-2/%80)</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 6 - 22/10 , ALT -  - 42/5 , UST -  - 0/10</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (2g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+SHORT - 6 - 7/3 , SHORT - 6 - 7/3 , SHORT - 6 - 7/3</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SKBNK</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 14 - 20/2 , ALT -  - 21/3 , LONG - 26 - 8/2</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-6/%75)</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-LONG - 1 - 34/1 , LONG - 1 - 34/1 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (12g/-2/%55)</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (9g/-14/%20)
-R - TP5/20G - %80 / 97 işlem - ADAY (9g/-14/%50)</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/0 , SHORT - 57 - 7/5 , ALT -  - 12/1</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/-3/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-3/%55)</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-2/%64)</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 2 - 15/6 , SHORT - 33 - 14/10 , -</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-M - TP5/20G - %90 / 49 işlem - ONAY (5g/-9/%93)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (5g/-9/%50)
-R - TP5/20G - %80 / 97 işlem - ADAY (5g/-9/%60)</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TKFEN</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 13 - 13/4 , SHORT - 7 - 8/8 , LONG - 1 - 10/1</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>K-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (8g/-3/%76)</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>FROTO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 36/1 , LONG - 75 - 11/9 , ALT -  - 30/7</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-3/%40)</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-UST -  - 2/11 , UST -  - 1/10 , SHORT - 5 - 3/7</t>
-        </is>
-      </c>
       <c r="F29" s="5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>1</v>
@@ -2164,48 +2156,48 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (10g/-2/%80)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
+        <v>3.5</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 6 - 7/3 , SHORT - 6 - 7/3 , SHORT - 6 - 7/3</t>
+          <t>BIS +2, PHL +2, CNDL +1, XU030 +1, TOPLAM 6, AL
+LONG - 2 - 13/8 , SHORT - 33 - 13/11 , -</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -2215,141 +2207,142 @@
         <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%87)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (5g/-7/%93)
+R - TP5/10G - %62 / 63 işlem - ADAY (5g/-7/%50)
+R - TP5/20G - %80 / 97 işlem - ADAY (5g/-7/%60)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
+        <v>-0.7</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 37 - 13/11 , SHORT - 5 - 3/7 , SHORT - 5 - 3/7</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/0/%89)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-4/%85)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
+        <v>-0.4</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 12 - 1/9 , SHORT - 12 - 1/9 , SHORT - 12 - 1/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 26 - 7/9 , LONG - 26 - 7/9 , LONG - 24 - 4/7</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (7g/+2/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (7g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (10g/0/%100)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -2361,30 +2354,30 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
+        <v>1.6</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 37 - 14/10 , SHORT - 5 - 3/7 , SHORT - 5 - 3/7</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 4 - 8/4 , LONG - 1 - 10/1 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -2397,17 +2390,17 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/-4/%80)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-4/%64)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -2419,111 +2412,113 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
+        <v>0.3</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 26 - 7/9 , LONG - 26 - 7/9 , LONG - 24 - 4/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 12 - 0/9 , SHORT - 12 - 0/9 , SHORT - 12 - 1/9</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (10g/0/%100)</t>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (7g/+3/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (7g/+3/%100)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
+        <v>0.5</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-LONG - 4 - 8/4 , LONG - 1 - 10/0 , ALT -  - 12/1</t>
+          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
+LONG - 26 - 3/6 , LONG - 10 - 11/6 , LONG - 11 - 9/7</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (8g/-5/%64)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2535,77 +2530,76 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
+        <v>1.8</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-LONG - 26 - 3/6 , LONG - 10 - 11/6 , LONG - 11 - 9/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 5 - 3/6 , SHORT - 5 - 3/6 , LONG - 40 - 7/9</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (2g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (2g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-2/%90)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
+        <v>2.4</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
@@ -2613,34 +2607,35 @@
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 5 - 4/6 , SHORT - 5 - 4/6 , SHORT - 5 - 4/5</t>
+LONG - 1 - 8/2 , SHORT - 6 - 7/3 , SHORT - 5 - 6/6</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-3/%90)</t>
+          <t>U - TP2/10G - %78 / 67 işlem - ADAY (8g/-6/%24)
+U - TP5/20G - %74 / 73 işlem - ADAY (7g/-7/%75)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -2652,182 +2647,123 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
+        <v>6.5</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 8/2 , SHORT - 6 - 8/3 , SHORT - 5 - 6/6</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 20/2 , ALT -  - 20/2 , -</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %78 / 67 işlem - ADAY (8g/-6/%24)
-U - TP5/20G - %74 / 73 işlem - ADAY (7g/-7/%75)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-3/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/-3/%91)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>ELDEKİ</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 21/3 , ALT -  - 21/3 , -</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 48/34 , ALT -  - 56/33 , ALT -  - 48/34</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (2g/-4/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/-4/%91)</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 49/34 , ALT -  - 56/33 , ALT -  - 49/34</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>L - TP5/10G - %79 / 42 işlem - ADAY (3g/-11/%90)
 T - TP5/20G - %77 / 124 işlem - ADAY (17g/-34/%10)</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>Günlük artış %5 veya üzeri; alınmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M40"/>
+  <autoFilter ref="A1:M39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HISSELER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,6 +448,2694 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="85" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Düne_Göre_%</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Yarın_Alım</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Puan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Onaylı_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Aday_Sistem_Sayısı</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Toplam_Öneren_Sistem</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sistem_Kodları</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Sistem_Detayı</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Neden</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Engel_Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KONTR</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>K-TP5/20G, M-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (11g/-17/%64)
+M - TP5/20G - %90 / 49 işlem - ONAY (11g/-17/%82)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASTOR</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 1 - 12/1 , LONG - 1 - 12/1 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, P-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (17g/-13/%60)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 6 - 8/4 , SHORT - 6 - 7/5 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-12/%71)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
+ALT -  - 13/1 , LONG - 2 - 12/0 , -</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>M-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (8g/-10/%92)</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SISE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 2 - 34/1 , SHORT - 140 - 21/10 , LONG - 2 - 9/2</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (7g/-2/%45)
+E - TP5/20G - %79 / 42 işlem - ADAY (10g/-2/%58)
+Q - TP5/20G - %68 / 68 işlem - ADAY (11g/-2/%65)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 45 hisse / 50 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HEKTS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL +1, XU030 0, TOPLAM 5, AL
+ALT -  - 41/5 , ALT -  - 27/8 , ALT -  - 20/6</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-3/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/-3/%76)
+Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TAVHL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 56 - 14/7 , SHORT - 56 - 12/4 , LONG - 3 - 8/2</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-7/%80)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 66 - 12/9 , SHORT - 66 - 13/8 , -</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (6g/-4/%82)
+L - TP5/10G - %79 / 42 işlem - ADAY (6g/-4/%78)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 18/1 , ALT -  - 18/1 , -</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-4/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (3g/-4/%90)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 50/36 , LONG - 2 - 30/4 , LONG - 1 - 9/2</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+1/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PGSUS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 0, TOPLAM 1, ALMA
+LONG - 14 - 7/3 , LONG - 27 - 7/5 , LONG - 11 - 10/3</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-2/%40)
+H - TP5/10G - %70 / 20 işlem - ADAY (3g/-1/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (3g/-1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-2/%47)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
+LONG - 28 - 5/5 , LONG - 26 - 6/4 , LONG - 26 - 6/4</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/0/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (13g/-1/%70)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PSGYO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (10g/-13/%40)</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ISMEN</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
+LONG - 5 - 29/4 , SHORT - 2 - 3/7 , LONG - 9 - 11/6</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%95)
+H - TP5/10G - %70 / 20 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MGROS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 27/8</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>E-TP2/10G, E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (17g/-5/%25)</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ANSGR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
+ALT -  - 11/0 , ALT -  - 12/1 , ALT -  - 12/2</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (13g/-9/%30)</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MAVI</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-6/%60)</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+ALT -  - 41/28 , ALT -  - 61/19 , ALT -  - 41/28</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-7/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (18g/-31/%5)</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CCOLA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
+ALT -  - 11/1 , ALT -  - 11/1 , LONG - 4 - 15/2</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-3/%55)
+I - TP5/20G - %84 / 49 işlem - ADAY (13g/-3/%77)
+Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-3/%60)</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-4/%35)</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SASA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 2 - 34/1 , LONG - 2 - 33/2 , ALT -  - 11/0</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-1/%65)</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BRYAT</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 2 - 8/2 , ALT -  - 30/11 , LONG - 27 - 20/5</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CWENE</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 13/2 , ALT -  - 13/2 , -</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/0/%93)</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+ALT -  - 30/3 , ALT -  - 14/1 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 2 - 33/2 , LONG - 2 - 33/2 , LONG - 2 - 8/2</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 17 - 18/8 , ALT -  - 19/6 , ALT -  - 18/5</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
+LONG - 7 - 22/10 , ALT -  - 43/6 , SHORT - 2 - 1/9</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+LONG - 15 - 17/5 , ALT -  - 18/1 , LONG - 27 - 6/5</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-3/%90)</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+ALT -  - 13/1 , SHORT - 58 - 8/4 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+SHORT - 14 - 12/5 , SHORT - 8 - 8/8 , LONG - 2 - 9/1</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-3/%71)</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 1 - 33/2 , LONG - 76 - 9/11 , ALT -  - 27/4</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-1/%25)</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 0, TOPLAM 1, ALMA
+ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/1</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-6/%82)</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SKBNK</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
+UST -  - 1/11 , UST -  - 1/10 , SHORT - 6 - 3/6</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-3/%71)</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EFOR</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 3 - 13/8 , SHORT - 34 - 13/11 , -</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (6g/-7/%93)
+R - TP5/10G - %62 / 63 işlem - ADAY (6g/-7/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (6g/-7/%60)</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TRALT</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+SHORT - 5 - 5/5 , LONG - 4 - 7/3 , SHORT - 6 - 7/3</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%100)</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 62 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ENJSA</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 38 - 14/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-4/%80)</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SAHOL</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
+LONG - 27 - 7/9 , LONG - 27 - 7/9 , LONG - 25 - 4/8</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (11g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TCELL</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 0, TOPLAM 1, ALMA
+LONG - 5 - 7/5 , LONG - 2 - 10/1 , ALT -  - 11/1</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-4/%64)</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>OYAKC</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL +1, XU030 0, TOPLAM 0, ALMA
+LONG - 2 - 7/3 , SHORT - 7 - 7/3 , SHORT - 6 - 6/6</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>U-TP2/10G, U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>U - TP2/10G - %78 / 67 işlem - ADAY (9g/-5/%7)
+U - TP5/20G - %74 / 73 işlem - ADAY (8g/-6/%80)</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 13 - 1/9 , SHORT - 13 - 1/9 , SHORT - 13 - 1/9</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+3/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (8g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ISCTR</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
+LONG - 27 - 4/6 , LONG - 11 - 10/6 , LONG - 12 - 9/7</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>T-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DOHOL</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , LONG - 41 - 7/9</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M45"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -613,8 +613,8 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 1 - 12/1 , LONG - 1 - 12/1 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 11/1 , LONG - 1 - 11/1 , -</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -624,26 +624,28 @@
         <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L-TP2/10G, P-TP5/20G, L-TP5/10G</t>
+          <t>L-TP2/10G, P-TP5/20G, L-TP5/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (17g/-13/%60)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)</t>
+P - TP5/20G - %91 / 43 işlem - ONAY (17g/-12/%60)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/+3/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -659,7 +661,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.6</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -673,8 +675,8 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 6 - 8/4 , SHORT - 6 - 7/5 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 6 - 8/5 , SHORT - 6 - 7/5 , -</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -713,11 +715,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.3</v>
+        <v>1.9</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -731,51 +733,53 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 0, TOPLAM 4, İZLE
-ALT -  - 13/1 , LONG - 2 - 12/0 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 41/4 , ALT -  - 27/8 , ALT -  - 19/6</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (8g/-10/%92)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1/%76)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 27 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2</v>
+        <v>-4.9</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -789,38 +793,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 2 - 34/1 , SHORT - 140 - 21/10 , LONG - 2 - 9/2</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 13/0</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G, R-TP2/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (7g/-2/%45)
-E - TP5/20G - %79 / 42 işlem - ADAY (10g/-2/%58)
-Q - TP5/20G - %68 / 68 işlem - ADAY (11g/-2/%65)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-5/%82)</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 45 hisse / 50 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -832,11 +833,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -850,8 +851,8 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL +1, XU030 0, TOPLAM 5, AL
-ALT -  - 41/5 , ALT -  - 27/8 , ALT -  - 20/6</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 56 - 14/7 , SHORT - 56 - 12/5 , LONG - 3 - 8/2</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -861,46 +862,40 @@
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-3/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/-3/%76)
-Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-6/%80)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 5 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>-1.1</v>
+        <v>0.6</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -914,51 +909,53 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 56 - 14/7 , SHORT - 56 - 12/4 , LONG - 3 - 8/2</t>
+          <t>BIS +2, PHL +2, CNDL +1, XU030 +1, TOPLAM 6, AL
+SHORT - 66 - 12/9 , SHORT - 66 - 13/8 , -</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-7/%80)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-3/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (6g/-3/%82)
+L - TP5/10G - %79 / 42 işlem - ADAY (6g/-3/%78)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -972,37 +969,35 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 66 - 12/9 , SHORT - 66 - 13/8 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 38/2 , ALT -  - 26/12 , LONG - 7 - 13/4</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
         <v>59</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-4/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (6g/-4/%82)
-L - TP5/10G - %79 / 42 işlem - ADAY (6g/-4/%78)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-2/%95)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1014,11 +1009,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1032,233 +1027,233 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 18/1 , ALT -  - 18/1 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 51/37 , LONG - 2 - 30/4 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>L-TP5/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PGSUS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+LONG - 14 - 8/3 , LONG - 27 - 7/5 , LONG - 5 - 10/2</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%87)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-2/%40)
+H - TP5/10G - %70 / 20 işlem - ADAY (3g/0/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (3g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-2/%47)</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 17 - 19/7 , ALT -  - 20/7 , ALT -  - 19/6</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, Q-TP2/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+Q - TP2/10G - %82 / 103 işlem - ADAY (1g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 18/1 , ALT -  - 18/1 , -</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-4/%91)
 L - TP5/10G - %79 / 42 işlem - ADAY (3g/-4/%90)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BTCIM</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 50/36 , LONG - 2 - 30/4 , LONG - 1 - 9/2</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>L-TP5/10G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+1/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PGSUS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 0, TOPLAM 1, ALMA
-LONG - 14 - 7/3 , LONG - 27 - 7/5 , LONG - 11 - 10/3</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-2/%40)
-H - TP5/10G - %70 / 20 işlem - ADAY (3g/-1/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (3g/-1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-2/%47)</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
-LONG - 28 - 5/5 , LONG - 26 - 6/4 , LONG - 26 - 6/4</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (13g/-1/%70)</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1272,38 +1267,36 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 14/1 , ALT -  - 13/0 , -</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
+          <t>M-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (10g/-13/%40)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (8g/-10/%92)
+I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -1315,11 +1308,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1333,8 +1326,8 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
-LONG - 5 - 29/4 , SHORT - 2 - 3/7 , LONG - 9 - 11/6</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 25/3 , ALT -  - 26/3 , ALT -  - 28/9</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1344,42 +1337,41 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/0/%95)
-H - TP5/10G - %70 / 20 işlem - ADAY (0g/0/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (17g/-5/%25)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1393,36 +1385,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 27/8</t>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 12/1 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (17g/-5/%25)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (13g/-9/%30)</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1434,11 +1425,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-0.8</v>
+        <v>-2.7</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1452,8 +1443,8 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
-ALT -  - 11/0 , ALT -  - 12/1 , ALT -  - 12/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -1475,7 +1466,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (13g/-9/%30)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-7/%35)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1496,7 +1487,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1510,8 +1501,8 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -1533,7 +1524,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-6/%60)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-7/%60)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1550,11 +1541,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1568,8 +1559,8 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-ALT -  - 41/28 , ALT -  - 61/19 , ALT -  - 41/28</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1579,25 +1570,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-7/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (18g/-31/%5)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-12/%40)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1609,11 +1599,11 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>SASA</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1627,37 +1617,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 0, TOPLAM -1, ALMA
-ALT -  - 11/1 , ALT -  - 11/1 , LONG - 4 - 15/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 33/2 , LONG - 2 - 32/3 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-3/%55)
-I - TP5/20G - %84 / 49 işlem - ADAY (13g/-3/%77)
-Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-3/%60)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/0/%100)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -1669,11 +1657,11 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1687,51 +1675,53 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
--</t>
+          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 13/2 , ALT -  - 13/2 , LONG - 3 - 16/1</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-4/%35)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4/%55)
+I - TP5/20G - %84 / 49 işlem - ADAY (13g/-4/%77)
+Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-4/%60)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1745,35 +1735,37 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 2 - 34/1 , LONG - 2 - 33/2 , ALT -  - 11/0</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 28 - 5/5 , LONG - 26 - 5/5 , LONG - 26 - 6/4</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-1/%65)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (13g/0/%100)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -1785,11 +1777,11 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1803,35 +1795,37 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 2 - 8/2 , ALT -  - 30/11 , LONG - 27 - 20/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 32/3 , SHORT - 140 - 19/12 , LONG - 2 - 7/3</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>R-TP2/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (7g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (10g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (11g/+1/%100)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -1843,11 +1837,11 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1861,12 +1855,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 10/1 , ALT -  - 31/12 , LONG - 27 - 22/4</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
@@ -1879,33 +1873,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>L-TP5/10G</t>
+          <t>R-TP2/10G</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/0/%93)</t>
+          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1919,8 +1913,8 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-ALT -  - 30/3 , ALT -  - 14/1 , LONG - 1 - 10/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 13/2 , ALT -  - 13/2 , -</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -1930,83 +1924,83 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 32/3 , ALT -  - 15/2 , LONG - 1 - 10/0</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="I26" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Q-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
 Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 2 - 33/2 , LONG - 2 - 33/2 , LONG - 2 - 8/2</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-2/%55)</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2018,11 +2012,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2036,8 +2030,8 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 26/3 , LONG - 2 - 31/3 , LONG - 2 - 7/3</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -2059,7 +2053,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0/%100)</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2076,11 +2070,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2094,52 +2088,51 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 17 - 18/8 , ALT -  - 19/6 , ALT -  - 18/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2153,40 +2146,41 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 0, TOPLAM -3, ALMA
-LONG - 7 - 22/10 , ALT -  - 43/6 , SHORT - 2 - 1/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 14/1 , SHORT - 58 - 8/4 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -2211,8 +2205,8 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-LONG - 15 - 17/5 , ALT -  - 18/1 , LONG - 27 - 6/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 15 - 18/4 , ALT -  - 19/1 , LONG - 27 - 6/4</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -2251,11 +2245,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>-0.5</v>
+        <v>1.1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2269,41 +2263,44 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-ALT -  - 13/1 , SHORT - 58 - 8/4 , ALT -  - 13/2</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 3 - 12/9 , SHORT - 34 - 11/12 , -</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>L-TP2/10G, M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+M - TP5/20G - %90 / 49 işlem - ONAY (6g/-6/%93)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (6g/-6/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (6g/-6/%60)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2311,7 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.2</v>
+        <v>-1</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2328,8 +2325,8 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-SHORT - 14 - 12/5 , SHORT - 8 - 8/8 , LONG - 2 - 9/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 14 - 14/3 , SHORT - 8 - 10/7 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -2351,7 +2348,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-3/%71)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-4/%71)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2372,7 +2369,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2386,8 +2383,8 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 1 - 33/2 , LONG - 76 - 9/11 , ALT -  - 27/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 33/2 , LONG - 76 - 9/11 , ALT -  - 28/5</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
@@ -2426,11 +2423,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>SKBNK</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>-5.8</v>
+        <v>0</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2444,8 +2441,8 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 0, TOPLAM 1, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -2467,7 +2464,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-6/%82)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2484,11 +2481,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2502,8 +2499,8 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
--</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 1 - 0/9 , SHORT - 1 - 1/9 , SHORT - 6 - 5/5</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
@@ -2520,33 +2517,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-3/%71)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2560,51 +2557,53 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 0, TOPLAM 0, ALMA
-UST -  - 1/11 , UST -  - 1/10 , SHORT - 6 - 3/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 5 - 5/5 , LONG - 4 - 8/3 , SHORT - 6 - 8/3</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, Q-TP2/10G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-3/%71)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
+Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%100)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2618,53 +2617,54 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 3 - 13/8 , SHORT - 34 - 13/11 , -</t>
+          <t>BIS -1, PHL 0, CNDL +1, XU030 +1, TOPLAM 1, ALMA
+LONG - 2 - 8/2 , SHORT - 8 - 8/3 , SHORT - 6 - 7/6</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (6g/-7/%93)
-R - TP5/10G - %62 / 63 işlem - ADAY (6g/-7/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (6g/-7/%60)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
+U - TP2/10G - %78 / 67 işlem - ADAY (9g/-5/%7)
+U - TP5/20G - %74 / 73 işlem - ADAY (8g/-6/%80)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>-1.2</v>
+        <v>3.3</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2678,35 +2678,36 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-SHORT - 5 - 5/5 , LONG - 4 - 7/3 , SHORT - 6 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 43/30 , ALT -  - 63/21 , ALT -  - 43/30</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Q-TP2/10G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%100)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-8/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (18g/-32/%5)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 62 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -2722,7 +2723,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2736,8 +2737,8 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 38 - 14/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 38 - 15/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
@@ -2780,7 +2781,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2794,8 +2795,8 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 0, TOPLAM 2, ALMA
-LONG - 27 - 7/9 , LONG - 27 - 7/9 , LONG - 25 - 4/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 27 - 7/9 , LONG - 27 - 7/9 , LONG - 25 - 4/7</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
@@ -2838,7 +2839,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -2852,8 +2853,8 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 0, TOPLAM 1, ALMA
-LONG - 5 - 7/5 , LONG - 2 - 10/1 , ALT -  - 11/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 5 - 7/5 , LONG - 1 - 9/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
@@ -2892,11 +2893,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -2910,8 +2911,8 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL +1, XU030 0, TOPLAM 0, ALMA
-LONG - 2 - 7/3 , SHORT - 7 - 7/3 , SHORT - 6 - 6/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 13 - 1/8 , SHORT - 13 - 1/8 , SHORT - 13 - 2/8</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
@@ -2928,30 +2929,30 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>U - TP2/10G - %78 / 67 işlem - ADAY (9g/-5/%7)
-U - TP5/20G - %74 / 73 işlem - ADAY (8g/-6/%80)</t>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+3/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (8g/+3/%100)</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2969,12 +2970,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 13 - 1/9 , SHORT - 13 - 1/9 , SHORT - 13 - 1/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 27 - 4/6 , LONG - 9 - 11/5 , LONG - 12 - 10/7</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0</v>
@@ -2987,34 +2988,34 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+3/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (8g/+3/%100)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
@@ -3028,52 +3029,51 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA
-LONG - 27 - 4/6 , LONG - 11 - 10/6 , LONG - 12 - 9/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , SHORT - 6 - 4/5</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
@@ -3087,8 +3087,8 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 0, TOPLAM -2, ALMA
-SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , LONG - 41 - 7/9</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 23/9 , ALT -  - 44/6 , SHORT - 2 - 1/8</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 11/1 , LONG - 1 - 11/1 , -</t>
+LONG - 1 - 12/1 , LONG - 1 - 12/1 , -</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -637,8 +637,8 @@
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (17g/-12/%60)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/+3/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (17g/-13/%60)
+L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)
 R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
 R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
         </is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -675,8 +675,8 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 6 - 8/5 , SHORT - 6 - 7/5 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 6 - 8/4 , SHORT - 6 - 7/5 , -</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -715,11 +715,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -733,42 +733,44 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 41/4 , ALT -  - 27/8 , ALT -  - 19/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 17 - 18/8 , ALT -  - 19/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, R-TP2/10G</t>
+          <t>I-TP2/10G, Q-TP2/10G, Q-TP5/20G, R-TP2/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (5g/-1/%76)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 51 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -779,7 +781,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-4.9</v>
+        <v>-4.5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -794,7 +796,7 @@
       <c r="E6" s="4" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 12/1 , ALT -  - 12/1 , ALT -  - 13/0</t>
+ALT -  - 12/1 , ALT -  - 12/1 , SHORT - 39 - 12/0</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -833,11 +835,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -851,51 +853,55 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 56 - 14/7 , SHORT - 56 - 12/5 , LONG - 3 - 8/2</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 27/8</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-6/%80)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 48 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.6</v>
+        <v>-2</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -909,53 +915,51 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL +1, XU030 +1, TOPLAM 6, AL
-SHORT - 66 - 12/9 , SHORT - 66 - 13/8 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 39/3 , ALT -  - 26/12 , LONG - 7 - 13/3</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-3/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (6g/-3/%82)
-L - TP5/10G - %79 / 42 işlem - ADAY (6g/-3/%78)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-2/%95)</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>-1.7</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -970,7 +974,7 @@
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 38/2 , ALT -  - 26/12 , LONG - 7 - 13/4</t>
+SHORT - 56 - 12/8 , SHORT - 56 - 11/6 , LONG - 3 - 7/3</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
@@ -992,7 +996,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-2/%95)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-5/%80)</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1009,181 +1013,181 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 66 - 13/7 , SHORT - 66 - 15/6 , -</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-5/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (6g/-5/%82)
+L - TP5/10G - %79 / 42 işlem - ADAY (6g/-5/%78)</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>BTCIM</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="B11" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 51/37 , LONG - 2 - 30/4 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
+ALT -  - 51/36 , LONG - 2 - 30/4 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>L-TP5/10G, R-TP2/10G</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)
 R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PGSUS</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B12" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 14 - 8/3 , LONG - 27 - 7/5 , LONG - 5 - 10/2</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
+LONG - 14 - 7/3 , LONG - 27 - 7/5 , LONG - 5 - 10/3</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%87)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-2/%40)
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (15g/-1/%40)
 H - TP5/10G - %70 / 20 işlem - ADAY (3g/0/%100)
 H - TP5/20G - %80 / 20 işlem - ADAY (3g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-2/%47)</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-1/%47)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AKSEN</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 17 - 19/7 , ALT -  - 20/7 , ALT -  - 19/6</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>I-TP2/10G, Q-TP2/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (1g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1198,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1209,7 +1213,7 @@
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 18/1 , ALT -  - 18/1 , -</t>
+ALT -  - 18/0 , ALT -  - 18/0 , -</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1231,8 +1235,8 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-4/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (3g/-4/%90)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-3/%91)
+L - TP5/10G - %79 / 42 işlem - ADAY (3g/-3/%90)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1253,7 +1257,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1267,8 +1271,8 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 14/1 , ALT -  - 13/0 , -</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 14/1 , LONG - 1 - 13/0 , -</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -1308,11 +1312,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1326,36 +1330,35 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-ALT -  - 25/3 , ALT -  - 26/3 , ALT -  - 28/9</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
         <v>54</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (17g/-5/%25)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-6/%35)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1367,11 +1370,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1385,8 +1388,8 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 12/1 , ALT -  - 13/2 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -1408,7 +1411,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (13g/-9/%30)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-6/%60)</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1425,11 +1428,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>-2.7</v>
+        <v>2.3</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1466,7 +1469,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-7/%35)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-11/%40)</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1483,11 +1486,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1501,51 +1504,53 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 35/6 , ALT -  - 29/10 , ALT -  - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 28 - 5/5 , LONG - 26 - 5/5 , LONG - 26 - 6/5</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-7/%60)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+2/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/+1/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (13g/0/%100)</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>BRYAT</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1559,12 +1564,12 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 9/1 , ALT -  - 31/11 , LONG - 27 - 21/5</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1577,33 +1582,33 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>R-TP2/10G</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-12/%40)</t>
+          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SASA</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1617,51 +1622,53 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 33/2 , LONG - 2 - 32/3 , LONG - 1 - 10/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 12/1 , ALT -  - 12/1 , LONG - 3 - 16/2</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-3/%55)
+I - TP5/20G - %84 / 49 işlem - ADAY (13g/-3/%77)
+Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-3/%60)</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1675,53 +1682,52 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL -1, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , LONG - 3 - 16/1</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 11/1 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>I-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-4/%55)
-I - TP5/20G - %84 / 49 işlem - ADAY (13g/-4/%77)
-Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-4/%60)</t>
+          <t>I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (13g/-9/%30)</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -1735,53 +1741,51 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 28 - 5/5 , LONG - 26 - 5/5 , LONG - 26 - 6/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , ALT -  - 11/0 , -</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>L-TP5/10G</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (13g/0/%100)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+3/%100)</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -1795,53 +1799,51 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 32/3 , SHORT - 140 - 19/12 , LONG - 2 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 15 - 14/7 , LONG - 1 - 16/2 , LONG - 27 - 3/7</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (7g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (10g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (11g/+1/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/0/%90)</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 38 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>-0.1</v>
+        <v>2.6</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -1855,12 +1857,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 10/1 , ALT -  - 31/12 , LONG - 27 - 22/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 25/2 , LONG - 2 - 30/4 , LONG - 2 - 6/4</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
@@ -1873,33 +1875,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>R-TP2/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1/%100)</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1914,11 +1916,11 @@
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 13/2 , ALT -  - 13/2 , -</t>
+-</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
@@ -1931,17 +1933,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>L-TP5/10G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+1/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0/%100)</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -1953,11 +1955,11 @@
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1972,11 +1974,11 @@
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 32/3 , ALT -  - 15/2 , LONG - 1 - 10/0</t>
+ALT -  - 14/1 , SHORT - 58 - 7/5 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
@@ -1989,18 +1991,18 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -2012,11 +2014,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ARCLK</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2031,50 +2033,50 @@
       <c r="E27" s="4" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 26/3 , LONG - 2 - 31/3 , LONG - 2 - 7/3</t>
+SHORT - 14 - 15/2 , SHORT - 8 - 10/6 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/0/%100)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-5/%71)</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>-0.2</v>
+        <v>2.7</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2087,169 +2089,168 @@
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 2 - 31/3 , ALT -  - 13/0 , LONG - 1 - 8/2</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 1 - 31/3 , LONG - 76 - 8/11 , ALT -  - 26/3</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (18g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SKBNK</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
 -</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-1/%64)</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 14/1 , SHORT - 58 - 8/4 , ALT -  - 14/3</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 15 - 18/4 , ALT -  - 19/1 , LONG - 27 - 6/4</t>
-        </is>
-      </c>
       <c r="F30" s="5" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-3/%90)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2263,55 +2264,51 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 3 - 12/9 , SHORT - 34 - 11/12 , -</t>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 1/10 , UST -  - 0/10 , SHORT - 6 - 4/6</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>L-TP2/10G, M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-M - TP5/20G - %90 / 49 işlem - ONAY (6g/-6/%93)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (6g/-6/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (6g/-6/%60)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-2/%71)</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>-1</v>
+        <v>1.6</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2325,51 +2322,54 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 14 - 14/3 , SHORT - 8 - 10/7 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 3 - 11/9 , SHORT - 34 - 11/13 , -</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-4/%71)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (6g/-5/%93)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (6g/-5/%50)
+R - TP5/20G - %80 / 97 işlem - ADAY (6g/-5/%65)</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 52 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2383,51 +2383,52 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 33/2 , LONG - 76 - 9/11 , ALT -  - 28/5</t>
+          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
+LONG - 7 - 23/9 , ALT -  - 44/6 , SHORT - 2 - 1/8</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-1/%25)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
+U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 33 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2442,34 +2443,35 @@
       <c r="E34" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
+ALT -  - 46/32 , ALT -  - 66/23 , ALT -  - 46/32</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-10/%91)
+T - TP5/20G - %77 / 124 işlem - ADAY (18g/-33/%5)</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -2481,11 +2483,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2499,35 +2501,35 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 1 - 0/9 , SHORT - 1 - 1/9 , SHORT - 6 - 5/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 5 - 4/6 , LONG - 4 - 6/4 , SHORT - 6 - 6/4</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>Q-TP2/10G</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-3/%71)</t>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 62 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -2539,11 +2541,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2557,53 +2559,51 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 5 - 5/5 , LONG - 4 - 8/3 , SHORT - 6 - 8/3</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+LONG - 38 - 15/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, Q-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
-I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (1g/-1/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-4/%85)</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2617,54 +2617,51 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL +1, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 8/2 , SHORT - 8 - 8/3 , SHORT - 6 - 7/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 27 - 6/9 , LONG - 27 - 6/9 , LONG - 25 - 4/8</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>I-TP2/10G, I-TP5/10G, U-TP2/10G, U-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
-I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
-U - TP2/10G - %78 / 67 işlem - ADAY (9g/-5/%7)
-U - TP5/20G - %74 / 73 işlem - ADAY (8g/-6/%80)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (11g/+2/%100)</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2679,35 +2676,34 @@
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 43/30 , ALT -  - 63/21 , ALT -  - 43/30</t>
+LONG - 5 - 7/5 , LONG - 1 - 10/1 , ALT -  - 11/1</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-8/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (18g/-32/%5)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-4/%64)</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -2719,11 +2715,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>-0.8</v>
+        <v>1.3</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2738,34 +2734,35 @@
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 38 - 15/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
+LONG - 2 - 7/3 , SHORT - 8 - 7/4 , SHORT - 6 - 5/6</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>U-TP2/10G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-4/%80)</t>
+          <t>U - TP2/10G - %78 / 67 işlem - ADAY (9g/-4/%7)
+U - TP5/20G - %74 / 73 işlem - ADAY (8g/-6/%80)</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -2777,11 +2774,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ALARK</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2795,51 +2792,52 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 27 - 7/9 , LONG - 27 - 7/9 , LONG - 25 - 4/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 13 - 1/9 , SHORT - 13 - 1/9 , SHORT - 13 - 1/9</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (11g/+1/%100)</t>
+          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+4/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (8g/+4/%100)</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -2853,35 +2851,36 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 7/5 , LONG - 1 - 9/1 , ALT -  - 11/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 27 - 4/6 , LONG - 9 - 11/5 , LONG - 12 - 9/7</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-4/%64)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -2893,11 +2892,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ALARK</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -2912,35 +2911,34 @@
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 13 - 1/8 , SHORT - 13 - 1/8 , SHORT - 13 - 2/8</t>
+SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+3/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (8g/+3/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -2952,11 +2950,11 @@
     <row r="43" ht="32" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -2970,162 +2968,45 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 27 - 4/6 , LONG - 9 - 11/5 , LONG - 12 - 10/7</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 36/0 , ALT -  - 22/4 , ALT -  - 15/2</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+3/%100)</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , SHORT - 6 - 4/5</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 23/9 , ALT -  - 44/6 , SHORT - 2 - 1/8</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M45"/>
+  <autoFilter ref="A1:M43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -609,12 +609,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-LONG - 2 - 12/1 , LONG - 2 - 12/1 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 13/0 , ALT -  - 13/0 , -</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -632,11 +632,11 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/+1/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (18g/-12/%50)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/+3/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (1g/+1/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (1g/+1/%100)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/-1/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (18g/-14/%50)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/+1/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (1g/-1/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (1g/-1/%100)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -646,18 +646,18 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>FENER</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -672,11 +672,11 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 7 - 8/4 , SHORT - 7 - 8/5 , -</t>
+ALT -  - 12/1 , ALT -  - 12/1 , LONG - 1 - 12/1</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>1</v>
@@ -689,17 +689,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-12/%71)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-5/%80)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -711,11 +711,11 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FENER</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -729,8 +729,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , ALT -  - 11/1 , LONG - 1 - 12/1</t>
+          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
+SHORT - 57 - 13/8 , SHORT - 57 - 11/5 , LONG - 4 - 7/3</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-5/%80)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-5/%60)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -769,11 +769,11 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -787,35 +787,37 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 57 - 12/8 , SHORT - 57 - 10/6 , LONG - 4 - 6/4</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+SHORT - 67 - 12/9 , SHORT - 67 - 13/7 , -</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
         <v>62</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-4/%60)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (7g/-4/%75)
+L - TP5/10G - %79 / 42 işlem - ADAY (7g/-4/%75)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -827,11 +829,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.6</v>
+        <v>-2.5</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -845,53 +847,51 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 1 - 12/0 , LONG - 1 - 11/1 , -</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 16 - 10/0 , LONG - 134 - 19/12 , -</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-9/%86)
-I - TP5/10G - %61 / 108 işlem - ADAY (1g/+2/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-2/%90)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-1.2</v>
+        <v>0.9</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -905,12 +905,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 16 - 9/2 , LONG - 134 - 18/13 , -</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 37/1 , ALT -  - 25/11 , LONG - 8 - 12/4</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1</v>
@@ -923,33 +923,33 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-1/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -963,51 +963,52 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 38/2 , ALT -  - 26/11 , LONG - 8 - 13/4</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 19 - 16/9 , ALT -  - 20/6 , ALT -  - 18/5</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>I-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-2/%89)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (2g/0/%100)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1021,53 +1022,54 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
-SHORT - 67 - 13/8 , SHORT - 67 - 14/6 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 25/3 , ALT -  - 27/4 , ALT -  - 28/9</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-6/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (7g/-5/%75)
-L - TP5/10G - %79 / 42 işlem - ADAY (7g/-5/%75)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-2/%50)
+E - TP5/20G - %79 / 42 işlem - ADAY (18g/-5/%25)
+Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1081,36 +1083,39 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 19 - 15/10 , ALT -  - 18/5 , ALT -  - 17/3</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 15 - 7/3 , LONG - 28 - 7/5 , LONG - 6 - 9/3</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Q-TP5/20G</t>
+          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+2/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/+1/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (16g/-1/%25)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/+1/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (4g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-1/%55)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1122,11 +1127,11 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>-0.3</v>
+        <v>0.7</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1140,36 +1145,37 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 51/36 , LONG - 3 - 29/4 , ALT -  - 12/1</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 29 - 4/6 , LONG - 27 - 5/5 , LONG - 27 - 5/5</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L-TP5/10G, R-TP2/10G</t>
+          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/+1/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/+2/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (18g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (14g/+1/%100)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1181,11 +1187,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1199,39 +1205,35 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 15 - 7/3 , LONG - 28 - 7/5 , LONG - 6 - 9/3</t>
+          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (16g/-1/%25)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/0/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (4g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-1/%55)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-4/%30)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1243,11 +1245,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1261,52 +1263,51 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 15/2 , LONG - 2 - 15/2 , -</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-2/%88)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-2/%91)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-6/%60)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1320,36 +1321,35 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 27/8</t>
+          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
         <v>54</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-1/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (18g/-5/%25)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1361,11 +1361,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1379,35 +1379,36 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+ALT -  - 13/0 , LONG - 1 - 12/1 , -</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
         <v>54</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>M-TP5/20G, I-TP5/10G</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-6/%60)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-10/%86)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1419,11 +1420,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRYAT</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1438,7 +1439,7 @@
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 3 - 8/2 , ALT -  - 30/11 , LONG - 28 - 20/5</t>
+ALT -  - 12/1 , ALT -  - 12/1 , LONG - 4 - 16/1</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -1448,100 +1449,101 @@
         <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>R-TP2/10G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>R - TP2/10G - %84 / 118 işlem - ADAY (2g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 12/1 , ALT -  - 12/1 , LONG - 4 - 15/2</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-3/%33)
 I - TP5/20G - %84 / 49 işlem - ADAY (14g/-3/%73)
 Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-3/%55)</t>
         </is>
       </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BSOKE</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 56/41 , ALT -  - 78/32 , ALT -  - 56/41</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, T-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-16/%89)
+T - TP5/20G - %77 / 124 işlem - ADAY (19g/-38/%0)</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1555,53 +1557,52 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 29 - 5/5 , LONG - 27 - 5/5 , LONG - 27 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 11/0 , ALT -  - 13/2 , ALT -  - 13/2</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>I-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/+2/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (18g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (14g/+1/%100)</t>
+          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (14g/-9/%30)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1614,345 +1615,344 @@
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
+ALT -  - 13/0 , SHORT - 59 - 7/5 , ALT -  - 13/2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-3/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-3/%25)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CWENE</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 10/1 , LONG - 1 - 10/1 , -</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-5/%30)</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="F22" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Q-TP2/10G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PSGYO</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TUKAS</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 16 - 16/5 , LONG - 2 - 17/0 , LONG - 28 - 5/5</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 26/3 , LONG - 3 - 31/3 , LONG - 3 - 7/3</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="F25" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/0/%58)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 52/38 , ALT -  - 74/29 , ALT -  - 52/38</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-14/%89)
-T - TP5/20G - %77 / 124 işlem - ADAY (19g/-37/%0)</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/0 , ALT -  - 13/2 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>I-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (14g/-9/%30)</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>GENIL</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/0/%95)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 25/2 , LONG - 3 - 30/4 , LONG - 3 - 6/4</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1966,52 +1966,51 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 13/0 , SHORT - 59 - 7/5 , ALT -  - 13/2</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 15 - 12/4 , SHORT - 13 - 12/4 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-3/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-3/%25)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-3/%69)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2026,11 +2025,11 @@
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 9/1 , LONG - 1 - 9/1 , -</t>
+LONG - 3 - 31/3 , LONG - 1 - 13/0 , LONG - 2 - 8/2</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0</v>
@@ -2043,17 +2042,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>L-TP5/10G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)</t>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+3/%100)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2065,11 +2064,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TUKAS</t>
+          <t>FROTO</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2084,11 +2083,11 @@
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 16 - 14/6 , LONG - 2 - 16/1 , LONG - 28 - 4/6</t>
+LONG - 2 - 30/4 , LONG - 77 - 8/12 , ALT -  - 25/2</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>0</v>
@@ -2101,17 +2100,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-1/%95)</t>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+1/%100)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2123,11 +2122,11 @@
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>-0.2</v>
+        <v>2.5</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2141,51 +2140,51 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+UST -  - 3/12 , UST -  - 2/11 , SHORT - 7 - 2/8</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/0/%100)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/0/%71)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>SKBNK</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2199,39 +2198,35 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 7/5 , SHORT - 28 - 21/10 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>L-TP2/10G, M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
-M - TP5/20G - %90 / 49 işlem - ONAY (7g/-6/%93)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (7g/-6/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (7g/-6/%60)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/+1/%100)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2243,11 +2238,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2262,11 +2257,11 @@
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 15 - 14/3 , SHORT - 9 - 10/6 , ALT -  - 11/0</t>
+LONG - 3 - 5/7 , LONG - 21 - 14/11 , LONG - 3 - 2/7</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>1</v>
@@ -2279,17 +2274,17 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>S-TP2/10G</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-5/%69)</t>
+          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/-1/%80)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2301,11 +2296,11 @@
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2319,51 +2314,53 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 3 - 31/3 , LONG - 1 - 13/0 , LONG - 2 - 8/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 5/7 , SHORT - 28 - 19/12 , -</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+3/%100)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-3/%93)
+R - TP5/10G - %62 / 63 işlem - ADAY (7g/-3/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (7g/-3/%70)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2378,50 +2375,51 @@
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 30/4 , LONG - 77 - 8/12 , ALT -  - 26/3</t>
+LONG - 2 - 15/2 , LONG - 2 - 15/2 , -</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+1/%100)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-2/%88)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-2/%91)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2.7</v>
+        <v>-2.1</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2435,51 +2433,52 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-UST -  - 3/12 , UST -  - 2/12 , SHORT - 7 - 2/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 54/39 , LONG - 3 - 32/3 , ALT -  - 14/3</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP5/10G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/0/%71)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/-1/%91)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/-2/%75)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2493,12 +2492,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 7 - 4/8 , SHORT - 7 - 4/8 , -</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>1</v>
@@ -2511,33 +2510,33 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/0/%100)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-9/%71)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2551,35 +2550,35 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 3 - 4/8 , LONG - 21 - 13/11 , LONG - 3 - 2/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 7 - 6/4 , SHORT - 7 - 6/4 , SHORT - 7 - 6/4</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>S-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/0/%80)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-4/%90)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -2591,11 +2590,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2609,8 +2608,8 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 7 - 3/6 , SHORT - 7 - 3/6 , LONG - 42 - 7/9</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 39 - 13/11 , SHORT - 7 - 3/7 , SHORT - 7 - 3/7</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
@@ -2632,7 +2631,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-2/%90)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -2649,11 +2648,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2667,8 +2666,8 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 39 - 14/11 , SHORT - 7 - 3/6 , SHORT - 7 - 3/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 8 - 22/10 , ALT -  - 43/6 , SHORT - 3 - 1/8</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
@@ -2690,7 +2689,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%90)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/0/%95)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -2707,11 +2706,11 @@
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2725,8 +2724,8 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-LONG - 8 - 23/9 , ALT -  - 44/6 , SHORT - 3 - 2/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 6/4 , SHORT - 9 - 6/4 , SHORT - 7 - 5/7</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
@@ -2748,7 +2747,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/-1/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-5/%90)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -2765,11 +2764,11 @@
     <row r="40" ht="32" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
@@ -2784,7 +2783,7 @@
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 6/4 , SHORT - 9 - 6/4 , SHORT - 7 - 5/7</t>
+LONG - 28 - 7/9 , LONG - 28 - 7/9 , LONG - 26 - 4/8</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
@@ -2806,7 +2805,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-5/%90)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+1/%100)</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -2823,11 +2822,11 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -2841,12 +2840,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 28 - 6/10 , LONG - 28 - 6/10 , LONG - 26 - 3/8</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 6 - 7/5 , LONG - 2 - 9/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>0</v>
@@ -2859,17 +2858,17 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+2/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-4/%58)</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -2881,11 +2880,11 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -2899,35 +2898,36 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 34/1 , ALT -  - 20/2 , ALT -  - 13/1</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 5 - 5/5 , LONG - 5 - 4/6 , SHORT - 7 - 4/6</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/+3/%100)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+2/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -2936,184 +2936,8 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 6 - 7/5 , LONG - 2 - 10/1 , ALT -  - 11/1</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-4/%58)</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ISCTR</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL -1, XU030 +1, TOPLAM 0, ALMA
-LONG - 28 - 4/6 , LONG - 10 - 11/6 , LONG - 13 - 9/7</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (4g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (4g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TRALT</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 6/4 , LONG - 5 - 5/5 , SHORT - 7 - 5/5</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M45"/>
+  <autoFilter ref="A1:M42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 13/0 , ALT -  - 13/0 , -</t>
+LONG - 2 - 13/0 , LONG - 2 - 13/0 , -</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -632,11 +632,11 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/-1/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (18g/-14/%50)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/+1/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (1g/-1/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (1g/-1/%100)</t>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (18g/-13/%50)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (1g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -672,7 +672,7 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 12/1 , ALT -  - 12/1 , LONG - 1 - 12/1</t>
+ALT -  - 11/1 , ALT -  - 11/1 , LONG - 1 - 12/1</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -729,8 +729,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL -1, XU030 +1, TOPLAM 2, ALMA
-SHORT - 57 - 13/8 , SHORT - 57 - 11/5 , LONG - 4 - 7/3</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 4 - 5/5 , SHORT - 57 - 10/7 , LONG - 4 - 6/4</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -752,7 +752,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-5/%60)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-4/%60)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -829,11 +829,11 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-2.5</v>
+        <v>2.3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -847,51 +847,53 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 16 - 10/0 , LONG - 134 - 19/12 , -</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 1 - 12/1 , LONG - 1 - 11/2 , -</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-2/%90)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-9/%86)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/+2/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -905,51 +907,52 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 37/1 , ALT -  - 25/11 , LONG - 8 - 12/4</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+-</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>I-TP2/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (2g/-1/%89)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>-0.7</v>
+        <v>-3.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -963,36 +966,35 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 19 - 16/9 , ALT -  - 20/6 , ALT -  - 18/5</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 11/0 , LONG - 134 - 20/11 , -</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Q-TP5/20G</t>
+          <t>I-TP2/10G</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (2g/0/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-3/%85)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1004,11 +1006,11 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-0.7</v>
+        <v>1.4</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1023,53 +1025,51 @@
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 25/3 , ALT -  - 27/4 , ALT -  - 28/9</t>
+LONG - 19 - 14/10 , ALT -  - 18/4 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G</t>
+          <t>I-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/-2/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (18g/-5/%25)
-Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 49 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1083,39 +1083,35 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 15 - 7/3 , LONG - 28 - 7/5 , LONG - 6 - 9/3</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 33/5 , ALT -  - 28/9 , LONG - 1 - 10/0</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/+1/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (16g/-1/%25)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/+1/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (4g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/-1/%55)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-6/%65)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1131,7 +1127,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1146,52 +1142,51 @@
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 29 - 4/6 , LONG - 27 - 5/5 , LONG - 27 - 5/5</t>
+LONG - 29 - 2/8 , LONG - 27 - 2/8 , LONG - 27 - 2/8</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
+          <t>T-TP5/20G, U-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (6g/+2/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (18g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (14g/+1/%100)</t>
+          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/+4/%100)
+U - TP5/20G - %74 / 73 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MAGEN</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1205,35 +1200,37 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 1 - 8/2 , LONG - 1 - 10/1 , LONG - 4 - 13/4</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-4/%30)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-1/%33)
+I - TP5/20G - %84 / 49 işlem - ADAY (14g/-1/%73)
+Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-1/%55)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1245,11 +1242,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1263,51 +1260,52 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/0</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 23/1 , ALT -  - 24/2 , ALT -  - 26/7</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-6/%60)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (18g/-3/%25)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1321,35 +1319,38 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
--</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 15 - 5/5 , LONG - 28 - 5/7 , LONG - 6 - 7/5</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/+1/%100)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/+3/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (4g/+3/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+1/%100)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1361,7 +1362,7 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1379,36 +1380,36 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 13/0 , LONG - 1 - 12/1 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 1 - 10/1 , ALT -  - 11/1 , ALT -  - 12/1</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>M-TP5/20G, I-TP5/10G</t>
+          <t>I-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-10/%86)
-I - TP5/10G - %61 / 108 işlem - ADAY (1g/+1/%100)</t>
+          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/+1/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (14g/-8/%30)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1420,11 +1421,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>-0.3</v>
+        <v>2.4</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1439,36 +1440,35 @@
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 12/1 , ALT -  - 12/1 , LONG - 4 - 16/1</t>
+LONG - 1 - 11/2 , SHORT - 59 - 5/7 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-3/%33)
-I - TP5/20G - %84 / 49 işlem - ADAY (14g/-3/%73)
-Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-3/%55)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-1/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-1/%25)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1480,11 +1480,11 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>-5.1</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1499,35 +1499,34 @@
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 56/41 , ALT -  - 78/32 , ALT -  - 56/41</t>
+LONG - 16 - 14/6 , LONG - 2 - 16/1 , LONG - 28 - 4/6</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-16/%89)
-T - TP5/20G - %77 / 124 işlem - ADAY (19g/-38/%0)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-1/%95)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1539,11 +1538,11 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>ARCLK</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>-0.4</v>
+        <v>1.1</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1557,52 +1556,51 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 11/0 , ALT -  - 13/2 , ALT -  - 13/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 22/0 , LONG - 3 - 28/5 , LONG - 3 - 5/5</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>I-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (14g/-9/%30)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+2/%100)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>TURSG</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1616,52 +1614,51 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>BIS -1, PHL 0, CNDL 0, XU030 +1, TOPLAM 0, ALMA
-ALT -  - 13/0 , SHORT - 59 - 7/5 , ALT -  - 13/2</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-3/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-3/%25)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/+1/%100)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>-0.4</v>
+        <v>3.1</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -1675,187 +1672,186 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 10/1 , LONG - 1 - 10/1 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 15 - 11/5 , SHORT - 13 - 11/5 , LONG - 1 - 8/2</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>L-TP5/10G</t>
+          <t>K-TP5/20G</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-2/%69)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 29/5 , LONG - 1 - 11/1 , LONG - 2 - 6/4</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+5/%100)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 28/5 , LONG - 77 - 6/13 , ALT -  - 24/1</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>GENIL</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="B24" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Q-TP2/10G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 16 - 16/5 , LONG - 2 - 17/0 , LONG - 28 - 5/5</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 26/3 , LONG - 3 - 31/3 , LONG - 3 - 7/3</t>
-        </is>
-      </c>
       <c r="F24" s="4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0</v>
@@ -1868,17 +1864,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>Q-TP5/20G</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/0/%100)</t>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+2/%100)</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -1890,11 +1886,11 @@
     <row r="25" ht="32" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>-0.3</v>
+        <v>3.3</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -1908,51 +1904,51 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+UST -  - 4/13 , UST -  - 3/12 , SHORT - 7 - 1/9</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/0/%58)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/+1/%100)</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1.9</v>
+        <v>-0.1</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1966,12 +1962,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 15 - 12/4 , SHORT - 13 - 12/4 , LONG - 1 - 9/1</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+LONG - 3 - 4/8 , LONG - 21 - 13/11 , LONG - 3 - 2/8</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>1</v>
@@ -1984,17 +1980,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>S-TP2/10G</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-3/%69)</t>
+          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/0/%80)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2006,11 +2002,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2024,51 +2020,53 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 3 - 31/3 , LONG - 1 - 13/0 , LONG - 2 - 8/2</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 3 - 4/8 , SHORT - 28 - 17/13 , -</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+3/%100)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-2/%93)
+R - TP5/10G - %62 / 63 işlem - ADAY (7g/-2/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (7g/-2/%85)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>IZENR</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2083,50 +2081,51 @@
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 30/4 , LONG - 77 - 8/12 , ALT -  - 25/2</t>
+LONG - 2 - 15/2 , LONG - 2 - 15/2 , -</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>L-TP5/20G, L-TP5/10G</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+1/%100)</t>
+          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-2/%88)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-2/%91)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2.5</v>
+        <v>-3.6</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2140,51 +2139,52 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-UST -  - 3/12 , UST -  - 2/11 , SHORT - 7 - 2/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 56/42 , LONG - 3 - 34/1 , ALT -  - 16/5</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP5/10G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/0/%71)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/-2/%91)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/-4/%75)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -2203,30 +2203,30 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/+1/%100)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-2/%30)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2238,11 +2238,11 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -2256,51 +2256,52 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 3 - 5/7 , LONG - 21 - 14/11 , LONG - 3 - 2/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 41/5 , ALT -  - 88/39 , ALT -  - 64/48</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>S-TP2/10G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/-1/%80)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-21/%89)
+T - TP5/20G - %77 / 124 işlem - ADAY (19g/-41/%0)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2315,52 +2316,50 @@
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 5/7 , SHORT - 28 - 19/12 , -</t>
+SHORT - 7 - 1/11 , SHORT - 7 - 0/11 , -</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-3/%93)
-R - TP5/10G - %62 / 63 işlem - ADAY (7g/-3/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (7g/-3/%70)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-5/%71)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2374,52 +2373,51 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 15/2 , LONG - 2 - 15/2 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 7 - 5/5 , SHORT - 7 - 5/5 , SHORT - 7 - 5/5</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-2/%88)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-2/%91)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-3/%90)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>-2.1</v>
+        <v>1.9</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2433,52 +2431,51 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 54/39 , LONG - 3 - 32/3 , ALT -  - 14/3</t>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+LONG - 39 - 13/11 , SHORT - 7 - 3/7 , SHORT - 7 - 3/7</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>L-TP5/10G, R-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/-1/%91)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/-2/%75)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2492,51 +2489,51 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 7 - 4/8 , SHORT - 7 - 4/8 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 8 - 22/10 , ALT -  - 43/6 , SHORT - 3 - 2/8</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-9/%71)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/0/%95)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>-1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2550,8 +2547,8 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 7 - 6/4 , SHORT - 7 - 6/4 , SHORT - 7 - 6/4</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 5/5 , SHORT - 9 - 5/5 , SHORT - 7 - 4/8</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
@@ -2573,7 +2570,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-4/%90)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-4/%90)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -2590,11 +2587,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2608,35 +2605,36 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 39 - 13/11 , SHORT - 7 - 3/7 , SHORT - 7 - 3/7</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 5 - 5/5 , LONG - 5 - 3/6 , SHORT - 7 - 4/6</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-3/%95)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+3/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+3/%100)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -2648,11 +2646,11 @@
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2666,12 +2664,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 8 - 22/10 , ALT -  - 43/6 , SHORT - 3 - 1/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 28 - 5/11 , LONG - 28 - 5/11 , LONG - 26 - 2/10</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0</v>
@@ -2689,7 +2687,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/0/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+4/%100)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -2699,18 +2697,18 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
@@ -2724,12 +2722,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 6/4 , SHORT - 9 - 6/4 , SHORT - 7 - 5/7</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 6 - 5/7 , LONG - 2 - 7/3 , LONG - 1 - 9/1</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>0</v>
@@ -2742,202 +2740,27 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-5/%90)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-2/%58)</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SAHOL</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 28 - 7/9 , LONG - 28 - 7/9 , LONG - 26 - 4/8</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 6 - 7/5 , LONG - 2 - 9/1 , ALT -  - 11/0</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-4/%58)</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TRALT</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 5/5 , LONG - 5 - 4/6 , SHORT - 7 - 4/6</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M42"/>
+  <autoFilter ref="A1:M39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -573,8 +573,8 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (12g/?/%?)
-M - TP5/20G - %90 / 49 işlem - ONAY (12g/?/%?)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (13g/?/%?)
+M - TP5/20G - %90 / 49 işlem - ONAY (13g/?/%?)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -609,12 +609,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 13/0 , LONG - 2 - 13/0 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 11/2 , LONG - 3 - 11/2 , -</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -632,268 +632,271 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (18g/-13/%50)
-L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/+1/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (19g/-12/%33)
+L - TP5/10G - %79 / 42 işlem - ADAY (3g/+3/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (2g/+1/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (2g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 8 - 2/10 , SHORT - 8 - 1/10 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (13g/-6/%67)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+ALT -  - 11/1 , ALT -  - 11/1 , LONG - 2 - 11/1</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-5/%73)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QUAGR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 69 - 12/12 , LONG - 2 - 10/3 , -</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (10g/-8/%82)
+I - TP5/10G - %61 / 108 işlem - ADAY (2g/+3/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 68 - 11/9 , SHORT - 68 - 12/8 , -</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (7g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (8g/-4/%80)
+L - TP5/10G - %79 / 42 işlem - ADAY (8g/-4/%56)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)
 R - TP5/10G - %62 / 63 işlem - ADAY (1g/0/%100)
 R - TP5/20G - %80 / 97 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 52 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/1 , ALT -  - 11/1 , LONG - 1 - 12/1</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-5/%80)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TAVHL</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 4 - 5/5 , SHORT - 57 - 10/7 , LONG - 4 - 6/4</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-4/%60)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-SHORT - 67 - 12/9 , SHORT - 67 - 13/7 , -</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-4/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (7g/-4/%75)
-L - TP5/10G - %79 / 42 işlem - ADAY (7g/-4/%75)</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 1 - 12/1 , LONG - 1 - 11/2 , -</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-9/%86)
-I - TP5/10G - %61 / 108 işlem - ADAY (1g/+2/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -907,12 +910,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 20 - 14/10 , ALT -  - 17/4 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1</v>
@@ -925,34 +928,34 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-TP2/10G, R-TP5/20G</t>
+          <t>I-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (2g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (3g/+2/%100)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>-3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -966,51 +969,54 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , LONG - 134 - 20/11 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 19/3 , ALT -  - 23/1 , ALT -  - 25/6</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>E-TP2/10G, E-TP5/20G, Q-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-3/%85)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (7g/0/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (19g/-3/%25)
+Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 49 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -1024,110 +1030,114 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 19 - 14/10 , ALT -  - 18/4 , ALT -  - 16/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Q-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+2/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-1/%100)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/-1/%100)
+I - TP5/20G - %84 / 49 işlem - ADAY (1g/-1/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (12g/-12/%35)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>TSKB</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>İZLEME | ELDEKİ</t>
+          <t>İZLEME</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>ELDE TUT</t>
+          <t>İZLE</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 33/5 , ALT -  - 28/9 , LONG - 1 - 10/0</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 30 - 2/8 , LONG - 28 - 2/8 , LONG - 28 - 2/8</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
         <v>54</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>H-TP2/10G, H-TP5/10G, H-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-6/%65)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (0g/0/%100)
+H - TP5/10G - %70 / 20 işlem - ADAY (0g/0/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Bugün 3 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 29 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSKB</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3.5</v>
+        <v>-0.2</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -1142,35 +1152,37 @@
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 29 - 2/8 , LONG - 27 - 2/8 , LONG - 27 - 2/8</t>
+LONG - 2 - 9/2 , LONG - 2 - 9/2 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>T-TP5/20G, U-TP5/20G</t>
+          <t>I-TP5/10G, Q-TP2/10G, Q-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>T - TP5/20G - %77 / 124 işlem - ADAY (14g/+4/%100)
-U - TP5/20G - %74 / 73 işlem - ADAY (0g/0/%100)</t>
+          <t>I - TP5/10G - %61 / 108 işlem - ADAY (2g/+1/%100)
+Q - TP2/10G - %82 / 103 işlem - ADAY (0g/0/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (15g/-7/%30)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi, U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 62 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 51 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1182,11 +1194,11 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -1200,37 +1212,37 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 8/2 , LONG - 1 - 10/1 , LONG - 4 - 13/4</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+SHORT - 17 - 9/1 , LONG - 135 - 18/13 , -</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/-1/%33)
-I - TP5/20G - %84 / 49 işlem - ADAY (14g/-1/%73)
-Q - TP5/20G - %68 / 68 işlem - ADAY (14g/-1/%55)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (2g/-2/%90)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/+1/%100)
+I - TP5/20G - %84 / 49 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1242,11 +1254,11 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1261,35 +1273,34 @@
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 23/1 , ALT -  - 24/2 , ALT -  - 26/7</t>
+ALT -  - 33/4 , ALT -  - 27/8 , ALT -  - 36/1</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
         <v>51</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (18g/-3/%25)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (11g/-5/%65)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1301,11 +1312,11 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -1319,54 +1330,53 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 15 - 5/5 , LONG - 28 - 5/7 , LONG - 6 - 7/5</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/+1/%100)
-H - TP5/10G - %70 / 20 işlem - ADAY (4g/+3/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (4g/+3/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+1/%100)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/0/%100)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/0/%100)
+I - TP5/20G - %84 / 49 işlem - ADAY (1g/0/%100)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANSGR</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -1380,52 +1390,53 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 1 - 10/1 , ALT -  - 11/1 , ALT -  - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 8/2 , LONG - 2 - 9/1 , LONG - 5 - 13/4</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-TP5/10G, R-TP5/20G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/+1/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (14g/-8/%30)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/-1/%40)
+I - TP5/20G - %84 / 49 işlem - ADAY (15g/-1/%73)
+Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-1/%50)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>THYAO</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2.4</v>
+        <v>-1</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1440,35 +1451,37 @@
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 1 - 11/2 , SHORT - 59 - 5/7 , ALT -  - 11/0</t>
+LONG - 16 - 4/6 , LONG - 29 - 4/8 , LONG - 7 - 6/6</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-1/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-1/%25)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/+2/%100)
+H - TP5/10G - %70 / 20 işlem - ADAY (5g/+3/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (5g/+3/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (17g/+2/%100)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1498,12 +1511,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 16 - 14/6 , LONG - 2 - 16/1 , LONG - 28 - 4/6</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 17 - 13/7 , LONG - 3 - 14/3 , LONG - 29 - 3/7</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -1521,7 +1534,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-1/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/0/%100)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -1531,7 +1544,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1555,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
@@ -1556,12 +1569,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 1 - 22/0 , LONG - 3 - 28/5 , LONG - 3 - 5/5</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 2 - 21/1 , LONG - 4 - 27/6 , LONG - 4 - 4/6</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0</v>
@@ -1579,7 +1592,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+2/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (15g/+3/%100)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -1589,7 +1602,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1613,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>1.3</v>
+        <v>-0.3</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1613,342 +1626,345 @@
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>THYAO</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 2 - 10/2 , SHORT - 60 - 5/7 , LONG - 2 - 10/0</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (19g/-1/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (19g/-1/%28)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 9 - 18/13 , LONG - 6 - 27/6 , UST -  - 1/10</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (5g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 3 - 12/4 , LONG - 3 - 12/4 , -</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/0/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (5g/-1/%89)
+L - TP5/10G - %79 / 42 işlem - ADAY (5g/-1/%89)</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 16 - 9/7 , SHORT - 14 - 9/7 , LONG - 2 - 6/4</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (11g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="F25" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TKFEN</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 15 - 11/5 , SHORT - 13 - 11/5 , LONG - 1 - 8/2</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>K-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-2/%69)</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CIMSA</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 29/5 , LONG - 1 - 11/1 , LONG - 2 - 6/4</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+5/%100)</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>FROTO</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 28/5 , LONG - 77 - 6/13 , ALT -  - 24/1</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>GENIL</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TRENJ</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-UST -  - 4/13 , UST -  - 3/12 , SHORT - 7 - 1/9</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>TRENJ</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -1962,12 +1978,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 3 - 4/8 , LONG - 21 - 13/11 , LONG - 3 - 2/8</t>
+          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+UST -  - 6/15 , UST -  - 5/14 , UST -  - 1/10</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>1</v>
@@ -1980,17 +1996,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>S-TP2/10G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/0/%80)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (13g/+3/%100)</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2002,11 +2018,11 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2020,37 +2036,36 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-LONG - 3 - 4/8 , SHORT - 28 - 17/13 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+UST -  - 5/26 , UST -  - 7/31 , UST -  - 16/26</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
+          <t>K-TP2/10G, K-TP5/10G</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-2/%93)
-R - TP5/10G - %62 / 63 işlem - ADAY (7g/-2/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (7g/-2/%85)</t>
+          <t>K - TP2/10G - %96 / 49 işlem - ONAY (1g/+1/%100)
+K - TP5/10G - %85 / 40 işlem - ONAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 17 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2062,11 +2077,11 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -2080,52 +2095,51 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 15/2 , LONG - 2 - 15/2 , -</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 4 - 3/9 , LONG - 22 - 12/12 , SHORT - 1 - 0/9</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>S-TP2/10G</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (4g/-2/%88)
-L - TP5/10G - %79 / 42 işlem - ADAY (4g/-2/%91)</t>
+          <t>S - TP2/10G - %91 / 57 işlem - ONAY (2g/+1/%100)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -2139,169 +2153,170 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 56/42 , LONG - 3 - 34/1 , ALT -  - 16/5</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 4 - 6/6 , SHORT - 29 - 19/12 , -</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>L-TP5/10G, R-TP2/10G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/-2/%91)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/-4/%75)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (8g/-4/%92)
+R - TP5/10G - %62 / 63 işlem - ADAY (8g/-4/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (8g/-4/%65)</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
+ALT -  - 56/41 , LONG - 4 - 32/2 , ALT -  - 14/3</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (3g/-3/%90)
+R - TP2/10G - %84 / 118 işlem - ADAY (2g/-4/%65)</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>MAGEN</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="B31" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>R-TP5/20G</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-2/%30)</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (18g/-1/%25)</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 41/5 , ALT -  - 88/39 , ALT -  - 64/48</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-21/%89)
-T - TP5/20G - %77 / 124 işlem - ADAY (19g/-41/%0)</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>10</v>
+        <v>-5.3</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -2316,50 +2331,50 @@
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 7 - 1/11 , SHORT - 7 - 0/11 , -</t>
+ALT -  - 43/6 , ALT -  - 96/45 , ALT -  - 71/54</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>L-TP5/10G</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-5/%71)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (6g/-25/%78)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Günlük artış %5 veya üzeri; alınmaz</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -2374,7 +2389,7 @@
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 7 - 5/5 , SHORT - 7 - 5/5 , SHORT - 7 - 5/5</t>
+LONG - 43 - 0/15 , LONG - 78 - 3/15 , UST -  - 1/16</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
@@ -2396,7 +2411,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-3/%90)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (1g/+1/%100)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -2413,11 +2428,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2431,8 +2446,8 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 39 - 13/11 , SHORT - 7 - 3/7 , SHORT - 7 - 3/7</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 4 - 4/6 , SHORT - 10 - 4/6 , SHORT - 8 - 3/9</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
@@ -2454,7 +2469,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (10g/-2/%95)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -2471,11 +2486,11 @@
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2489,8 +2504,8 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 8 - 22/10 , ALT -  - 43/6 , SHORT - 3 - 2/8</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 29 - 4/11 , LONG - 29 - 4/11 , LONG - 27 - 1/10</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -2512,7 +2527,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/0/%95)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (13g/+5/%100)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -2529,11 +2544,11 @@
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OYAKC</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2548,11 +2563,11 @@
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 5/5 , SHORT - 9 - 5/5 , SHORT - 7 - 4/8</t>
+LONG - 7 - 4/8 , LONG - 3 - 6/4 , LONG - 2 - 7/3</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>0</v>
@@ -2565,17 +2580,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-4/%90)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (11g/-1/%58)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -2587,11 +2602,11 @@
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>2.5</v>
+        <v>-0.3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2605,52 +2620,51 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 5/5 , LONG - 5 - 3/6 , SHORT - 7 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 8 - 5/5 , SHORT - 8 - 5/5 , SHORT - 8 - 5/5</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+3/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (1g/+3/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-3/%90)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2665,7 +2679,7 @@
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 28 - 5/11 , LONG - 28 - 5/11 , LONG - 26 - 2/10</t>
+LONG - 40 - 10/14 , SHORT - 8 - 0/9 , SHORT - 8 - 0/9</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
@@ -2687,7 +2701,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+4/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/0/%100)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -2701,66 +2715,8 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TCELL</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 6 - 5/7 , LONG - 2 - 7/3 , LONG - 1 - 9/1</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-2/%58)</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M39"/>
+  <autoFilter ref="A1:M38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2771,7 +2727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2863,7 +2819,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>-1.5</v>
+        <v>0.6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -2900,8 +2856,8 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (11g/-16/%64)
-M - TP5/20G - %90 / 49 işlem - ONAY (11g/-16/%82)</t>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (12g/-15/%67)
+M - TP5/20G - %90 / 49 işlem - ONAY (12g/-15/%75)</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -2922,7 +2878,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>-0.1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -2936,12 +2892,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 12/0 , LONG - 1 - 12/0 , -</t>
+          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
+LONG - 2 - 12/0 , LONG - 2 - 12/0 , -</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -2959,79 +2915,84 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (17g/-13/%60)
-L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (1g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (18g/-13/%50)
+L - TP5/10G - %79 / 42 işlem - ADAY (2g/+2/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (1g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (1g/0/%100)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KLRHO</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>İZLEME | ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL +1, XU030 +1, TOPLAM 6, AL
+SHORT - 67 - 11/9 , SHORT - 67 - 13/8 , -</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (6g/-4/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (7g/-4/%75)
+L - TP5/10G - %79 / 42 işlem - ADAY (7g/-4/%75)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
 R - TP5/10G - %62 / 63 işlem - ADAY (0g/0/%100)
 R - TP5/20G - %80 / 97 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 6 - 11/2 , SHORT - 6 - 10/2 , -</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-14/%71)</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 52 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3003,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3056,8 +3017,8 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 13/2 , ALT -  - 13/2 , ALT -  - 13/0</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+ALT -  - 12/1 , ALT -  - 12/1 , LONG - 1 - 12/1</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -3079,7 +3040,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (4g/-5/%82)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (5g/-5/%80)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -3096,30 +3057,30 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CVKMD</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>İZLEME</t>
+          <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>İZLE</t>
+          <t>ELDE TUT</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 15 - 8/3 , LONG - 133 - 17/13 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 4 - 4/6 , SHORT - 57 - 9/7 , LONG - 4 - 5/5</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>1</v>
@@ -3132,33 +3093,33 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>I-TP2/10G</t>
+          <t>H-TP2/10G</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)</t>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (9g/-3/%60)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Sistem geçmişi yaklaşık 64 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3172,12 +3133,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 17 - 18/7 , ALT -  - 19/6 , ALT -  - 18/5</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 1 - 12/1 , LONG - 1 - 10/2 , -</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>
@@ -3190,35 +3151,35 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-TP2/10G, Q-TP2/10G, Q-TP5/20G</t>
+          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
-Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+1/%100)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (9g/-9/%86)
+I - TP5/10G - %61 / 108 işlem - ADAY (1g/+2/%100)
+R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 48 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>PSGYO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-1.9</v>
+        <v>0.3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3232,8 +3193,8 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 39/2 , ALT -  - 26/12 , LONG - 7 - 13/4</t>
+          <t>BIS +1, PHL 0, CNDL +1, XU030 +1, TOPLAM 3, İZLE
+-</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -3243,40 +3204,43 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (1g/-2/%95)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %84 / 49 işlem - ADAY (0g/0/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (11g/-11/%40)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 3 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -3290,51 +3254,52 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 56 - 13/8 , SHORT - 56 - 11/5 , LONG - 3 - 7/3</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 19 - 14/10 , ALT -  - 18/4 , ALT -  - 16/3</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>I-TP2/10G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (8g/-5/%80)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/+1/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+2/%100)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 59 hisse / 41 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLRHO</t>
+          <t>MAVI</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-1.6</v>
+        <v>0.8</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3348,53 +3313,51 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 66 - 14/7 , SHORT - 66 - 15/6 , -</t>
+          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
+ALT -  - 33/4 , ALT -  - 27/8 , LONG - 1 - 10/1</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+          <t>R-TP5/20G</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (5g/-5/%100)
-L - TP5/20G - %91 / 44 işlem - ONAY (6g/-5/%82)
-L - TP5/10G - %79 / 42 işlem - ADAY (6g/-5/%78)</t>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-5/%65)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 15 hisse / 40 giriş gününe yayılıyor</t>
+          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Risk sayısı 1</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IZENR</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3409,51 +3372,52 @@
       <c r="E11" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL +2, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 1 - 16/1 , LONG - 1 - 16/1 , -</t>
+SHORT - 16 - 10/0 , LONG - 134 - 19/12 , -</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>L-TP5/20G, L-TP5/10G</t>
+          <t>I-TP2/10G, I-TP5/10G, I-TP5/20G</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/20G - %91 / 44 işlem - ONAY (3g/-2/%91)
-L - TP5/10G - %79 / 42 işlem - ADAY (3g/-2/%90)</t>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (1g/-2/%90)
+I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
+I - TP5/20G - %84 / 49 işlem - ADAY (0g/0/%100)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ONAY L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 18 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 58 hisse / 35 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -3468,51 +3432,52 @@
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 51/37 , LONG - 2 - 31/4 , ALT -  - 13/3</t>
+LONG - 1 - 7/3 , LONG - 1 - 9/2 , LONG - 4 - 12/4</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L-TP5/10G, R-TP2/10G</t>
+          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+1/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/0/%33)
+I - TP5/20G - %84 / 49 işlem - ADAY (14g/0/%73)
+Q - TP5/20G - %68 / 68 işlem - ADAY (14g/0/%55)</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PGSUS</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -3526,55 +3491,52 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>BIS +1, PHL 0, CNDL 0, XU030 +1, TOPLAM 2, ALMA
-LONG - 14 - 7/3 , LONG - 27 - 7/5 , LONG - 5 - 10/3</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 19/3 , ALT -  - 23/1 , ALT -  - 24/6</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>H-TP2/10G, E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
+          <t>E-TP2/10G, E-TP5/20G</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/0/%100)
-E - TP5/20G - %79 / 42 işlem - ADAY (15g/-1/%40)
-H - TP5/10G - %70 / 20 işlem - ADAY (3g/0/%100)
-H - TP5/20G - %80 / 20 işlem - ADAY (3g/0/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (15g/-1/%47)</t>
+          <t>E - TP2/10G - %87 / 62 işlem - ONAY (6g/+1/%100)
+E - TP5/20G - %79 / 42 işlem - ADAY (18g/-2/%25)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 36 hisse / 35 giriş gününe yayılıyor</t>
+          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>-1</v>
+        <v>4.1</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -3588,52 +3550,54 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
-ALT -  - 15/2 , ALT -  - 14/1 , -</t>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 15 - 3/7 , LONG - 28 - 3/9 , LONG - 6 - 5/7</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>M-TP5/20G, I-TP5/10G</t>
+          <t>E-TP5/20G, H-TP5/10G, H-TP5/20G, Q-TP5/20G</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (8g/-11/%92)
-I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (16g/+3/%100)
+H - TP5/10G - %70 / 20 işlem - ADAY (4g/+4/%100)
+H - TP5/20G - %80 / 20 işlem - ADAY (4g/+4/%100)
+Q - TP5/20G - %68 / 68 işlem - ADAY (16g/+3/%100)</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 54 hisse / 33 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, H: gecikmiş BSL sinyalinin yeniden test fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 33 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
+          <t>YOK</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>ANSGR</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -3647,36 +3611,36 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-ALT -  - 25/2 , ALT -  - 26/3 , ALT -  - 28/9</t>
+          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
+LONG - 1 - 9/1 , LONG - 1 - 9/1 , ALT -  - 11/0</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E-TP2/10G, E-TP5/20G</t>
+          <t>I-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>E - TP2/10G - %87 / 62 işlem - ONAY (5g/-1/%50)
-E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)</t>
+          <t>I - TP5/10G - %61 / 108 işlem - ADAY (1g/+2/%100)
+R - TP5/20G - %80 / 97 işlem - ADAY (14g/-7/%35)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ONAY E: PFY göreceli ucuzluk teyidi; ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 29 hisse / 38 giriş gününe yayılıyor</t>
+          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -3688,11 +3652,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MAVI</t>
+          <t>TUKAS</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -3707,11 +3671,11 @@
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 34/5 , ALT -  - 28/9 , ALT -  - 11/1</t>
+LONG - 16 - 14/7 , LONG - 2 - 15/2 , LONG - 28 - 3/6</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3724,17 +3688,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>R-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (9g/-6/%60)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/0/%95)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -3746,11 +3710,11 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PSGYO</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -3763,759 +3727,752 @@
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 1 - 10/3 , SHORT - 59 - 5/7 , LONG - 1 - 10/1</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>E-TP5/20G, Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (18g/-1/%25)
+Q - TP5/20G - %68 / 68 işlem - ADAY (18g/-1/%25)</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KUYAS</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 8 - 19/12 , LONG - 2 - 31/3 , UST -  - 1/11</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>U-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (4g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARCLK</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 1 - 21/1 , LONG - 3 - 27/6 , LONG - 3 - 4/6</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (14g/+3/%100)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TURSG</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>E-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IZENR</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 2 - 14/3 , LONG - 2 - 14/3 , -</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>I-TP2/10G, L-TP5/20G, L-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>I - TP2/10G - %87 / 114 işlem - ONAY (0g/0/%100)
+L - TP5/20G - %91 / 44 işlem - ONAY (4g/-1/%88)
+L - TP5/10G - %79 / 42 işlem - ADAY (4g/-1/%91)</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>ONAY I: endeks yükselirken göreceli geri kalma fırsatı, L: PHL istatistik teyidi; ADAY L: PHL istatistik teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 37 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TKFEN</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+SHORT - 15 - 10/7 , SHORT - 13 - 10/7 , LONG - 1 - 7/4</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>K-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (10g/-1/%69)</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CIMSA</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 28/5 , LONG - 1 - 11/2 , LONG - 2 - 6/4</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (2g/+5/%100)</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FROTO</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 2 - 26/7 , LONG - 77 - 5/14 , LONG - 1 - 22/0</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (19g/+4/%100)</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GENIL</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Q-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TRENJ</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+UST -  - 5/14 , UST -  - 4/13 , SHORT - 7 - 0/9</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/+2/%100)</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TOASO</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 3 - 3/9 , LONG - 21 - 11/13 , LONG - 3 - 0/9</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>S-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>S - TP2/10G - %91 / 57 işlem - ONAY (1g/+1/%100)</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>ONAY S: %4 üzeri fiyat momentumu teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 40 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BTCIM</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 56/42 , LONG - 3 - 34/1 , ALT -  - 16/5</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>L-TP5/10G, R-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (2g/-3/%91)
+R - TP2/10G - %84 / 118 işlem - ADAY (1g/-4/%75)</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 56 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MAGEN</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ELDEKİ</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
 -</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="F29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>R-TP5/20G</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (10g/-11/%40)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>R - TP5/20G - %80 / 97 işlem - ADAY (17g/-2/%30)</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 28 - 5/5 , LONG - 26 - 5/5 , LONG - 26 - 5/5</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+2/%100)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/+1/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (13g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 56 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL +1, XU030 +1, TOPLAM 0, ALMA
--</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/20G - %80 / 97 işlem - ADAY (16g/-4/%35)</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 60 hisse / 59 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BSOKE</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 50/35 , ALT -  - 70/26 , ALT -  - 50/35</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>L-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (4g/-12/%91)
-T - TP5/20G - %77 / 124 işlem - ADAY (18g/-35/%5)</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BRYAT</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-LONG - 2 - 9/2 , ALT -  - 30/11 , LONG - 27 - 21/5</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>R - TP2/10G - %84 / 118 işlem - ADAY (1g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 57 hisse / 63 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CCOLA</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-ALT -  - 12/1 , ALT -  - 12/1 , LONG - 3 - 15/2</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, I-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/-3/%55)
-I - TP5/20G - %84 / 49 işlem - ADAY (13g/-3/%77)
-Q - TP5/20G - %68 / 68 işlem - ADAY (13g/-3/%60)</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, I: endeks yükselirken göreceli geri kalma fırsatı, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ANSGR</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL +1, XU030 +1, TOPLAM 2, ALMA
-ALT -  - 11/1 , ALT -  - 12/2 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>I-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>I - TP5/10G - %61 / 108 işlem - ADAY (0g/0/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (13g/-8/%30)</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 1 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 61 hisse / 47 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CWENE</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-ALT -  - 11/0 , ALT -  - 11/0 , -</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>L-TP5/10G</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>L - TP5/10G - %79 / 42 işlem - ADAY (1g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>ADAY L: PHL istatistik teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 14 hisse / 36 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TUKAS</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 15 - 15/6 , LONG - 1 - 17/1 , LONG - 27 - 4/6</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-1/%90)</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ARCLK</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 25/2 , LONG - 2 - 30/4 , LONG - 2 - 6/4</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (13g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TURSG</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
--</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 13/1 , SHORT - 58 - 7/5 , ALT -  - 13/2</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>E-TP5/20G, Q-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (17g/-4/%25)
-Q - TP5/20G - %68 / 68 işlem - ADAY (17g/-4/%40)</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi, Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 41 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>EFOR</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 12/9 , SHORT - 34 - 12/12 , -</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>L-TP2/10G, M-TP5/20G, R-TP2/10G, R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (0g/0/%100)
-M - TP5/20G - %90 / 49 işlem - ONAY (6g/-6/%93)
-R - TP2/10G - %84 / 118 işlem - ADAY (0g/0/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (6g/-6/%40)
-R - TP5/20G - %80 / 97 işlem - ADAY (6g/-6/%60)</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>ONAY L: PHL istatistik teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 46 hisse / 53 giriş gününe yayılıyor</t>
-        </is>
-      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TKFEN</t>
+          <t>BSOKE</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>-1.8</v>
+        <v>-9.9</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
@@ -4529,51 +4486,52 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 14 - 15/2 , SHORT - 8 - 10/6 , ALT -  - 12/1</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+ALT -  - 41/4 , ALT -  - 88/39 , ALT -  - 64/48</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>K-TP5/20G</t>
+          <t>L-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (9g/-5/%71)</t>
+          <t>L - TP5/10G - %79 / 42 işlem - ADAY (5g/-21/%89)
+T - TP5/20G - %77 / 124 işlem - ADAY (19g/-41/%0)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ONAY K: PFY-S göreceli fırsat teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 42 hisse / 53 giriş gününe yayılıyor</t>
+          <t>ADAY L: PHL istatistik teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
@@ -4587,51 +4545,51 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 31/3 , ALT -  - 13/0 , LONG - 1 - 8/2</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+SHORT - 7 - 1/11 , SHORT - 7 - 0/11 , -</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>P-TP5/20G</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (1g/+3/%100)</t>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (12g/-5/%71)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Günlük artış %5 veya üzeri; alınmaz</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FROTO</t>
+          <t>ENJSA</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -4646,11 +4604,11 @@
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 1 - 32/3 , LONG - 76 - 9/11 , ALT -  - 27/4</t>
+LONG - 39 - 13/11 , SHORT - 7 - 2/7 , SHORT - 7 - 2/7</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G32" s="4" t="n">
         <v>0</v>
@@ -4663,33 +4621,33 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Q-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Q - TP5/20G - %68 / 68 işlem - ADAY (18g/0/%25)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 45 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>YOK</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SKBNK</t>
+          <t>OYAKC</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
@@ -4703,35 +4661,35 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
--</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 3 - 4/6 , SHORT - 9 - 4/6 , SHORT - 7 - 3/9</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (3g/-1/%87)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (9g/-3/%90)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -4743,11 +4701,11 @@
     <row r="34" ht="32" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>-0.2</v>
+        <v>3.3</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -4761,51 +4719,52 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>BIS -2, PHL +2, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-UST -  - 1/10 , SHORT - 1 - 0/9 , SHORT - 6 - 4/6</t>
+          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
+LONG - 5 - 4/6 , LONG - 5 - 3/7 , SHORT - 7 - 3/7</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
+          <t>T-TP5/10G, T-TP5/20G</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (11g/-3/%71)</t>
+          <t>T - TP5/10G - %65 / 140 işlem - ADAY (1g/+3/%100)
+T - TP5/20G - %77 / 124 işlem - ADAY (1g/+3/%100)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -4820,52 +4779,50 @@
       <c r="E35" s="3" t="inlineStr">
         <is>
           <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 5 - 3/7 , LONG - 4 - 6/4 , SHORT - 6 - 6/4</t>
+SHORT - 7 - 4/5 , SHORT - 7 - 4/5 , SHORT - 7 - 5/5</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Q-TP2/10G, T-TP5/10G, T-TP5/20G</t>
+          <t>U-TP5/20G</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Q - TP2/10G - %82 / 103 işlem - ADAY (1g/+1/%100)
-T - TP5/10G - %65 / 140 işlem - ADAY (0g/0/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (0g/0/%100)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (8g/-3/%90)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>ADAY Q: gecikmiş sinyal ve göreceli geri kalma teyidi, T: gap-down sonrası gün içi toparlanma teyidi; Bugün 2 sistem/profil yeni giriş veriyor; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 66 hisse / 57 giriş gününe yayılıyor</t>
+          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>TP5/20G ONAY yok; Yalnız ADAY sinyali; Açık pozisyon varken yeni işlem açılmaz; Güncel SAT/risk teyidi var; Risk sayısı 2</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENJSA</t>
+          <t>SAHOL</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>-0.6</v>
+        <v>2.6</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -4879,12 +4836,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 38 - 15/10 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 28 - 4/12 , LONG - 28 - 4/12 , LONG - 26 - 1/10</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>0</v>
@@ -4902,7 +4859,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (6g/-4/%80)</t>
+          <t>U - TP5/20G - %74 / 73 işlem - ADAY (12g/+4/%100)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -4912,18 +4869,18 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAHOL</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -4937,12 +4894,12 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 27 - 6/10 , LONG - 27 - 6/10 , LONG - 25 - 4/8</t>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+LONG - 6 - 4/7 , LONG - 2 - 6/4 , LONG - 1 - 8/2</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>
@@ -4955,33 +4912,33 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>U-TP5/20G</t>
+          <t>E-TP5/20G</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (11g/+2/%100)</t>
+          <t>E - TP5/20G - %79 / 42 işlem - ADAY (10g/-1/%58)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
+          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
+          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -4995,396 +4952,47 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 5 - 7/5 , LONG - 1 - 9/1 , ALT -  - 11/0</t>
+          <t>BIS +2, PHL +2, CNDL 0, XU030 +1, TOPLAM 5, AL
+LONG - 3 - 2/9 , SHORT - 28 - 16/15 , -</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>E-TP5/20G</t>
+          <t>M-TP5/20G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (9g/-4/%64)</t>
+          <t>M - TP5/20G - %90 / 49 işlem - ONAY (7g/-1/%93)
+R - TP5/10G - %62 / 63 işlem - ADAY (7g/-1/%40)
+R - TP5/20G - %80 / 97 işlem - ADAY (7g/-1/%85)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
+          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 49 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OYAKC</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 2 - 7/3 , SHORT - 8 - 6/4 , SHORT - 6 - 5/7</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>U-TP2/10G, U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>U - TP2/10G - %78 / 67 işlem - ADAY (9g/-4/%7)
-U - TP5/20G - %74 / 73 işlem - ADAY (8g/-5/%80)</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 44 hisse / 44 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ALARK</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-UST -  - 0/10 , UST -  - 0/10 , SHORT - 13 - 0/10</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>R-TP5/10G, R-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>R - TP5/10G - %62 / 63 işlem - ADAY (8g/+5/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (8g/+5/%100)</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>ADAY R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 53 hisse / 54 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ISCTR</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-LONG - 27 - 4/6 , LONG - 9 - 11/5 , LONG - 12 - 9/7</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>T-TP5/10G, T-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>T - TP5/10G - %65 / 140 işlem - ADAY (3g/+2/%100)
-T - TP5/20G - %77 / 124 işlem - ADAY (3g/+2/%100)</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>ADAY T: gap-down sonrası gün içi toparlanma teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 71 hisse / 55 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DOHOL</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
-SHORT - 6 - 4/6 , SHORT - 6 - 4/6 , SHORT - 6 - 4/6</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (7g/-2/%95)</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>KUYAS</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>BIS -2, PHL 0, CNDL -1, XU030 +1, TOPLAM -2, ALMA
-LONG - 7 - 22/10 , ALT -  - 44/6 , SHORT - 2 - 1/9</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>U-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>U - TP5/20G - %74 / 73 işlem - ADAY (3g/0/%90)</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>ADAY U: volatilite sıkışması sonrası kontrollü kırılım teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 50 hisse / 42 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Güncel SAT/risk teyidi var; Risk sayısı 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>HEKTS</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL +1, XU030 +1, TOPLAM 4, İZLE
-LONG - 1 - 35/0 , ALT -  - 21/3 , ALT -  - 14/1</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>E-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>E - TP5/20G - %79 / 42 işlem - ADAY (5g/+3/%100)</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>ADAY E: PFY göreceli ucuzluk teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 27 hisse / 30 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
           <t>Günlük artış %5 veya üzeri; alınmaz; Güncel SAT/risk teyidi var; Risk sayısı 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M44"/>
+  <autoFilter ref="A1:M38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TSBT_tr.xlsx
+++ b/TSBT_tr.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DUNKU_SONUCLAR" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HISSELER'!$A$1:$M$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DUNKU_SONUCLAR'!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -76,12 +76,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -539,31 +539,35 @@
           <t>KONTR</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 0, TOPLAM 0, ALMA</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+-</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4" t="n">
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -571,20 +575,20 @@
           <t>K-TP5/20G, M-TP5/20G</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>K - TP5/20G - %92 / 72 işlem - ONAY (13g/?/%?)
-M - TP5/20G - %90 / 49 işlem - ONAY (13g/?/%?)</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>K - TP5/20G - %92 / 72 işlem - ONAY (13g/-15/%64)
+M - TP5/20G - %90 / 49 işlem - ONAY (13g/-15/%78)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>ONAY K: PFY-S göreceli fırsat teyidi, M: TDA ve PFY-S birlikte dönüş teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 40 hisse / 42 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
@@ -594,35 +598,35 @@
           <t>ASTOR</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-LONG - 3 - 11/2 , LONG - 3 - 11/2 , -</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
+LONG - 3 - 13/0 , LONG - 3 - 13/0 , -</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -630,21 +634,21 @@
           <t>L-TP2/10G, P-TP5/20G, L-TP5/10G, R-TP5/10G, R-TP5/20G</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/+1/%100)
-P - TP5/20G - %91 / 43 işlem - ONAY (19g/-12/%33)
-L - TP5/10G - %79 / 42 işlem - ADAY (3g/+3/%100)
-R - TP5/10G - %62 / 63 işlem - ADAY (2g/+1/%100)
-R - TP5/20G - %80 / 97 işlem - ADAY (2g/+1/%100)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>L - TP2/10G - %100 / 52 işlem - ONAY (2g/0/%100)
+P - TP5/20G - %91 / 43 işlem - ONAY (19g/-13/%33)
+L - TP5/10G - %79 / 42 işlem - ADAY (3g/+2/%100)
+R - TP5/10G - %62 / 63 işlem - ADAY (2g/0/%95)
+R - TP5/20G - %80 / 97 işlem - ADAY (2g/0/%95)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>ONAY L: PHL istatistik teyidi, P: %3-%6 kontrollü momentum ve çoklu teyit; ADAY L: PHL istatistik teyidi, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 35 hisse / 48 giriş gününe yayılıyor</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
@@ -653,56 +657,56 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ALTNY</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          <t>FENER</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-SHORT - 8 - 2/10 , SHORT - 8 - 1/10 , -</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
+ALT -  - 11/1 , ALT -  - 11/1 , LONG - 2 - 12/1</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>P-TP5/20G</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>P - TP5/20G - %91 / 43 işlem - ONAY (13g/-6/%67)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
+          <t>H-TP2/10G</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-6/%73)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>YOK</t>
         </is>
@@ -711,494 +715,491 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FENER</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+          <t>ALTNY</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>İZLEME | ELDEKİ</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>BIS 0, PHL 0, CNDL 0, XU030 +1, TOPLAM 1, ALMA
-ALT -  - 11/1 , ALT -  - 11/1 , LONG - 2 - 11/1</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ELDE TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>BIS -2, PHL 0, CNDL 0, XU030 +1, TOPLAM -1, ALMA
+SHORT - 8 - 1/10 , SHORT - 8 - 1/11 , -</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>H-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>H - TP2/10G - %94 / 48 işlem - ONAY (6g/-5/%73)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>ONAY H: gecikmiş BSL sinyalinin yeniden test fırsatı; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 37 hisse / 41 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
+          <t>P-TP5/20G</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>P - TP5/20G - %91 / 43 işlem - ONAY (13g/-6/%67)</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>ONAY P: %3-%6 kontrollü momentum ve çoklu teyit; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 21 hisse / 39 giriş gününe yayılıyor</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Risk sayısı 1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUAGR</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>İZLEME | ELDEKİ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ELDE TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+          <t>MIATK</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>İZLEME</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>İZLE</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>BIS +2, PHL 0, CNDL 0, XU030 +1, TOPLAM 3, İZLE
-SHORT - 69 - 12/12 , LONG - 2 - 10/3 , -</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
+-</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <v>3</v>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M-TP5/20G, I-TP5/10G, R-TP2/10G</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>M - TP5/20G - %90 / 49 işlem - ONAY (10g/-8/%82)
-I - TP5/10G - %61 / 108 işlem - ADAY (2g/+3/%100)
-R - TP2/10G - %84 / 118 işlem - ADAY (1g/0/%100)</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>ONAY M: TDA ve PFY-S birlikte dönüş teyidi; ADAY I: endeks yükselirken göreceli geri kalma fırsatı, R: WMA5 erken dönüş ve WMA20 uzamama teyidi; Açık pozisyon devam ediyor; Sistem geçmişi yaklaşık 55 hisse / 46 giriş gününe yayılıyor</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>YOK</t>
+          <t>K-TP2/10G, K-TP5/10G</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>K - TP2/10G - %96 / 49 işlem - ONAY (0g/0/%100)
+K - TP5/10G - %85 / 40 işlem - ONAY (0g/0/%100)</t>
+        <